--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="47" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -488,20 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Godari Gattupaina.jpg</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>home/06-04-2026/Maa Behen.jpg</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Momacu</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -511,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -519,20 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Blast Zone.jpg</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>home/06-04-2026/Momacu.jpg</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ebWqjLUBgqE</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -542,7 +550,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -550,30 +558,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Carmeni Selvam.jpg</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>home/06-04-2026/Maa Behen.jpg</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Premam Madhuram</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -581,30 +593,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Kattalan.jpg</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
+          <t>home/06-04-2026/Premam Madhuram.jpg</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RkMt3-2m2mw</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Beast of War</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -612,20 +628,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Kara.jpg</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>home/06-04-2026/Beast of War.jpg</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -643,10 +663,9 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Sandigdham.jpg</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>home/06-02-2026/Godari Gattupaina.jpg</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -656,7 +675,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -674,10 +693,9 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Purushaha.jpg</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+          <t>home/06-02-2026/Blast Zone.jpg</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -687,7 +705,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -705,10 +723,9 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Ramani Kalyanam.jpg</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>home/06-02-2026/Carmeni Selvam.jpg</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -718,7 +735,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bhishmar</t>
+          <t>Kattalan</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -728,7 +745,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -736,10 +753,9 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Bhishmar.jpg</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>home/06-02-2026/Kattalan.jpg</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -749,7 +765,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Madhuvidhu</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -759,7 +775,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -767,10 +783,9 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Madhuvidhu.jpg</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>home/06-02-2026/Kara.jpg</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -780,12 +795,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Sandigdham</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -798,10 +813,9 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/06-02-2026/14.jpg</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>home/06-02-2026/Sandigdham.jpg</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -811,7 +825,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lee Cronin’s The Mummy</t>
+          <t>Purushaha</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -821,7 +835,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -829,10 +843,9 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Lee Cronin’s The Mummy.jpg</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>home/06-02-2026/Purushaha.jpg</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -842,7 +855,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Ramani Kalyanam</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -860,10 +873,9 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Carmeni Selvam.jpg</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>home/06-02-2026/Ramani Kalyanam.jpg</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -873,17 +885,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rescue Dawn</t>
+          <t>Bhishmar</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -891,10 +903,9 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Rescue Dawn.jpg</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>home/06-02-2026/Bhishmar.jpg</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -904,12 +915,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Aaahladam</t>
+          <t>Madhuvidhu</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -922,10 +933,9 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Aaahladam.jpg</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>home/06-02-2026/Madhuvidhu.jpg</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -935,12 +945,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -953,10 +963,9 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Trikala Script of God.jpg</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>home/06-02-2026/14.jpg</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -966,7 +975,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Lee Cronin’s The Mummy</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -976,7 +985,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -984,10 +993,9 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Blast Zone.jpg</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>home/06-02-2026/Lee Cronin’s The Mummy.jpg</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -997,7 +1005,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1015,10 +1023,9 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Kattalan.jpg</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>home/06-02-2026/Carmeni Selvam.jpg</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1028,17 +1035,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Rescue Dawn</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1046,10 +1053,9 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Sandigdham.jpg</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>home/06-02-2026/Rescue Dawn.jpg</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1059,17 +1065,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>The Exorcism Of Emily Rose</t>
+          <t>Aaahladam</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1077,10 +1083,9 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/06-02-2026/The Exorcism Of Emily Rose.jpg</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>home/06-02-2026/Aaahladam.jpg</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1090,7 +1095,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1100,7 +1105,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1108,10 +1113,9 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Kattalan.jpg</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>home/06-02-2026/Trikala Script of God.jpg</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1121,7 +1125,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1139,10 +1143,9 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Purushaha.jpg</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>home/06-02-2026/Blast Zone.jpg</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1152,7 +1155,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Faces</t>
+          <t>Kattalan</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1162,7 +1165,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1170,10 +1173,9 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Faces.jpg</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>home/06-02-2026/Kattalan.jpg</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>2026-06-02</t>
@@ -1183,29 +1185,178 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Sandigdham</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Sandigdham.jpg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>The Exorcism Of Emily Rose</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/The Exorcism Of Emily Rose.jpg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Kattalan</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Kattalan.jpg</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Purushaha</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Purushaha.jpg</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Faces</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Faces.jpg</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Nawab Cafe</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>home/06-02-2026/Nawab Cafe.jpg</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
@@ -1222,7 +1373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1251,6 +1402,16 @@
         <v>24</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/06-04-2026/Maa Behen.jpg</t>
+          <t>home/06-05-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Momacu</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -523,24 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/06-04-2026/Momacu.jpg</t>
+          <t>home/06-05-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ebWqjLUBgqE</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -558,34 +558,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/06-04-2026/Maa Behen.jpg</t>
+          <t>home/06-05-2026/29.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=qWSGdwHeKD4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Premam Madhuram</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -593,34 +593,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/06-04-2026/Premam Madhuram.jpg</t>
+          <t>home/06-05-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RkMt3-2m2mw</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -628,24 +628,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/06-04-2026/Beast of War.jpg</t>
+          <t>home/06-05-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -663,19 +663,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-05-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -685,7 +690,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -693,19 +698,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Blast Zone.jpg</t>
+          <t>home/06-05-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=T7vWnJ8yuQs</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -715,7 +725,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -723,19 +733,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-05-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -745,7 +760,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -753,19 +768,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Kattalan.jpg</t>
+          <t>home/06-05-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=qWSGdwHeKD4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -775,7 +795,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -783,19 +803,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Kara.jpg</t>
+          <t>home/06-05-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -805,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -813,19 +838,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Sandigdham.jpg</t>
+          <t>home/06-05-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -835,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -843,19 +873,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Purushaha.jpg</t>
+          <t>home/06-05-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Office Romance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -865,7 +900,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -873,19 +908,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-05-2026/Office Romance.jpg</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bhishmar</t>
+          <t>The Marked Woman</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -895,7 +935,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -903,19 +943,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Bhishmar.jpg</t>
+          <t>home/06-05-2026/The Marked Woman.jpg</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=161b4xLkokE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Madhuvidhu</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -925,7 +970,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -933,29 +978,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Madhuvidhu.jpg</t>
+          <t>home/06-05-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -963,19 +1013,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/06-02-2026/14.jpg</t>
+          <t>home/06-05-2026/Sukhamano Sukhamann.jpg</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lee Cronin’s The Mummy</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -985,7 +1040,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -993,19 +1048,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Lee Cronin’s The Mummy.jpg</t>
+          <t>home/06-05-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1023,24 +1083,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-05-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rescue Dawn</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1053,29 +1118,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Rescue Dawn.jpg</t>
+          <t>home/06-04-2026/Maa Behen.jpg</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Aaahladam</t>
+          <t>Momacu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1083,19 +1153,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Aaahladam.jpg</t>
+          <t>home/06-04-2026/Momacu.jpg</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=ebWqjLUBgqE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1105,7 +1180,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1113,29 +1188,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Trikala Script of God.jpg</t>
+          <t>home/06-04-2026/Maa Behen.jpg</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Premam Madhuram</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1143,29 +1223,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Blast Zone.jpg</t>
+          <t>home/06-04-2026/Premam Madhuram.jpg</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=RkMt3-2m2mw</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Beast of War</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1173,19 +1258,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Kattalan.jpg</t>
+          <t>home/06-04-2026/Beast of War.jpg</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1203,7 +1293,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Sandigdham.jpg</t>
+          <t>home/06-02-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1215,17 +1305,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>The Exorcism Of Emily Rose</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1233,7 +1323,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/06-02-2026/The Exorcism Of Emily Rose.jpg</t>
+          <t>home/06-02-2026/Blast Zone.jpg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1245,7 +1335,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1255,7 +1345,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1263,7 +1353,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Kattalan.jpg</t>
+          <t>home/06-02-2026/Carmeni Selvam.jpg</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1275,7 +1365,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Kattalan</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1293,7 +1383,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Purushaha.jpg</t>
+          <t>home/06-02-2026/Kattalan.jpg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1305,7 +1395,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Faces</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1315,7 +1405,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1323,7 +1413,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Faces.jpg</t>
+          <t>home/06-02-2026/Kara.jpg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1335,28 +1425,568 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Sandigdham</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Sandigdham.jpg</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Purushaha</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Purushaha.jpg</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ramani Kalyanam</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Ramani Kalyanam.jpg</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bhishmar</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Bhishmar.jpg</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Madhuvidhu</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Madhuvidhu.jpg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/14.jpg</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Lee Cronin’s The Mummy</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Lee Cronin’s The Mummy.jpg</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Carmeni Selvam</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Carmeni Selvam.jpg</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rescue Dawn</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Rescue Dawn.jpg</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Aaahladam</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Aaahladam.jpg</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trikala: Script of God</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Trikala Script of God.jpg</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Blast Zone</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Blast Zone.jpg</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Kattalan</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Kattalan.jpg</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Sandigdham</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Sandigdham.jpg</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>The Exorcism Of Emily Rose</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/The Exorcism Of Emily Rose.jpg</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Kattalan</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Kattalan.jpg</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Purushaha</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Purushaha.jpg</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Faces</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>home/06-02-2026/Faces.jpg</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>Nawab Cafe</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>home/06-02-2026/Nawab Cafe.jpg</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
@@ -1373,7 +2003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1395,11 +2025,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -1410,6 +2040,16 @@
       </c>
       <c r="B3" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,14 +418,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
     <col width="47" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
@@ -488,7 +488,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/06-05-2026/Peddi.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/06-05-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -558,24 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/06-05-2026/29.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qWSGdwHeKD4</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -593,24 +593,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/06-05-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -628,24 +628,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/06-05-2026/KD The Devil.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -663,24 +663,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/06-05-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -698,24 +698,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/06-05-2026/Peter.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=T7vWnJ8yuQs</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -733,24 +733,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/06-05-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,24 +768,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/06-05-2026/29.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qWSGdwHeKD4</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -803,24 +803,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/06-05-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,24 +838,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/06-05-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,24 +873,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/06-05-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Office Romance</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -908,24 +908,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/06-05-2026/Office Romance.jpg</t>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>The Marked Woman</t>
+          <t>Kattalan</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -943,24 +943,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/06-05-2026/The Marked Woman.jpg</t>
+          <t>home/06-06-2026/Kattalan.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=161b4xLkokE</t>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Ramani Kalyanam</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -978,34 +978,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/06-05-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>Beast of War</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,24 +1013,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/06-05-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-06-2026/Beast of War.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Sandigdham</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1048,24 +1048,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/06-05-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1083,24 +1083,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/06-05-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Kara.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1118,24 +1118,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/06-04-2026/Maa Behen.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Momacu</t>
+          <t>Purushaha</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/06-04-2026/Momacu.jpg</t>
+          <t>home/06-06-2026/Purushaha.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ebWqjLUBgqE</t>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1188,34 +1188,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/06-04-2026/Maa Behen.jpg</t>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Premam Madhuram</t>
+          <t>Summer House</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1223,34 +1223,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/06-04-2026/Premam Madhuram.jpg</t>
+          <t>home/06-06-2026/Summer House.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RkMt3-2m2mw</t>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1258,24 +1258,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/06-04-2026/Beast of War.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Juniors Journey</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1293,19 +1293,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Ginny Weds Sunny 2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1315,7 +1320,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1323,19 +1328,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Blast Zone.jpg</t>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1345,7 +1355,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1353,19 +1363,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-06-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1375,7 +1390,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1383,19 +1398,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Kattalan.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1405,7 +1425,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1413,19 +1433,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Kara.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1435,7 +1460,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1443,19 +1468,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Sandigdham.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1465,7 +1495,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1473,19 +1503,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Purushaha.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1495,7 +1530,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1503,19 +1538,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bhishmar</t>
+          <t>Office Romance</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1525,7 +1565,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1533,462 +1573,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/06-02-2026/Bhishmar.jpg</t>
+          <t>home/06-06-2026/Office Romance.jpg</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Madhuvidhu</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Malayalam</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>home/06-02-2026/Madhuvidhu.jpg</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Telugu</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>home/06-02-2026/14.jpg</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Lee Cronin’s The Mummy</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>home/06-02-2026/Lee Cronin’s The Mummy.jpg</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Carmeni Selvam</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Telugu</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>home/06-02-2026/Carmeni Selvam.jpg</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Rescue Dawn</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>home/06-02-2026/Rescue Dawn.jpg</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Aaahladam</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Malayalam</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>home/06-02-2026/Aaahladam.jpg</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Trikala: Script of God</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Telugu</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>home/06-02-2026/Trikala Script of God.jpg</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Blast Zone</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Telugu</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>home/06-02-2026/Blast Zone.jpg</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Kattalan</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Telugu</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>home/06-02-2026/Kattalan.jpg</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Sandigdham</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Telugu</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>home/06-02-2026/Sandigdham.jpg</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>The Exorcism Of Emily Rose</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>home/06-02-2026/The Exorcism Of Emily Rose.jpg</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Kattalan</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Hindi</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>home/06-02-2026/Kattalan.jpg</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Purushaha</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Telugu</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>home/06-02-2026/Purushaha.jpg</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Faces</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>home/06-02-2026/Faces.jpg</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Nawab Cafe</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>home/06-02-2026/Nawab Cafe.jpg</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -2003,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2025,31 +1620,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peddi.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,24 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Veerabhadrudu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -593,24 +593,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -628,24 +628,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -663,34 +663,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Pongala</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -698,24 +698,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-16-2026/Pongala.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
+          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -733,24 +733,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Trikala Script of God.jpg</t>
+          <t>home/06-16-2026/Shelter.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
+          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,24 +768,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Whistle.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -803,24 +803,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,34 +838,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>The Deep</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,34 +873,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Blast Zone.jpg</t>
+          <t>home/06-16-2026/The Deep.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Seven Years in Tibet</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -908,24 +908,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Maa Behen.jpg</t>
+          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Kolahalamedu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -943,24 +943,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kattalan.jpg</t>
+          <t>home/06-16-2026/Kolahalamedu.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -978,34 +978,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-16-2026/Normal.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,24 +1013,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Beast of War.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Vikalpa</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1048,24 +1048,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sandigdham.jpg</t>
+          <t>home/06-16-2026/Vikalpa.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1083,24 +1083,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kara.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Karuppu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1118,24 +1118,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Karuppu.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Sshhh Season 3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Purushaha.jpg</t>
+          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Hai Jawani Toh Ishq Hona Hai</t>
+          <t>R.L. Stine’s Pumpkinhead</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1188,24 +1188,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Summer House</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Summer House.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1240,7 +1240,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1275,7 +1275,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Juniors Journey</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Juniors Journey.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1310,7 +1310,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ginny Weds Sunny 2</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1328,12 +1328,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1345,7 +1345,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peter.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1415,7 +1415,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1450,7 +1450,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1485,7 +1485,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1520,7 +1520,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1555,33 +1555,768 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Carmeni Selvam</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Blast Zone</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Maa Behen</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Kattalan</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Kattalan.jpg</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Ramani Kalyanam</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Beast of War</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Beast of War.jpg</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sandigdham</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Kara</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Kara.jpg</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>KD: The Devil</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Purushaha</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Purushaha.jpg</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Summer House</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Summer House.jpg</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Juniors Journey</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ginny Weds Sunny 2</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ugly Story</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Office Romance</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>Telugu Dubbed</t>
         </is>
       </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
         <is>
           <t>home/06-06-2026/Office Romance.jpg</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
@@ -1598,7 +2333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1620,10 +2355,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,24 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Veerabhadrudu</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -593,24 +593,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sattendru Maarudhu Vaanilai</t>
+          <t>Thank You Subbarao</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -628,24 +628,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
+          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -663,29 +663,29 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pongala</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -698,24 +698,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Pongala.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Husbands in Action</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -733,24 +733,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Shelter.jpg</t>
+          <t>home/06-19-2026/Husbands in Action.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
+          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Whistle</t>
+          <t>Cocktail 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,24 +768,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Whistle.jpg</t>
+          <t>home/06-19-2026/Cocktail 2.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
+          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -803,24 +803,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Voicemails for Isabelle</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,34 +838,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>The Deep</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,34 +873,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/06-16-2026/The Deep.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Seven Years in Tibet</t>
+          <t>Save The Tigers Season 3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -908,24 +908,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
+          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
+          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kolahalamedu</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -943,34 +943,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kolahalamedu.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>The Grey Men 2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -978,24 +978,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Normal.jpg</t>
+          <t>home/06-19-2026/The Grey Men 2.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
+          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,24 +1013,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Vikalpa</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1048,24 +1048,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Vikalpa.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1083,24 +1083,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Karuppu</t>
+          <t>Mortal Kombat 2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1118,24 +1118,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Karuppu.jpg</t>
+          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
+          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sshhh Season 3</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1170,7 +1170,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R.L. Stine’s Pumpkinhead</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1205,7 +1205,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Veerabhadrudu</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peddi.jpg</t>
+          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
+          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1258,24 +1258,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1328,34 +1328,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Pongala</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1363,24 +1363,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Pongala.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1398,24 +1398,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-16-2026/Shelter.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1433,24 +1433,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-16-2026/Whistle.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
+          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1468,24 +1468,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Trikala Script of God.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1503,34 +1503,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>The Deep</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1538,34 +1538,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-16-2026/The Deep.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Seven Years in Tibet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1573,24 +1573,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Kolahalamedu</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1608,24 +1608,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Blast Zone.jpg</t>
+          <t>home/06-16-2026/Kolahalamedu.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Maa Behen.jpg</t>
+          <t>home/06-16-2026/Normal.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1678,24 +1678,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kattalan.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Vikalpa</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1713,34 +1713,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-16-2026/Vikalpa.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1748,24 +1748,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Beast of War.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Karuppu</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sandigdham.jpg</t>
+          <t>home/06-16-2026/Karuppu.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Sshhh Season 3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1818,24 +1818,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kara.jpg</t>
+          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>R.L. Stine’s Pumpkinhead</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1853,24 +1853,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Purushaha.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1905,7 +1905,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Hai Jawani Toh Ishq Hona Hai</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1940,7 +1940,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Summer House</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Summer House.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1975,7 +1975,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Juniors Journey</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2028,12 +2028,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Juniors Journey.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ginny Weds Sunny 2</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peter.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2115,7 +2115,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2150,7 +2150,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2185,7 +2185,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2220,7 +2220,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2290,33 +2290,698 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Maa Behen</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Kattalan</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Kattalan.jpg</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ramani Kalyanam</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Beast of War</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Beast of War.jpg</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sandigdham</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Kara</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Kara.jpg</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>KD: The Devil</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Purushaha</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Purushaha.jpg</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Summer House</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Summer House.jpg</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Juniors Journey</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Ginny Weds Sunny 2</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Ugly Story</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>Office Romance</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
         <is>
           <t>Telugu Dubbed</t>
         </is>
       </c>
-      <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="inlineStr">
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="inlineStr">
         <is>
           <t>home/06-06-2026/Office Romance.jpg</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
@@ -2333,7 +2998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2355,20 +3020,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Maa Inti Bangaaram</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Deewana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,24 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Deewana.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Vanda Devullu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/Vanda Devullu.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -593,24 +593,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Thank You Subbarao</t>
+          <t>M4M: Motive for Murder</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -628,24 +628,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
+          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
+          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Blast</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -663,34 +663,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Blast.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
+          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Avatar: Fire and Ash</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -698,24 +698,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Husbands in Action</t>
+          <t>The Sheep Detectives</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -733,34 +733,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Husbands in Action.jpg</t>
+          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
+          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cocktail 2</t>
+          <t>Gladiator Underground</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,24 +768,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Cocktail 2.jpg</t>
+          <t>home/06-24-2026/Gladiator Underground.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
+          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -803,24 +803,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Voicemails for Isabelle</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,24 +838,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Painkili</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,34 +873,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/Painkili.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Save The Tigers Season 3</t>
+          <t>Seems Like Old Times</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -908,34 +908,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
+          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
+          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>The Furies</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -943,34 +943,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/The Furies.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>The Grey Men 2</t>
+          <t>Garbham</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -978,34 +978,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/06-19-2026/The Grey Men 2.jpg</t>
+          <t>home/06-24-2026/Garbham.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
+          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Blind Waters</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,24 +1013,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Blind Waters.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1048,12 +1048,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mortal Kombat 2</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Thank You Subbarao</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1188,24 +1188,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Veerabhadrudu</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
+          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1258,24 +1258,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sattendru Maarudhu Vaanilai</t>
+          <t>Husbands in Action</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+          <t>home/06-19-2026/Husbands in Action.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
+          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Cocktail 2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1328,34 +1328,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Cocktail 2.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pongala</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1363,24 +1363,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Pongala.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Voicemails for Isabelle</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1398,24 +1398,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Shelter.jpg</t>
+          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
+          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Whistle</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1433,24 +1433,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Whistle.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Save The Tigers Season 3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1468,24 +1468,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1503,29 +1503,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>The Deep</t>
+          <t>The Grey Men 2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1538,34 +1538,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/06-16-2026/The Deep.jpg</t>
+          <t>home/06-19-2026/The Grey Men 2.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
+          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Seven Years in Tibet</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1573,24 +1573,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Kolahalamedu</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1608,24 +1608,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kolahalamedu.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Normal.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Mortal Kombat 2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1678,24 +1678,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Vikalpa</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Vikalpa.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1730,7 +1730,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1765,7 +1765,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Karuppu</t>
+          <t>Veerabhadrudu</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Karuppu.jpg</t>
+          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
+          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1800,7 +1800,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sshhh Season 3</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>R.L. Stine’s Pumpkinhead</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
+          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
+          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1870,7 +1870,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1888,34 +1888,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peddi.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Pongala</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1923,24 +1923,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-16-2026/Pongala.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1958,24 +1958,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-16-2026/Shelter.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1993,24 +1993,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Whistle.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2028,24 +2028,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2063,34 +2063,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>The Deep</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2098,34 +2098,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-16-2026/The Deep.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
+          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>Seven Years in Tibet</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2133,24 +2133,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Trikala Script of God.jpg</t>
+          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
+          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Kolahalamedu</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2168,24 +2168,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Kolahalamedu.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2203,24 +2203,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-16-2026/Normal.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Vikalpa</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2273,24 +2273,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Blast Zone.jpg</t>
+          <t>home/06-16-2026/Vikalpa.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2308,24 +2308,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Maa Behen.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Karuppu</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2343,24 +2343,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kattalan.jpg</t>
+          <t>home/06-16-2026/Karuppu.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Sshhh Season 3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2378,29 +2378,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>R.L. Stine’s Pumpkinhead</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2413,24 +2413,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Beast of War.jpg</t>
+          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sandigdham.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2465,7 +2465,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kara.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2500,7 +2500,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2535,7 +2535,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Purushaha.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2570,7 +2570,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Hai Jawani Toh Ishq Hona Hai</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Summer House</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Summer House.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2640,7 +2640,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2675,7 +2675,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Juniors Journey</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Juniors Journey.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2710,7 +2710,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ginny Weds Sunny 2</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peter.jpg</t>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2780,7 +2780,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2815,7 +2815,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2885,7 +2885,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Kattalan</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Kattalan.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2920,7 +2920,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Ramani Kalyanam</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2955,33 +2955,593 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>Beast of War</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Beast of War.jpg</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sandigdham</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Kara</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Kara.jpg</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>KD: The Devil</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Purushaha</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Purushaha.jpg</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Summer House</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Summer House.jpg</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Juniors Journey</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Ginny Weds Sunny 2</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Ugly Story</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>Office Romance</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
         <is>
           <t>Telugu Dubbed</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="inlineStr">
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
         <is>
           <t>home/06-06-2026/Office Romance.jpg</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
@@ -2998,7 +3558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3020,30 +3580,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B5" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Maa Inti Bangaaram</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deewana</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -523,24 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Deewana.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Vanda Devullu</t>
+          <t>Lingam Season 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Vanda Devullu.jpg</t>
+          <t>home/06-25-2026/Lingam Season 1.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
+          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Moondram Kan</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -593,24 +593,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-25-2026/Moondram Kan.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M4M: Motive for Murder</t>
+          <t>Raja Shivaji</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -628,24 +628,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
+          <t>home/06-25-2026/Raja Shivaji.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
+          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Blast</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -663,34 +663,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blast.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Avatar: Fire and Ash</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -698,24 +698,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>The Sheep Detectives</t>
+          <t>In the Hand of Dante</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -733,34 +733,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
+          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
+          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gladiator Underground</t>
+          <t>Maa Inti Bangaaram</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,12 +768,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Gladiator Underground.jpg</t>
+          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
+          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -785,7 +785,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Deewana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-24-2026/Deewana.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -820,7 +820,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Vanda Devullu</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,12 +838,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-24-2026/Vanda Devullu.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -855,7 +855,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Painkili</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,12 +873,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Painkili.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -890,17 +890,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Seems Like Old Times</t>
+          <t>M4M: Motive for Murder</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -908,12 +908,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
+          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
+          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -925,17 +925,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>The Furies</t>
+          <t>Blast</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -943,12 +943,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Furies.jpg</t>
+          <t>home/06-24-2026/Blast.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
+          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -960,17 +960,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Garbham</t>
+          <t>Avatar: Fire and Ash</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -978,12 +978,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Garbham.jpg</t>
+          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
+          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -995,17 +995,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Blind Waters</t>
+          <t>The Sheep Detectives</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blind Waters.jpg</t>
+          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
+          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1030,17 +1030,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Gladiator Underground</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1048,24 +1048,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Gladiator Underground.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1083,24 +1083,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1118,24 +1118,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Painkili</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1153,34 +1153,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Painkili.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Thank You Subbarao</t>
+          <t>Seems Like Old Times</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1188,34 +1188,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
+          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
+          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>The Furies</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/The Furies.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
+          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Garbham</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1258,34 +1258,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Garbham.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Husbands in Action</t>
+          <t>Blind Waters</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Husbands in Action.jpg</t>
+          <t>home/06-24-2026/Blind Waters.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
+          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cocktail 2</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1328,12 +1328,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Cocktail 2.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1345,7 +1345,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1380,7 +1380,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Voicemails for Isabelle</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1450,7 +1450,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Save The Tigers Season 3</t>
+          <t>Thank You Subbarao</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
+          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
+          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1485,7 +1485,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1520,17 +1520,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>The Grey Men 2</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/06-19-2026/The Grey Men 2.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Husbands in Action</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Husbands in Action.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1590,7 +1590,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Cocktail 2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-19-2026/Cocktail 2.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1625,7 +1625,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1660,7 +1660,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mortal Kombat 2</t>
+          <t>Voicemails for Isabelle</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
+          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
+          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1713,24 +1713,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Save The Tigers Season 3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1748,24 +1748,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Veerabhadrudu</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1783,34 +1783,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>The Grey Men 2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1818,24 +1818,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/The Grey Men 2.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sattendru Maarudhu Vaanilai</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1853,24 +1853,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1888,34 +1888,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pongala</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1923,24 +1923,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Pongala.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Mortal Kombat 2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1958,24 +1958,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Shelter.jpg</t>
+          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
+          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Whistle</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Whistle.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Veerabhadrudu</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2080,17 +2080,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>The Deep</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>home/06-16-2026/The Deep.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2115,17 +2115,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Seven Years in Tibet</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
+          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
+          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2150,7 +2150,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kolahalamedu</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kolahalamedu.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2185,12 +2185,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Pongala</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Normal.jpg</t>
+          <t>home/06-16-2026/Pongala.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
+          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2220,7 +2220,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-16-2026/Shelter.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vikalpa</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Vikalpa.jpg</t>
+          <t>home/06-16-2026/Whistle.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
+          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2290,7 +2290,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2325,7 +2325,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Karuppu</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Karuppu.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2360,17 +2360,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sshhh Season 3</t>
+          <t>The Deep</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
+          <t>home/06-16-2026/The Deep.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
+          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2395,12 +2395,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>R.L. Stine’s Pumpkinhead</t>
+          <t>Seven Years in Tibet</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
+          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
+          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2430,7 +2430,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Kolahalamedu</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2448,24 +2448,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peddi.jpg</t>
+          <t>home/06-16-2026/Kolahalamedu.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
+          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2483,24 +2483,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-16-2026/Normal.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2518,24 +2518,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Vikalpa</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2553,24 +2553,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Vikalpa.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Karuppu</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2623,24 +2623,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-16-2026/Karuppu.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Sshhh Season 3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2658,24 +2658,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
+          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>R.L. Stine’s Pumpkinhead</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2693,24 +2693,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Trikala Script of God.jpg</t>
+          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
+          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2780,7 +2780,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2815,7 +2815,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Blast Zone.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Maa Behen.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2885,7 +2885,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kattalan.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2920,7 +2920,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2955,17 +2955,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Beast of War.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sandigdham.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3025,7 +3025,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kara.jpg</t>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3060,7 +3060,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3095,7 +3095,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Purushaha.jpg</t>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3130,7 +3130,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Hai Jawani Toh Ishq Hona Hai</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3165,7 +3165,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Summer House</t>
+          <t>Kattalan</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Summer House.jpg</t>
+          <t>home/06-06-2026/Kattalan.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3200,7 +3200,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Ramani Kalyanam</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3235,17 +3235,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Juniors Journey</t>
+          <t>Beast of War</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Juniors Journey.jpg</t>
+          <t>home/06-06-2026/Beast of War.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3270,7 +3270,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ginny Weds Sunny 2</t>
+          <t>Sandigdham</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3305,7 +3305,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peter.jpg</t>
+          <t>home/06-06-2026/Kara.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3340,7 +3340,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3375,7 +3375,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Purushaha</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/Purushaha.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3410,7 +3410,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Summer House</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Summer House.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3480,7 +3480,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3515,33 +3515,313 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>Juniors Journey</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Ginny Weds Sunny 2</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Ugly Story</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
           <t>Office Romance</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
         <is>
           <t>Telugu Dubbed</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" t="inlineStr">
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="inlineStr">
         <is>
           <t>home/06-06-2026/Office Romance.jpg</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
@@ -3558,7 +3838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3580,40 +3860,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B6" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -523,24 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lingam Season 1</t>
+          <t>Elra Kaaleliyatte Kaala</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -558,24 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Lingam Season 1.jpg</t>
+          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
+          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Moondram Kan</t>
+          <t>Hunting Jessica Brok</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -593,24 +593,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Moondram Kan.jpg</t>
+          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
+          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Raja Shivaji</t>
+          <t>Obsession</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -628,34 +628,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Raja Shivaji.jpg</t>
+          <t>home/07-01-2026/Obsession.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
+          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Continental Split</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -663,34 +663,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-01-2026/Continental Split.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Great White Waters</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -698,34 +698,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-01-2026/Great White Waters.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>In the Hand of Dante</t>
+          <t>Road Wars: Max Fury</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -733,24 +733,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
+          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
+          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Maa Inti Bangaaram</t>
+          <t>Supergirl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,34 +768,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
+          <t>home/07-01-2026/Supergirl.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
+          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deewana</t>
+          <t>The Last Breath</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -803,24 +803,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Deewana.jpg</t>
+          <t>home/07-01-2026/The Last Breath.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
+          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Vanda Devullu</t>
+          <t>Little Brother</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,24 +838,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Vanda Devullu.jpg</t>
+          <t>home/07-01-2026/Little Brother.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
+          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,24 +873,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M4M: Motive for Murder</t>
+          <t>The Yeti</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -908,24 +908,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
+          <t>home/07-01-2026/The Yeti.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
+          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Blast</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -943,34 +943,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blast.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Avatar: Fire and Ash</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -978,24 +978,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>The Sheep Detectives</t>
+          <t>Lingam Season 1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,34 +1013,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
+          <t>home/06-25-2026/Lingam Season 1.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
+          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Gladiator Underground</t>
+          <t>Moondram Kan</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1048,24 +1048,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Gladiator Underground.jpg</t>
+          <t>home/06-25-2026/Moondram Kan.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
+          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Raja Shivaji</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1083,24 +1083,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-25-2026/Raja Shivaji.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1118,24 +1118,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Painkili</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1153,29 +1153,29 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Painkili.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Seems Like Old Times</t>
+          <t>In the Hand of Dante</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1188,34 +1188,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
+          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
+          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>The Furies</t>
+          <t>Maa Inti Bangaaram</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Furies.jpg</t>
+          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
+          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1240,7 +1240,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Garbham</t>
+          <t>Deewana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Garbham.jpg</t>
+          <t>home/06-24-2026/Deewana.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
+          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1275,17 +1275,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Blind Waters</t>
+          <t>Vanda Devullu</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blind Waters.jpg</t>
+          <t>home/06-24-2026/Vanda Devullu.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
+          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1310,7 +1310,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1328,24 +1328,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>M4M: Motive for Murder</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1363,24 +1363,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Blast</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1398,34 +1398,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/Blast.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Avatar: Fire and Ash</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1433,24 +1433,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Thank You Subbarao</t>
+          <t>The Sheep Detectives</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1468,34 +1468,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
+          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
+          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Gladiator Underground</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1503,24 +1503,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Gladiator Underground.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
+          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1538,24 +1538,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Husbands in Action</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1573,24 +1573,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Husbands in Action.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cocktail 2</t>
+          <t>Painkili</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1608,34 +1608,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Cocktail 2.jpg</t>
+          <t>home/06-24-2026/Painkili.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
+          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Seems Like Old Times</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1643,34 +1643,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Voicemails for Isabelle</t>
+          <t>The Furies</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1678,24 +1678,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
+          <t>home/06-24-2026/The Furies.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
+          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Garbham</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1713,34 +1713,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/Garbham.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Save The Tigers Season 3</t>
+          <t>Blind Waters</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1748,24 +1748,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
+          <t>home/06-24-2026/Blind Waters.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
+          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1800,17 +1800,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>The Grey Men 2</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>home/06-19-2026/The Grey Men 2.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1905,7 +1905,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Thank You Subbarao</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1940,7 +1940,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mortal Kombat 2</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
+          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1975,7 +1975,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1993,24 +1993,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Husbands in Action</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2028,24 +2028,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Husbands in Action.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Veerabhadrudu</t>
+          <t>Cocktail 2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2063,24 +2063,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
+          <t>home/06-19-2026/Cocktail 2.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
+          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2098,24 +2098,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sattendru Maarudhu Vaanilai</t>
+          <t>Voicemails for Isabelle</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2133,24 +2133,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
+          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2168,34 +2168,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pongala</t>
+          <t>Save The Tigers Season 3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2203,24 +2203,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Pongala.jpg</t>
+          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
+          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2238,29 +2238,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Shelter.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Whistle</t>
+          <t>The Grey Men 2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2273,24 +2273,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Whistle.jpg</t>
+          <t>home/06-19-2026/The Grey Men 2.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
+          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2308,24 +2308,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2343,34 +2343,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>The Deep</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2378,29 +2378,29 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>home/06-16-2026/The Deep.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Seven Years in Tibet</t>
+          <t>Mortal Kombat 2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2413,24 +2413,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
+          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
+          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Kolahalamedu</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kolahalamedu.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2465,7 +2465,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Normal.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2500,7 +2500,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Veerabhadrudu</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2535,7 +2535,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Vikalpa</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Vikalpa.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2570,7 +2570,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Karuppu</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Karuppu.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2640,17 +2640,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sshhh Season 3</t>
+          <t>Pongala</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
+          <t>home/06-16-2026/Pongala.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
+          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2675,7 +2675,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>R.L. Stine’s Pumpkinhead</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
+          <t>home/06-16-2026/Shelter.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
+          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2710,7 +2710,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peddi.jpg</t>
+          <t>home/06-16-2026/Whistle.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
+          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2763,24 +2763,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2798,34 +2798,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>The Deep</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2833,34 +2833,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/The Deep.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Seven Years in Tibet</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2868,24 +2868,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Kolahalamedu</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2903,24 +2903,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-16-2026/Kolahalamedu.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2938,24 +2938,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-16-2026/Normal.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
+          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2973,24 +2973,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Trikala Script of God.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Vikalpa</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3008,24 +3008,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Vikalpa.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3043,24 +3043,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Karuppu</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3078,24 +3078,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-16-2026/Karuppu.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Sshhh Season 3</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3113,24 +3113,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Blast Zone.jpg</t>
+          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>R.L. Stine’s Pumpkinhead</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3148,24 +3148,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Maa Behen.jpg</t>
+          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kattalan.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3200,7 +3200,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3235,17 +3235,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Beast of War.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3270,7 +3270,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sandigdham.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3305,7 +3305,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kara.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3340,7 +3340,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3375,7 +3375,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Purushaha.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3410,7 +3410,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Hai Jawani Toh Ishq Hona Hai</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Summer House</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Summer House.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3480,7 +3480,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3515,7 +3515,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Juniors Journey</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Juniors Journey.jpg</t>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3550,7 +3550,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ginny Weds Sunny 2</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3585,7 +3585,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peter.jpg</t>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3620,7 +3620,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Kattalan</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Kattalan.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3655,7 +3655,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Ramani Kalyanam</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3690,17 +3690,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Beast of War</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Beast of War.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3725,7 +3725,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Sandigdham</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3760,7 +3760,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Kara.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3795,33 +3795,488 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>KD: The Devil</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Purushaha</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Purushaha.jpg</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Summer House</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Summer House.jpg</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Juniors Journey</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Ginny Weds Sunny 2</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Ugly Story</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>Office Romance</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
         <is>
           <t>Telugu Dubbed</t>
         </is>
       </c>
-      <c r="D97" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" t="inlineStr">
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr">
         <is>
           <t>home/06-06-2026/Office Romance.jpg</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
@@ -3838,7 +4293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3860,50 +4315,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B7" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -523,24 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Elra Kaaleliyatte Kaala</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -558,24 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hunting Jessica Brok</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -593,34 +593,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Obsession</t>
+          <t>Bossa Nova</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -628,34 +628,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Obsession.jpg</t>
+          <t>home/07-02-2026/Bossa Nova.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
+          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Continental Split</t>
+          <t>Super Dog and Super Cat</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -663,34 +663,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Continental Split.jpg</t>
+          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
+          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Great White Waters</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -698,12 +698,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Great White Waters.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -715,17 +715,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Road Wars: Max Fury</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -733,12 +733,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Supergirl</t>
+          <t>Elra Kaaleliyatte Kaala</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,12 +768,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Supergirl.jpg</t>
+          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
+          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -785,12 +785,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>The Last Breath</t>
+          <t>Hunting Jessica Brok</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Last Breath.jpg</t>
+          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
+          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -820,7 +820,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Little Brother</t>
+          <t>Obsession</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,12 +838,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Little Brother.jpg</t>
+          <t>home/07-01-2026/Obsession.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
+          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -855,17 +855,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Continental Split</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,12 +873,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
+          <t>home/07-01-2026/Continental Split.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
+          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -890,17 +890,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>The Yeti</t>
+          <t>Great White Waters</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -908,12 +908,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Yeti.jpg</t>
+          <t>home/07-01-2026/Great White Waters.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
+          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -925,17 +925,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Road Wars: Max Fury</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -943,24 +943,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Supergirl</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -978,34 +978,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-01-2026/Supergirl.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lingam Season 1</t>
+          <t>The Last Breath</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,24 +1013,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Lingam Season 1.jpg</t>
+          <t>home/07-01-2026/The Last Breath.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
+          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Moondram Kan</t>
+          <t>Little Brother</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1048,24 +1048,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Moondram Kan.jpg</t>
+          <t>home/07-01-2026/Little Brother.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
+          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Raja Shivaji</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1083,24 +1083,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Raja Shivaji.jpg</t>
+          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
+          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>The Yeti</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1118,24 +1118,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-01-2026/The Yeti.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1170,7 +1170,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>In the Hand of Dante</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1205,7 +1205,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Maa Inti Bangaaram</t>
+          <t>Lingam Season 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
+          <t>home/06-25-2026/Lingam Season 1.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
+          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deewana</t>
+          <t>Moondram Kan</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1258,24 +1258,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Deewana.jpg</t>
+          <t>home/06-25-2026/Moondram Kan.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
+          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Vanda Devullu</t>
+          <t>Raja Shivaji</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Vanda Devullu.jpg</t>
+          <t>home/06-25-2026/Raja Shivaji.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
+          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1328,24 +1328,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>M4M: Motive for Murder</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1363,24 +1363,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Blast</t>
+          <t>In the Hand of Dante</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1398,34 +1398,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blast.jpg</t>
+          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
+          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Avatar: Fire and Ash</t>
+          <t>Maa Inti Bangaaram</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
+          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
+          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1450,7 +1450,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>The Sheep Detectives</t>
+          <t>Deewana</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
+          <t>home/06-24-2026/Deewana.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
+          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1485,17 +1485,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gladiator Underground</t>
+          <t>Vanda Devullu</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Gladiator Underground.jpg</t>
+          <t>home/06-24-2026/Vanda Devullu.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
+          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>M4M: Motive for Murder</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1590,7 +1590,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Painkili</t>
+          <t>Blast</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Painkili.jpg</t>
+          <t>home/06-24-2026/Blast.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
+          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1625,12 +1625,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Seems Like Old Times</t>
+          <t>Avatar: Fire and Ash</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
+          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
+          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1660,17 +1660,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>The Furies</t>
+          <t>The Sheep Detectives</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Furies.jpg</t>
+          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
+          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1695,17 +1695,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Garbham</t>
+          <t>Gladiator Underground</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Garbham.jpg</t>
+          <t>home/06-24-2026/Gladiator Underground.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
+          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1730,17 +1730,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Blind Waters</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blind Waters.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1765,7 +1765,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Painkili</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1818,34 +1818,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Painkili.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Seems Like Old Times</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1853,34 +1853,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>The Furies</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1888,24 +1888,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/The Furies.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Thank You Subbarao</t>
+          <t>Garbham</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1923,34 +1923,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
+          <t>home/06-24-2026/Garbham.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
+          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Blind Waters</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1958,17 +1958,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Blind Waters.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
+          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2010,7 +2010,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Husbands in Action</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2028,12 +2028,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Husbands in Action.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cocktail 2</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Cocktail 2.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2115,7 +2115,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Voicemails for Isabelle</t>
+          <t>Thank You Subbarao</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
+          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
+          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2150,7 +2150,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2185,7 +2185,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Save The Tigers Season 3</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2220,7 +2220,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Husbands in Action</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-19-2026/Husbands in Action.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2255,17 +2255,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>The Grey Men 2</t>
+          <t>Cocktail 2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>home/06-19-2026/The Grey Men 2.jpg</t>
+          <t>home/06-19-2026/Cocktail 2.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
+          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2290,7 +2290,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2325,7 +2325,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Voicemails for Isabelle</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2360,7 +2360,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2395,7 +2395,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mortal Kombat 2</t>
+          <t>Save The Tigers Season 3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
+          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
+          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2430,7 +2430,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2448,34 +2448,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>The Grey Men 2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2483,24 +2483,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/The Grey Men 2.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Veerabhadrudu</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2518,24 +2518,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2553,24 +2553,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sattendru Maarudhu Vaanilai</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Mortal Kombat 2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2623,34 +2623,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Pongala</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Pongala.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2675,7 +2675,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Shelter.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2710,7 +2710,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Whistle</t>
+          <t>Veerabhadrudu</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Whistle.jpg</t>
+          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
+          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2780,7 +2780,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2815,17 +2815,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>The Deep</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>home/06-16-2026/The Deep.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2850,17 +2850,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Seven Years in Tibet</t>
+          <t>Pongala</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
+          <t>home/06-16-2026/Pongala.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
+          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2885,7 +2885,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kolahalamedu</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kolahalamedu.jpg</t>
+          <t>home/06-16-2026/Shelter.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
+          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2920,7 +2920,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Normal.jpg</t>
+          <t>home/06-16-2026/Whistle.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
+          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2955,7 +2955,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Vikalpa</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Vikalpa.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3025,17 +3025,17 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>The Deep</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-16-2026/The Deep.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3060,17 +3060,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Karuppu</t>
+          <t>Seven Years in Tibet</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Karuppu.jpg</t>
+          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
+          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3095,7 +3095,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sshhh Season 3</t>
+          <t>Kolahalamedu</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
+          <t>home/06-16-2026/Kolahalamedu.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
+          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3130,7 +3130,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>R.L. Stine’s Pumpkinhead</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
+          <t>home/06-16-2026/Normal.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
+          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3165,7 +3165,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3183,24 +3183,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peddi.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Vikalpa</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3218,24 +3218,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-16-2026/Vikalpa.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3253,24 +3253,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Karuppu</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3288,24 +3288,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Karuppu.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Sshhh Season 3</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3323,24 +3323,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>R.L. Stine’s Pumpkinhead</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3358,24 +3358,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3410,7 +3410,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Trikala Script of God.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3480,7 +3480,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3515,7 +3515,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3550,7 +3550,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Blast Zone.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3585,7 +3585,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Maa Behen.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3620,7 +3620,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kattalan.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3655,7 +3655,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3690,17 +3690,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Beast of War.jpg</t>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3725,7 +3725,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sandigdham.jpg</t>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3760,7 +3760,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kara.jpg</t>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3795,7 +3795,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Kattalan</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Purushaha.jpg</t>
+          <t>home/06-06-2026/Kattalan.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3865,7 +3865,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Hai Jawani Toh Ishq Hona Hai</t>
+          <t>Ramani Kalyanam</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3900,12 +3900,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Summer House</t>
+          <t>Beast of War</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Summer House.jpg</t>
+          <t>home/06-06-2026/Beast of War.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3935,7 +3935,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Sandigdham</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3970,7 +3970,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Juniors Journey</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Juniors Journey.jpg</t>
+          <t>home/06-06-2026/Kara.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4005,7 +4005,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ginny Weds Sunny 2</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4040,7 +4040,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Purushaha</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peter.jpg</t>
+          <t>home/06-06-2026/Purushaha.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4075,7 +4075,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Summer House</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/Summer House.jpg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4180,7 +4180,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Juniors Journey</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4215,7 +4215,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Ginny Weds Sunny 2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4250,33 +4250,243 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Ugly Story</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
           <t>Office Romance</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
         <is>
           <t>Telugu Dubbed</t>
         </is>
       </c>
-      <c r="D110" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" t="inlineStr">
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="inlineStr">
         <is>
           <t>home/06-06-2026/Office Romance.jpg</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
@@ -4293,7 +4503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4315,60 +4525,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B8" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,24 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -558,24 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -593,34 +593,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bossa Nova</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -628,24 +628,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Bossa Nova.jpg</t>
+          <t>home/07-03-2026/Alpha.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
+          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Super Dog and Super Cat</t>
+          <t>Pritam and Pedro Season 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -663,24 +663,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
+          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
+          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Charukesi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -698,24 +698,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-03-2026/Charukesi.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -733,24 +733,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Elra Kaaleliyatte Kaala</t>
+          <t>Daadi Ki Shaadi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,24 +768,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
+          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
+          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hunting Jessica Brok</t>
+          <t>Hangman</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -803,24 +803,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
+          <t>home/07-03-2026/Hangman.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
+          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Obsession</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,34 +838,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Obsession.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Continental Split</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,34 +873,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Continental Split.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Great White Waters</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -908,34 +908,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Great White Waters.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Road Wars: Max Fury</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -943,24 +943,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Supergirl</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -978,34 +978,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Supergirl.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>The Last Breath</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,24 +1013,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Last Breath.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Little Brother</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1048,24 +1048,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Little Brother.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1083,24 +1083,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>The Yeti</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1118,34 +1118,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Yeti.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Bossa Nova</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-02-2026/Bossa Nova.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Super Dog and Super Cat</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1188,24 +1188,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lingam Season 1</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Lingam Season 1.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Moondram Kan</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1258,24 +1258,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Moondram Kan.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Raja Shivaji</t>
+          <t>Elra Kaaleliyatte Kaala</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Raja Shivaji.jpg</t>
+          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
+          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Hunting Jessica Brok</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1328,24 +1328,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Obsession</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1363,34 +1363,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-01-2026/Obsession.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>In the Hand of Dante</t>
+          <t>Continental Split</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1398,34 +1398,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
+          <t>home/07-01-2026/Continental Split.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
+          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Maa Inti Bangaaram</t>
+          <t>Great White Waters</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1433,34 +1433,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
+          <t>home/07-01-2026/Great White Waters.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
+          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Deewana</t>
+          <t>Road Wars: Max Fury</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1468,24 +1468,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Deewana.jpg</t>
+          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
+          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Vanda Devullu</t>
+          <t>Supergirl</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1503,34 +1503,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Vanda Devullu.jpg</t>
+          <t>home/07-01-2026/Supergirl.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
+          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>The Last Breath</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1538,24 +1538,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/07-01-2026/The Last Breath.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>M4M: Motive for Murder</t>
+          <t>Little Brother</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1573,24 +1573,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
+          <t>home/07-01-2026/Little Brother.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
+          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Blast</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1608,29 +1608,29 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blast.jpg</t>
+          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
+          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Avatar: Fire and Ash</t>
+          <t>The Yeti</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
+          <t>home/07-01-2026/The Yeti.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
+          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>The Sheep Detectives</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1678,34 +1678,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Gladiator Underground</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1713,24 +1713,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Gladiator Underground.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Lingam Season 1</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1748,24 +1748,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-25-2026/Lingam Season 1.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Moondram Kan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-25-2026/Moondram Kan.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Painkili</t>
+          <t>Raja Shivaji</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1818,34 +1818,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Painkili.jpg</t>
+          <t>home/06-25-2026/Raja Shivaji.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
+          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Seems Like Old Times</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1853,34 +1853,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>The Furies</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1888,24 +1888,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Furies.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Garbham</t>
+          <t>In the Hand of Dante</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1923,34 +1923,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Garbham.jpg</t>
+          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
+          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Blind Waters</t>
+          <t>Maa Inti Bangaaram</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blind Waters.jpg</t>
+          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
+          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1975,7 +1975,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Deewana</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1993,24 +1993,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Deewana.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Vanda Devullu</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2028,24 +2028,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Vanda Devullu.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2063,24 +2063,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>M4M: Motive for Murder</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2098,24 +2098,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Thank You Subbarao</t>
+          <t>Blast</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2133,34 +2133,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
+          <t>home/06-24-2026/Blast.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
+          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Avatar: Fire and Ash</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2168,24 +2168,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
+          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>The Sheep Detectives</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2203,29 +2203,29 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Husbands in Action</t>
+          <t>Gladiator Underground</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Husbands in Action.jpg</t>
+          <t>home/06-24-2026/Gladiator Underground.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
+          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cocktail 2</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2273,24 +2273,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Cocktail 2.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2308,24 +2308,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Voicemails for Isabelle</t>
+          <t>Painkili</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2343,34 +2343,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
+          <t>home/06-24-2026/Painkili.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
+          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Seems Like Old Times</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2378,34 +2378,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Save The Tigers Season 3</t>
+          <t>The Furies</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2413,24 +2413,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
+          <t>home/06-24-2026/The Furies.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
+          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Garbham</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2448,34 +2448,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/Garbham.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>The Grey Men 2</t>
+          <t>Blind Waters</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2483,24 +2483,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>home/06-19-2026/The Grey Men 2.jpg</t>
+          <t>home/06-24-2026/Blind Waters.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
+          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2535,7 +2535,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2570,7 +2570,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mortal Kombat 2</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2640,7 +2640,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Thank You Subbarao</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2658,24 +2658,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2693,24 +2693,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Veerabhadrudu</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Husbands in Action</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2763,24 +2763,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Husbands in Action.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sattendru Maarudhu Vaanilai</t>
+          <t>Cocktail 2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2798,24 +2798,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+          <t>home/06-19-2026/Cocktail 2.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
+          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2833,34 +2833,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Pongala</t>
+          <t>Voicemails for Isabelle</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2868,24 +2868,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Pongala.jpg</t>
+          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
+          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2903,24 +2903,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Shelter.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Whistle</t>
+          <t>Save The Tigers Season 3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2938,24 +2938,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Whistle.jpg</t>
+          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
+          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2973,34 +2973,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>The Grey Men 2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3008,34 +3008,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/The Grey Men 2.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>The Deep</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3043,34 +3043,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>home/06-16-2026/The Deep.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Seven Years in Tibet</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3078,24 +3078,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Kolahalamedu</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3113,24 +3113,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kolahalamedu.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Mortal Kombat 2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3148,17 +3148,17 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Normal.jpg</t>
+          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
+          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3200,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Vikalpa</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Vikalpa.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3235,7 +3235,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Veerabhadrudu</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3270,7 +3270,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Karuppu</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Karuppu.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3305,7 +3305,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sshhh Season 3</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
+          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
+          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3340,7 +3340,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>R.L. Stine’s Pumpkinhead</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3375,17 +3375,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Pongala</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3393,24 +3393,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peddi.jpg</t>
+          <t>home/06-16-2026/Pongala.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
+          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3428,24 +3428,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-16-2026/Shelter.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3463,24 +3463,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-16-2026/Whistle.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3498,24 +3498,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3533,34 +3533,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>The Deep</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3568,34 +3568,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-16-2026/The Deep.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Seven Years in Tibet</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3603,24 +3603,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
+          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>Kolahalamedu</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3638,24 +3638,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Trikala Script of God.jpg</t>
+          <t>home/06-16-2026/Kolahalamedu.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
+          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3673,24 +3673,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Normal.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3708,24 +3708,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Vikalpa</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3743,24 +3743,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-16-2026/Vikalpa.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3778,24 +3778,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Blast Zone.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Karuppu</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3813,24 +3813,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Maa Behen.jpg</t>
+          <t>home/06-16-2026/Karuppu.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Sshhh Season 3</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3848,24 +3848,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kattalan.jpg</t>
+          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>R.L. Stine’s Pumpkinhead</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3883,34 +3883,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Beast of War.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3935,7 +3935,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sandigdham.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3970,7 +3970,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kara.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4040,7 +4040,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Purushaha.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4075,7 +4075,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Hai Jawani Toh Ishq Hona Hai</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Summer House</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Summer House.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4145,7 +4145,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4180,7 +4180,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Juniors Journey</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Juniors Journey.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4215,7 +4215,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Ginny Weds Sunny 2</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4250,7 +4250,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peter.jpg</t>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4285,7 +4285,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4320,7 +4320,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4355,7 +4355,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Kattalan</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Kattalan.jpg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Ramani Kalyanam</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4425,17 +4425,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Beast of War</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Beast of War.jpg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4460,33 +4460,558 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>Sandigdham</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Kara</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Kara.jpg</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>KD: The Devil</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Purushaha</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Purushaha.jpg</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Summer House</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Summer House.jpg</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Juniors Journey</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Ginny Weds Sunny 2</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Ugly Story</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
           <t>Office Romance</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
         <is>
           <t>Telugu Dubbed</t>
         </is>
       </c>
-      <c r="D116" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" t="inlineStr">
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="inlineStr">
         <is>
           <t>home/06-06-2026/Office Romance.jpg</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
@@ -4503,7 +5028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4525,70 +5050,80 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,17 +523,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -585,7 +585,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -610,7 +610,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -628,12 +628,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Alpha.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pritam and Pedro Season 1</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -663,12 +663,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -680,7 +680,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Charukesi</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -698,12 +698,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Charukesi.jpg</t>
+          <t>home/07-03-2026/Alpha.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
+          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Pritam and Pedro Season 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -733,12 +733,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Daadi Ki Shaadi</t>
+          <t>Charukesi</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,12 +768,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
+          <t>home/07-03-2026/Charukesi.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
+          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -785,7 +785,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hangman</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -803,12 +803,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Hangman.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -820,7 +820,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Daadi Ki Shaadi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,12 +838,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -855,7 +855,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Hangman</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,12 +873,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-03-2026/Hangman.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -935,7 +935,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -960,7 +960,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -995,7 +995,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1013,24 +1013,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1048,17 +1048,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -1135,17 +1135,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bossa Nova</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Bossa Nova.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1170,7 +1170,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Super Dog and Super Cat</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1205,12 +1205,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Bossa Nova</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-02-2026/Bossa Nova.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Super Dog and Super Cat</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1258,24 +1258,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Elra Kaaleliyatte Kaala</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1310,7 +1310,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hunting Jessica Brok</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1328,12 +1328,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1345,7 +1345,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Obsession</t>
+          <t>Elra Kaaleliyatte Kaala</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Obsession.jpg</t>
+          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
+          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1380,17 +1380,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Continental Split</t>
+          <t>Hunting Jessica Brok</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Continental Split.jpg</t>
+          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
+          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Great White Waters</t>
+          <t>Obsession</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Great White Waters.jpg</t>
+          <t>home/07-01-2026/Obsession.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
+          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1450,7 +1450,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Road Wars: Max Fury</t>
+          <t>Continental Split</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
+          <t>home/07-01-2026/Continental Split.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
+          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1485,17 +1485,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Supergirl</t>
+          <t>Great White Waters</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Supergirl.jpg</t>
+          <t>home/07-01-2026/Great White Waters.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
+          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1520,7 +1520,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>The Last Breath</t>
+          <t>Road Wars: Max Fury</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Last Breath.jpg</t>
+          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
+          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Little Brother</t>
+          <t>Supergirl</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Little Brother.jpg</t>
+          <t>home/07-01-2026/Supergirl.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
+          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1590,17 +1590,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>The Last Breath</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
+          <t>home/07-01-2026/The Last Breath.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
+          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1625,7 +1625,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>The Yeti</t>
+          <t>Little Brother</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Yeti.jpg</t>
+          <t>home/07-01-2026/Little Brother.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
+          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1660,7 +1660,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1678,24 +1678,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>The Yeti</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1713,24 +1713,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-01-2026/The Yeti.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lingam Season 1</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Lingam Season 1.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1765,7 +1765,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Moondram Kan</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Moondram Kan.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1800,7 +1800,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Raja Shivaji</t>
+          <t>Lingam Season 1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Raja Shivaji.jpg</t>
+          <t>home/06-25-2026/Lingam Season 1.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
+          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Moondram Kan</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/06-25-2026/Moondram Kan.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1870,7 +1870,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Raja Shivaji</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/06-25-2026/Raja Shivaji.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1905,7 +1905,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>In the Hand of Dante</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1940,7 +1940,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Maa Inti Bangaaram</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1958,24 +1958,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Deewana</t>
+          <t>In the Hand of Dante</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1993,24 +1993,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Deewana.jpg</t>
+          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
+          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Vanda Devullu</t>
+          <t>Maa Inti Bangaaram</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2028,12 +2028,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Vanda Devullu.jpg</t>
+          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
+          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2045,7 +2045,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Deewana</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-24-2026/Deewana.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>M4M: Motive for Murder</t>
+          <t>Vanda Devullu</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
+          <t>home/06-24-2026/Vanda Devullu.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
+          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2115,7 +2115,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Blast</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blast.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2150,17 +2150,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Avatar: Fire and Ash</t>
+          <t>M4M: Motive for Murder</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
+          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
+          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2185,7 +2185,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>The Sheep Detectives</t>
+          <t>Blast</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
+          <t>home/06-24-2026/Blast.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
+          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2220,7 +2220,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Gladiator Underground</t>
+          <t>Avatar: Fire and Ash</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Gladiator Underground.jpg</t>
+          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
+          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>The Sheep Detectives</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2290,17 +2290,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Gladiator Underground</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-24-2026/Gladiator Underground.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2325,7 +2325,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Painkili</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Painkili.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2360,17 +2360,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Seems Like Old Times</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2395,17 +2395,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>The Furies</t>
+          <t>Painkili</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Furies.jpg</t>
+          <t>home/06-24-2026/Painkili.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
+          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2430,17 +2430,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Garbham</t>
+          <t>Seems Like Old Times</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Garbham.jpg</t>
+          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
+          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2465,12 +2465,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Blind Waters</t>
+          <t>The Furies</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blind Waters.jpg</t>
+          <t>home/06-24-2026/The Furies.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
+          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2500,7 +2500,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Garbham</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2518,34 +2518,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Garbham.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Blind Waters</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2553,24 +2553,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Blind Waters.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2640,7 +2640,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Thank You Subbarao</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2710,7 +2710,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Thank You Subbarao</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Husbands in Action</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Husbands in Action.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
+          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2780,7 +2780,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cocktail 2</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Cocktail 2.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2815,7 +2815,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Husbands in Action</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-19-2026/Husbands in Action.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Voicemails for Isabelle</t>
+          <t>Cocktail 2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
+          <t>home/06-19-2026/Cocktail 2.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
+          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2920,7 +2920,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Save The Tigers Season 3</t>
+          <t>Voicemails for Isabelle</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
+          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
+          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2955,7 +2955,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2990,17 +2990,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>The Grey Men 2</t>
+          <t>Save The Tigers Season 3</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>home/06-19-2026/The Grey Men 2.jpg</t>
+          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
+          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3025,7 +3025,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3060,17 +3060,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>The Grey Men 2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-19-2026/The Grey Men 2.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3130,7 +3130,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mortal Kombat 2</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3165,7 +3165,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3183,24 +3183,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Mortal Kombat 2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3218,24 +3218,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Veerabhadrudu</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3270,7 +3270,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3305,7 +3305,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sattendru Maarudhu Vaanilai</t>
+          <t>Veerabhadrudu</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
+          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3375,17 +3375,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Pongala</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Pongala.jpg</t>
+          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
+          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3410,7 +3410,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Shelter.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3445,17 +3445,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Whistle</t>
+          <t>Pongala</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Whistle.jpg</t>
+          <t>home/06-16-2026/Pongala.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
+          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3480,7 +3480,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-16-2026/Shelter.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3515,7 +3515,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-16-2026/Whistle.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3550,17 +3550,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>The Deep</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>home/06-16-2026/The Deep.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3585,17 +3585,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Seven Years in Tibet</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3620,17 +3620,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Kolahalamedu</t>
+          <t>The Deep</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kolahalamedu.jpg</t>
+          <t>home/06-16-2026/The Deep.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
+          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3655,17 +3655,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Seven Years in Tibet</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Normal.jpg</t>
+          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
+          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Kolahalamedu</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-16-2026/Kolahalamedu.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3725,7 +3725,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Vikalpa</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Vikalpa.jpg</t>
+          <t>home/06-16-2026/Normal.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
+          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3760,7 +3760,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3795,7 +3795,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Karuppu</t>
+          <t>Vikalpa</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Karuppu.jpg</t>
+          <t>home/06-16-2026/Vikalpa.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
+          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sshhh Season 3</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3865,7 +3865,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>R.L. Stine’s Pumpkinhead</t>
+          <t>Karuppu</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
+          <t>home/06-16-2026/Karuppu.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
+          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3900,7 +3900,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Sshhh Season 3</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3918,24 +3918,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peddi.jpg</t>
+          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
+          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>R.L. Stine’s Pumpkinhead</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3953,24 +3953,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4005,7 +4005,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4040,7 +4040,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4075,7 +4075,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4145,7 +4145,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Trikala Script of God.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4180,7 +4180,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4215,7 +4215,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4250,7 +4250,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4285,7 +4285,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Blast Zone.jpg</t>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4320,7 +4320,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Maa Behen.jpg</t>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4355,7 +4355,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kattalan.jpg</t>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4425,17 +4425,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>Kattalan</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Beast of War.jpg</t>
+          <t>home/06-06-2026/Kattalan.jpg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4460,7 +4460,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Ramani Kalyanam</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sandigdham.jpg</t>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4495,17 +4495,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Beast of War</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kara.jpg</t>
+          <t>home/06-06-2026/Beast of War.jpg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4530,7 +4530,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Sandigdham</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4565,7 +4565,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Purushaha.jpg</t>
+          <t>home/06-06-2026/Kara.jpg</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4600,7 +4600,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Hai Jawani Toh Ishq Hona Hai</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4635,7 +4635,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Summer House</t>
+          <t>Purushaha</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Summer House.jpg</t>
+          <t>home/06-06-2026/Purushaha.jpg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4670,7 +4670,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4705,7 +4705,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Juniors Journey</t>
+          <t>Summer House</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4723,12 +4723,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Juniors Journey.jpg</t>
+          <t>home/06-06-2026/Summer House.jpg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4740,7 +4740,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ginny Weds Sunny 2</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4775,7 +4775,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Juniors Journey</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4793,12 +4793,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peter.jpg</t>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4810,7 +4810,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Ginny Weds Sunny 2</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4845,7 +4845,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/Peter.jpg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4880,7 +4880,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4915,7 +4915,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4933,12 +4933,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4950,7 +4950,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4985,33 +4985,103 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>Ugly Story</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
           <t>Office Romance</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
         <is>
           <t>Telugu Dubbed</t>
         </is>
       </c>
-      <c r="D131" t="n">
-        <v>1</v>
-      </c>
-      <c r="E131" t="inlineStr">
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
         <is>
           <t>home/06-06-2026/Office Romance.jpg</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
@@ -5028,7 +5098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5050,80 +5120,90 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B10" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G133"/>
+  <dimension ref="A1:G138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Chand Mera Dil</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -523,24 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-06-2026/Chand Mera Dil.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=rRQ8oKCoYrQ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Kotha Malupu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-06-2026/Kotha Malupu.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=qnd1Xwv9NP8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Double Barrel</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -593,24 +593,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-06-2026/Double Barrel.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=Ij0mjRt1QIA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -628,24 +628,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -663,24 +663,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -698,24 +698,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Alpha.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pritam and Pedro Season 1</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -750,7 +750,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Charukesi</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,12 +768,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Charukesi.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -820,7 +820,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Daadi Ki Shaadi</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,12 +838,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -855,7 +855,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hangman</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,12 +873,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Hangman.jpg</t>
+          <t>home/07-03-2026/Alpha.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
+          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Pritam and Pedro Season 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -925,7 +925,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Charukesi</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-03-2026/Charukesi.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -995,7 +995,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Daadi Ki Shaadi</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1030,7 +1030,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Hangman</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1048,12 +1048,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-03-2026/Hangman.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1083,24 +1083,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1118,24 +1118,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1188,34 +1188,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bossa Nova</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Bossa Nova.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Super Dog and Super Cat</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1275,7 +1275,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1328,24 +1328,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Elra Kaaleliyatte Kaala</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1363,29 +1363,29 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Hunting Jessica Brok</t>
+          <t>Bossa Nova</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1398,24 +1398,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
+          <t>home/07-02-2026/Bossa Nova.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
+          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Obsession</t>
+          <t>Super Dog and Super Cat</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1433,34 +1433,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Obsession.jpg</t>
+          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
+          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Continental Split</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Continental Split.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1485,17 +1485,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Great White Waters</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Great White Waters.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1520,17 +1520,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Road Wars: Max Fury</t>
+          <t>Elra Kaaleliyatte Kaala</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
+          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
+          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Supergirl</t>
+          <t>Hunting Jessica Brok</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Supergirl.jpg</t>
+          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
+          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1590,17 +1590,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>The Last Breath</t>
+          <t>Obsession</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Last Breath.jpg</t>
+          <t>home/07-01-2026/Obsession.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
+          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1625,17 +1625,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Little Brother</t>
+          <t>Continental Split</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Little Brother.jpg</t>
+          <t>home/07-01-2026/Continental Split.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
+          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1660,17 +1660,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Great White Waters</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
+          <t>home/07-01-2026/Great White Waters.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
+          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1695,17 +1695,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>The Yeti</t>
+          <t>Road Wars: Max Fury</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Yeti.jpg</t>
+          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
+          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1730,7 +1730,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Supergirl</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1748,34 +1748,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-01-2026/Supergirl.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>The Last Breath</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-01-2026/The Last Breath.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lingam Season 1</t>
+          <t>Little Brother</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1818,24 +1818,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Lingam Season 1.jpg</t>
+          <t>home/07-01-2026/Little Brother.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
+          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Moondram Kan</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1853,24 +1853,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Moondram Kan.jpg</t>
+          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
+          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Raja Shivaji</t>
+          <t>The Yeti</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1888,17 +1888,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Raja Shivaji.jpg</t>
+          <t>home/07-01-2026/The Yeti.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
+          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>In the Hand of Dante</t>
+          <t>Lingam Season 1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1993,12 +1993,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
+          <t>home/06-25-2026/Lingam Season 1.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
+          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Maa Inti Bangaaram</t>
+          <t>Moondram Kan</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2028,24 +2028,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
+          <t>home/06-25-2026/Moondram Kan.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
+          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Deewana</t>
+          <t>Raja Shivaji</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2063,24 +2063,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Deewana.jpg</t>
+          <t>home/06-25-2026/Raja Shivaji.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
+          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Vanda Devullu</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2098,24 +2098,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Vanda Devullu.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2133,24 +2133,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>M4M: Motive for Murder</t>
+          <t>In the Hand of Dante</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2168,24 +2168,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
+          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
+          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Blast</t>
+          <t>Maa Inti Bangaaram</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blast.jpg</t>
+          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
+          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2220,17 +2220,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Avatar: Fire and Ash</t>
+          <t>Deewana</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
+          <t>home/06-24-2026/Deewana.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
+          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>The Sheep Detectives</t>
+          <t>Vanda Devullu</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
+          <t>home/06-24-2026/Vanda Devullu.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
+          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2290,17 +2290,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Gladiator Underground</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Gladiator Underground.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2325,7 +2325,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>M4M: Motive for Murder</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2360,7 +2360,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Blast</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-24-2026/Blast.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2395,17 +2395,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Painkili</t>
+          <t>Avatar: Fire and Ash</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Painkili.jpg</t>
+          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
+          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2430,12 +2430,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Seems Like Old Times</t>
+          <t>The Sheep Detectives</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
+          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
+          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2465,17 +2465,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>The Furies</t>
+          <t>Gladiator Underground</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Furies.jpg</t>
+          <t>home/06-24-2026/Gladiator Underground.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
+          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2500,7 +2500,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Garbham</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Garbham.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2535,17 +2535,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Blind Waters</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blind Waters.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2570,7 +2570,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Painkili</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2588,34 +2588,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Painkili.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Seems Like Old Times</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2623,34 +2623,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>The Furies</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2658,24 +2658,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/The Furies.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Garbham</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2693,34 +2693,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Garbham.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Thank You Subbarao</t>
+          <t>Blind Waters</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
+          <t>home/06-24-2026/Blind Waters.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
+          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2780,7 +2780,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2815,7 +2815,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Husbands in Action</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Husbands in Action.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cocktail 2</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Cocktail 2.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2885,7 +2885,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Thank You Subbarao</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2920,7 +2920,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Voicemails for Isabelle</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
+          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2955,7 +2955,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Save The Tigers Season 3</t>
+          <t>Husbands in Action</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
+          <t>home/06-19-2026/Husbands in Action.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
+          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3025,7 +3025,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Cocktail 2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-19-2026/Cocktail 2.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3060,17 +3060,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>The Grey Men 2</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>home/06-19-2026/The Grey Men 2.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3095,7 +3095,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Voicemails for Isabelle</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3130,7 +3130,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3165,7 +3165,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Save The Tigers Season 3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3200,7 +3200,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mortal Kombat 2</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3235,17 +3235,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>The Grey Men 2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3253,24 +3253,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/The Grey Men 2.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3288,24 +3288,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Veerabhadrudu</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3323,24 +3323,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3358,24 +3358,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sattendru Maarudhu Vaanilai</t>
+          <t>Mortal Kombat 2</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3393,24 +3393,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
+          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3445,17 +3445,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Pongala</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Pongala.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3480,7 +3480,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Veerabhadrudu</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Shelter.jpg</t>
+          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
+          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3515,7 +3515,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Whistle</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Whistle.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3550,7 +3550,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3568,12 +3568,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3585,7 +3585,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3620,17 +3620,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>The Deep</t>
+          <t>Pongala</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>home/06-16-2026/The Deep.jpg</t>
+          <t>home/06-16-2026/Pongala.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
+          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3655,12 +3655,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Seven Years in Tibet</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
+          <t>home/06-16-2026/Shelter.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
+          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Kolahalamedu</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kolahalamedu.jpg</t>
+          <t>home/06-16-2026/Whistle.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
+          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3725,7 +3725,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Normal.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3760,7 +3760,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3795,17 +3795,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Vikalpa</t>
+          <t>The Deep</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Vikalpa.jpg</t>
+          <t>home/06-16-2026/The Deep.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
+          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3830,17 +3830,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Seven Years in Tibet</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3865,7 +3865,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Karuppu</t>
+          <t>Kolahalamedu</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Karuppu.jpg</t>
+          <t>home/06-16-2026/Kolahalamedu.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
+          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3900,7 +3900,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Sshhh Season 3</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
+          <t>home/06-16-2026/Normal.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
+          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3935,7 +3935,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>R.L. Stine’s Pumpkinhead</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3970,7 +3970,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Vikalpa</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3988,24 +3988,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peddi.jpg</t>
+          <t>home/06-16-2026/Vikalpa.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
+          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4023,24 +4023,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Karuppu</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4058,24 +4058,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-16-2026/Karuppu.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Sshhh Season 3</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4093,24 +4093,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>R.L. Stine’s Pumpkinhead</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4128,24 +4128,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4180,7 +4180,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4215,7 +4215,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Trikala Script of God.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4250,7 +4250,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4285,7 +4285,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4320,7 +4320,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4355,7 +4355,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Blast Zone.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Maa Behen.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4425,7 +4425,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kattalan.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4460,7 +4460,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4495,17 +4495,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Beast of War.jpg</t>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4530,7 +4530,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sandigdham.jpg</t>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4565,7 +4565,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kara.jpg</t>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4600,7 +4600,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Kattalan</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-06-2026/Kattalan.jpg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4635,7 +4635,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Ramani Kalyanam</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Purushaha.jpg</t>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4670,17 +4670,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Hai Jawani Toh Ishq Hona Hai</t>
+          <t>Beast of War</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+          <t>home/06-06-2026/Beast of War.jpg</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4705,7 +4705,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Summer House</t>
+          <t>Sandigdham</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4723,12 +4723,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Summer House.jpg</t>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4740,7 +4740,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Kara.jpg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4775,7 +4775,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Juniors Journey</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4793,12 +4793,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Juniors Journey.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4810,7 +4810,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ginny Weds Sunny 2</t>
+          <t>Purushaha</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+          <t>home/06-06-2026/Purushaha.jpg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4845,7 +4845,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peter.jpg</t>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4880,7 +4880,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Summer House</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Summer House.jpg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4915,7 +4915,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4933,12 +4933,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4950,7 +4950,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Juniors Journey</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4985,7 +4985,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Ginny Weds Sunny 2</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5020,7 +5020,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Peter.jpg</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5055,33 +5055,208 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Ugly Story</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
           <t>Office Romance</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
         <is>
           <t>Telugu Dubbed</t>
         </is>
       </c>
-      <c r="D133" t="n">
-        <v>1</v>
-      </c>
-      <c r="E133" t="inlineStr">
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="inlineStr">
         <is>
           <t>home/06-06-2026/Office Romance.jpg</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="G138" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
@@ -5098,7 +5273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5120,90 +5295,100 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B11" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G138"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Nagabandham</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Nagabandham.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chand Mera Dil</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -515,7 +515,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -523,24 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Chand Mera Dil.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rRQ8oKCoYrQ</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kotha Malupu</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Kotha Malupu.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qnd1Xwv9NP8</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Double Barrel</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -593,24 +593,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Double Barrel.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Ij0mjRt1QIA</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nagabandham</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -628,24 +628,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Nagabandham.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -663,24 +663,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -698,24 +698,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Pati Patni Aur Woh Do</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -733,24 +733,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Pati Patni Aur Woh Do.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=ceooxuS-sww</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,24 +768,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -803,24 +803,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,24 +838,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,24 +873,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Alpha.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pritam and Pedro Season 1</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,24 +908,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Charukesi</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -943,24 +943,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Charukesi.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -978,24 +978,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Daadi Ki Shaadi</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,24 +1013,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hangman</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1048,24 +1048,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Hangman.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Chand Mera Dil</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1083,24 +1083,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-06-2026/Chand Mera Dil.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=rRQ8oKCoYrQ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Kotha Malupu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1118,24 +1118,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-06-2026/Kotha Malupu.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=qnd1Xwv9NP8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Double Barrel</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-06-2026/Double Barrel.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=Ij0mjRt1QIA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1188,24 +1188,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1258,24 +1258,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1328,24 +1328,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1363,34 +1363,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bossa Nova</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1398,24 +1398,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Bossa Nova.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Super Dog and Super Cat</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1433,24 +1433,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
+          <t>home/07-03-2026/Alpha.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
+          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Pritam and Pedro Season 1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1468,24 +1468,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Charukesi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1503,24 +1503,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-03-2026/Charukesi.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Elra Kaaleliyatte Kaala</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1538,24 +1538,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Hunting Jessica Brok</t>
+          <t>Daadi Ki Shaadi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1573,24 +1573,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
+          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
+          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Obsession</t>
+          <t>Hangman</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1608,34 +1608,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Obsession.jpg</t>
+          <t>home/07-03-2026/Hangman.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
+          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Continental Split</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1643,34 +1643,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Continental Split.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Great White Waters</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1678,34 +1678,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Great White Waters.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Road Wars: Max Fury</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1713,24 +1713,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Supergirl</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1748,34 +1748,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Supergirl.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>The Last Breath</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Last Breath.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Little Brother</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1818,24 +1818,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Little Brother.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1853,24 +1853,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>The Yeti</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1888,24 +1888,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Yeti.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1923,34 +1923,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Bossa Nova</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1958,24 +1958,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-02-2026/Bossa Nova.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lingam Season 1</t>
+          <t>Super Dog and Super Cat</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1993,24 +1993,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Lingam Season 1.jpg</t>
+          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
+          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Moondram Kan</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2028,24 +2028,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Moondram Kan.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Raja Shivaji</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2063,24 +2063,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Raja Shivaji.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Elra Kaaleliyatte Kaala</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2098,24 +2098,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Hunting Jessica Brok</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2133,24 +2133,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>In the Hand of Dante</t>
+          <t>Obsession</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2168,34 +2168,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
+          <t>home/07-01-2026/Obsession.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
+          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Maa Inti Bangaaram</t>
+          <t>Continental Split</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2203,34 +2203,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
+          <t>home/07-01-2026/Continental Split.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
+          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Deewana</t>
+          <t>Great White Waters</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2238,34 +2238,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Deewana.jpg</t>
+          <t>home/07-01-2026/Great White Waters.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
+          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Vanda Devullu</t>
+          <t>Road Wars: Max Fury</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2273,24 +2273,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Vanda Devullu.jpg</t>
+          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
+          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Supergirl</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2308,34 +2308,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/07-01-2026/Supergirl.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>M4M: Motive for Murder</t>
+          <t>The Last Breath</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2343,24 +2343,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
+          <t>home/07-01-2026/The Last Breath.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
+          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Blast</t>
+          <t>Little Brother</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2378,34 +2378,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blast.jpg</t>
+          <t>home/07-01-2026/Little Brother.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
+          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Avatar: Fire and Ash</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2413,24 +2413,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
+          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
+          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>The Sheep Detectives</t>
+          <t>The Yeti</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2448,34 +2448,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
+          <t>home/07-01-2026/The Yeti.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
+          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Gladiator Underground</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2483,24 +2483,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Gladiator Underground.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2518,24 +2518,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Lingam Season 1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2553,24 +2553,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-25-2026/Lingam Season 1.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Painkili</t>
+          <t>Moondram Kan</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2588,34 +2588,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Painkili.jpg</t>
+          <t>home/06-25-2026/Moondram Kan.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
+          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Seems Like Old Times</t>
+          <t>Raja Shivaji</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2623,34 +2623,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
+          <t>home/06-25-2026/Raja Shivaji.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
+          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>The Furies</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2658,24 +2658,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Furies.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Garbham</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2693,34 +2693,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Garbham.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Blind Waters</t>
+          <t>In the Hand of Dante</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blind Waters.jpg</t>
+          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
+          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Maa Inti Bangaaram</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2763,24 +2763,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Deewana</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2798,24 +2798,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Deewana.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Vanda Devullu</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2833,24 +2833,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/Vanda Devullu.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2868,24 +2868,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Thank You Subbarao</t>
+          <t>M4M: Motive for Murder</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2903,24 +2903,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
+          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
+          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Blast</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2938,34 +2938,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Blast.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
+          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Avatar: Fire and Ash</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2973,24 +2973,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Husbands in Action</t>
+          <t>The Sheep Detectives</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3008,34 +3008,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Husbands in Action.jpg</t>
+          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
+          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cocktail 2</t>
+          <t>Gladiator Underground</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3043,24 +3043,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Cocktail 2.jpg</t>
+          <t>home/06-24-2026/Gladiator Underground.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
+          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3078,24 +3078,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Voicemails for Isabelle</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3113,24 +3113,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Painkili</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3148,34 +3148,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/Painkili.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Save The Tigers Season 3</t>
+          <t>Seems Like Old Times</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3183,34 +3183,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
+          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
+          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>The Furies</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3218,34 +3218,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/The Furies.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>The Grey Men 2</t>
+          <t>Garbham</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3253,34 +3253,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>home/06-19-2026/The Grey Men 2.jpg</t>
+          <t>home/06-24-2026/Garbham.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
+          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Blind Waters</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3288,24 +3288,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Blind Waters.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3375,7 +3375,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Mortal Kombat 2</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3410,7 +3410,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3428,24 +3428,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Thank You Subbarao</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3463,24 +3463,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Veerabhadrudu</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3498,24 +3498,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
+          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3533,24 +3533,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sattendru Maarudhu Vaanilai</t>
+          <t>Husbands in Action</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3568,24 +3568,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+          <t>home/06-19-2026/Husbands in Action.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
+          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Cocktail 2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3603,34 +3603,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Cocktail 2.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Pongala</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3638,24 +3638,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Pongala.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Voicemails for Isabelle</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3673,24 +3673,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Shelter.jpg</t>
+          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
+          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Whistle</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3708,24 +3708,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Whistle.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Save The Tigers Season 3</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3743,24 +3743,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3778,29 +3778,29 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>The Deep</t>
+          <t>The Grey Men 2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3813,34 +3813,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>home/06-16-2026/The Deep.jpg</t>
+          <t>home/06-19-2026/The Grey Men 2.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
+          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Seven Years in Tibet</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3848,24 +3848,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Kolahalamedu</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3883,24 +3883,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kolahalamedu.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3918,24 +3918,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Normal.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Mortal Kombat 2</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3953,24 +3953,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Vikalpa</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Vikalpa.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4005,7 +4005,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4040,7 +4040,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Karuppu</t>
+          <t>Veerabhadrudu</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Karuppu.jpg</t>
+          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
+          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4075,7 +4075,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sshhh Season 3</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>R.L. Stine’s Pumpkinhead</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
+          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
+          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4145,7 +4145,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4163,34 +4163,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peddi.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Pongala</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4198,24 +4198,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-16-2026/Pongala.jpg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4233,24 +4233,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-16-2026/Shelter.jpg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4268,24 +4268,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Whistle.jpg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4303,24 +4303,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4338,34 +4338,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>The Deep</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4373,34 +4373,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-16-2026/The Deep.jpg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
+          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>Seven Years in Tibet</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4408,24 +4408,24 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Trikala Script of God.jpg</t>
+          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
+          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Kolahalamedu</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4443,24 +4443,24 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Kolahalamedu.jpg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4478,24 +4478,24 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-16-2026/Normal.jpg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4513,24 +4513,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Vikalpa</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4548,24 +4548,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Blast Zone.jpg</t>
+          <t>home/06-16-2026/Vikalpa.jpg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4583,24 +4583,24 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Maa Behen.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Karuppu</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4618,24 +4618,24 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kattalan.jpg</t>
+          <t>home/06-16-2026/Karuppu.jpg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Sshhh Season 3</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4653,29 +4653,29 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>R.L. Stine’s Pumpkinhead</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -4688,24 +4688,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Beast of War.jpg</t>
+          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4723,12 +4723,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sandigdham.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4740,7 +4740,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kara.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4775,7 +4775,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4793,12 +4793,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4810,7 +4810,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Purushaha.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4845,7 +4845,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Hai Jawani Toh Ishq Hona Hai</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4880,7 +4880,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Summer House</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Summer House.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4915,7 +4915,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4933,12 +4933,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4950,7 +4950,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Juniors Journey</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Juniors Journey.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4985,7 +4985,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ginny Weds Sunny 2</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5020,7 +5020,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peter.jpg</t>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5055,7 +5055,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5090,7 +5090,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5125,7 +5125,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5160,7 +5160,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Kattalan</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Kattalan.jpg</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5195,7 +5195,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Ramani Kalyanam</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5230,33 +5230,593 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>Beast of War</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Beast of War.jpg</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Sandigdham</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Kara</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Kara.jpg</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>KD: The Devil</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Purushaha</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Purushaha.jpg</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Summer House</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Summer House.jpg</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Juniors Journey</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Ginny Weds Sunny 2</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Ugly Story</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
           <t>Office Romance</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
         <is>
           <t>Telugu Dubbed</t>
         </is>
       </c>
-      <c r="D138" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" t="inlineStr">
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="inlineStr">
         <is>
           <t>home/06-06-2026/Office Romance.jpg</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F154" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="G154" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
@@ -5273,7 +5833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5295,100 +5855,110 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B12" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Lenin</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-13-2026/Lenin.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Ikka</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,24 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/Ikka.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Mukhbir: The Story of a Spy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Tholaivil Oru Kadhal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -593,34 +593,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-13-2026/Tholaivil Oru Kadhal.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=bR1s6WIsyfE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>The Trip</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -628,34 +628,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/The Trip.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=K9bPJmy68Rs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Hollow Man 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -663,24 +663,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-13-2026/Hollow Man 2.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=koZuEDeQf3Q</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Lenin</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -698,34 +698,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-13-2026/Lenin.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pati Patni Aur Woh Do</t>
+          <t>Only the Brave</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -733,24 +733,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Pati Patni Aur Woh Do.jpg</t>
+          <t>home/07-13-2026/Only the Brave.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ceooxuS-sww</t>
+          <t>https://www.youtube.com/watch?v=EE_GY6zccqc</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Dhamaal 4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,24 +768,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-13-2026/Dhamaal 4.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=IG-eByZdz6Y</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Ikka</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -803,24 +803,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-13-2026/Ikka.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Mukhbir: The Story of a Spy</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,24 +838,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Shikhandi</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,24 +873,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-13-2026/Shikhandi.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=vLuLhH7oREY</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -960,7 +960,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -995,7 +995,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1030,7 +1030,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nagabandham</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1048,24 +1048,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Nagabandham.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Chand Mera Dil</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1083,24 +1083,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Chand Mera Dil.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rRQ8oKCoYrQ</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Kotha Malupu</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1118,24 +1118,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Kotha Malupu.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qnd1Xwv9NP8</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Double Barrel</t>
+          <t>Pati Patni Aur Woh Do</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Double Barrel.jpg</t>
+          <t>home/07-09-2026/Pati Patni Aur Woh Do.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Ij0mjRt1QIA</t>
+          <t>https://www.youtube.com/watch?v=ceooxuS-sww</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nagabandham</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1188,24 +1188,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Nagabandham.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1258,24 +1258,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1328,24 +1328,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1363,24 +1363,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1398,24 +1398,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1433,24 +1433,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Alpha.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Pritam and Pedro Season 1</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1468,24 +1468,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Charukesi</t>
+          <t>Chand Mera Dil</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1503,24 +1503,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Charukesi.jpg</t>
+          <t>home/07-06-2026/Chand Mera Dil.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
+          <t>https://www.youtube.com/watch?v=rRQ8oKCoYrQ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Kotha Malupu</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1538,24 +1538,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-06-2026/Kotha Malupu.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=qnd1Xwv9NP8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Daadi Ki Shaadi</t>
+          <t>Double Barrel</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1573,24 +1573,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
+          <t>home/07-06-2026/Double Barrel.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
+          <t>https://www.youtube.com/watch?v=Ij0mjRt1QIA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Hangman</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1608,24 +1608,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Hangman.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1678,17 +1678,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1765,7 +1765,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1800,7 +1800,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1818,24 +1818,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1853,24 +1853,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-03-2026/Alpha.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Pritam and Pedro Season 1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1888,24 +1888,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Charukesi</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1923,34 +1923,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-03-2026/Charukesi.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Bossa Nova</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1958,24 +1958,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Bossa Nova.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Super Dog and Super Cat</t>
+          <t>Daadi Ki Shaadi</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1993,24 +1993,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
+          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
+          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Hangman</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2028,24 +2028,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-03-2026/Hangman.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2063,24 +2063,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Elra Kaaleliyatte Kaala</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2098,24 +2098,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Hunting Jessica Brok</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2133,24 +2133,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Obsession</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2168,34 +2168,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Obsession.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Continental Split</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2203,34 +2203,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Continental Split.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Great White Waters</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2238,34 +2238,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Great White Waters.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Road Wars: Max Fury</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2273,24 +2273,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Supergirl</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2308,34 +2308,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Supergirl.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>The Last Breath</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2343,29 +2343,29 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Last Breath.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Little Brother</t>
+          <t>Bossa Nova</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2378,24 +2378,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Little Brother.jpg</t>
+          <t>home/07-02-2026/Bossa Nova.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
+          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Super Dog and Super Cat</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2413,24 +2413,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
+          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
+          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>The Yeti</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Yeti.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2465,7 +2465,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2483,24 +2483,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Elra Kaaleliyatte Kaala</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2518,24 +2518,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Lingam Season 1</t>
+          <t>Hunting Jessica Brok</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2553,24 +2553,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Lingam Season 1.jpg</t>
+          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
+          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Moondram Kan</t>
+          <t>Obsession</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2588,34 +2588,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Moondram Kan.jpg</t>
+          <t>home/07-01-2026/Obsession.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
+          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Raja Shivaji</t>
+          <t>Continental Split</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2623,34 +2623,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Raja Shivaji.jpg</t>
+          <t>home/07-01-2026/Continental Split.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
+          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Great White Waters</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2658,34 +2658,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-01-2026/Great White Waters.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Road Wars: Max Fury</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2693,24 +2693,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>In the Hand of Dante</t>
+          <t>Supergirl</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2728,34 +2728,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
+          <t>home/07-01-2026/Supergirl.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
+          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Maa Inti Bangaaram</t>
+          <t>The Last Breath</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2763,24 +2763,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
+          <t>home/07-01-2026/The Last Breath.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
+          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Deewana</t>
+          <t>Little Brother</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2798,24 +2798,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Deewana.jpg</t>
+          <t>home/07-01-2026/Little Brother.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
+          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Vanda Devullu</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2833,24 +2833,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Vanda Devullu.jpg</t>
+          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
+          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>The Yeti</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2868,24 +2868,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/07-01-2026/The Yeti.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>M4M: Motive for Murder</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2903,24 +2903,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Blast</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2938,34 +2938,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blast.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Avatar: Fire and Ash</t>
+          <t>Lingam Season 1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2973,24 +2973,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
+          <t>home/06-25-2026/Lingam Season 1.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
+          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>The Sheep Detectives</t>
+          <t>Moondram Kan</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3008,34 +3008,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
+          <t>home/06-25-2026/Moondram Kan.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
+          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Gladiator Underground</t>
+          <t>Raja Shivaji</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3043,24 +3043,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Gladiator Underground.jpg</t>
+          <t>home/06-25-2026/Raja Shivaji.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
+          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3078,24 +3078,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3113,24 +3113,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Painkili</t>
+          <t>In the Hand of Dante</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3148,34 +3148,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Painkili.jpg</t>
+          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
+          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Seems Like Old Times</t>
+          <t>Maa Inti Bangaaram</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
+          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
+          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3200,17 +3200,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>The Furies</t>
+          <t>Deewana</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Furies.jpg</t>
+          <t>home/06-24-2026/Deewana.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
+          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3235,7 +3235,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Garbham</t>
+          <t>Vanda Devullu</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Garbham.jpg</t>
+          <t>home/06-24-2026/Vanda Devullu.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
+          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3270,17 +3270,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Blind Waters</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blind Waters.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3305,7 +3305,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>M4M: Motive for Murder</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3323,24 +3323,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Blast</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3358,34 +3358,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Blast.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Avatar: Fire and Ash</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3393,24 +3393,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>The Sheep Detectives</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3428,34 +3428,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Thank You Subbarao</t>
+          <t>Gladiator Underground</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3463,24 +3463,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
+          <t>home/06-24-2026/Gladiator Underground.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
+          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3498,24 +3498,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3533,24 +3533,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Husbands in Action</t>
+          <t>Painkili</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3568,34 +3568,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Husbands in Action.jpg</t>
+          <t>home/06-24-2026/Painkili.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
+          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cocktail 2</t>
+          <t>Seems Like Old Times</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3603,34 +3603,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Cocktail 2.jpg</t>
+          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
+          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>The Furies</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3638,24 +3638,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/The Furies.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Voicemails for Isabelle</t>
+          <t>Garbham</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3673,34 +3673,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
+          <t>home/06-24-2026/Garbham.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
+          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Blind Waters</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3708,24 +3708,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/Blind Waters.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Save The Tigers Season 3</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3760,7 +3760,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3795,17 +3795,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>The Grey Men 2</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>home/06-19-2026/The Grey Men 2.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3865,7 +3865,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Thank You Subbarao</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3900,7 +3900,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -3935,7 +3935,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Mortal Kombat 2</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -3970,7 +3970,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Husbands in Action</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3988,24 +3988,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Husbands in Action.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Cocktail 2</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4023,24 +4023,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Cocktail 2.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Veerabhadrudu</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4058,24 +4058,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Voicemails for Isabelle</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4093,24 +4093,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sattendru Maarudhu Vaanilai</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4128,24 +4128,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Save The Tigers Season 3</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4163,34 +4163,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Pongala</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4198,29 +4198,29 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Pongala.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>The Grey Men 2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4233,24 +4233,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Shelter.jpg</t>
+          <t>home/06-19-2026/The Grey Men 2.jpg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
+          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Whistle</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4268,24 +4268,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Whistle.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4303,24 +4303,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4338,29 +4338,29 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>The Deep</t>
+          <t>Mortal Kombat 2</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -4373,34 +4373,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>home/06-16-2026/The Deep.jpg</t>
+          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
+          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Seven Years in Tibet</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -4425,7 +4425,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Kolahalamedu</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kolahalamedu.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -4460,7 +4460,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Veerabhadrudu</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4478,12 +4478,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Normal.jpg</t>
+          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
+          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -4495,7 +4495,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -4530,7 +4530,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Vikalpa</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Vikalpa.jpg</t>
+          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
+          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4600,17 +4600,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Karuppu</t>
+          <t>Pongala</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Karuppu.jpg</t>
+          <t>home/06-16-2026/Pongala.jpg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
+          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4635,7 +4635,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sshhh Season 3</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
+          <t>home/06-16-2026/Shelter.jpg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
+          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4670,7 +4670,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>R.L. Stine’s Pumpkinhead</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
+          <t>home/06-16-2026/Whistle.jpg</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
+          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4705,7 +4705,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4723,24 +4723,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peddi.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4758,34 +4758,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>The Deep</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4793,34 +4793,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-16-2026/The Deep.jpg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Seven Years in Tibet</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4828,24 +4828,24 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Kolahalamedu</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4863,24 +4863,24 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Kolahalamedu.jpg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4898,24 +4898,24 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-16-2026/Normal.jpg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4933,24 +4933,24 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>Vikalpa</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4968,24 +4968,24 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Trikala Script of God.jpg</t>
+          <t>home/06-16-2026/Vikalpa.jpg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
+          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5003,24 +5003,24 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>Karuppu</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5038,24 +5038,24 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-16-2026/Karuppu.jpg</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Sshhh Season 3</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5073,24 +5073,24 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>R.L. Stine’s Pumpkinhead</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5108,24 +5108,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Blast Zone.jpg</t>
+          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Maa Behen.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5160,7 +5160,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kattalan.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5195,7 +5195,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5230,17 +5230,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Beast of War.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5265,7 +5265,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sandigdham.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5300,7 +5300,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kara.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5335,7 +5335,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -5370,7 +5370,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5388,12 +5388,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Purushaha.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -5405,7 +5405,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Hai Jawani Toh Ishq Hona Hai</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -5440,7 +5440,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Summer House</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Summer House.jpg</t>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5475,7 +5475,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5510,7 +5510,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Juniors Journey</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Juniors Journey.jpg</t>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5545,7 +5545,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ginny Weds Sunny 2</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5580,7 +5580,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Kattalan</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peter.jpg</t>
+          <t>home/06-06-2026/Kattalan.jpg</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Ramani Kalyanam</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5650,17 +5650,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Beast of War</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/Beast of War.jpg</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5685,7 +5685,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Sandigdham</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5720,7 +5720,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Kara.jpg</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5755,7 +5755,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5790,33 +5790,453 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>Purushaha</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Purushaha.jpg</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Summer House</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Summer House.jpg</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Juniors Journey</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Ginny Weds Sunny 2</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Ugly Story</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
           <t>Office Romance</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
         <is>
           <t>Telugu Dubbed</t>
         </is>
       </c>
-      <c r="D154" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" t="inlineStr">
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="inlineStr">
         <is>
           <t>home/06-06-2026/Office Romance.jpg</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="F166" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="G166" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
@@ -5833,7 +6253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5855,110 +6275,120 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B13" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G166"/>
+  <dimension ref="A1:G183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lenin</t>
+          <t>Vadala</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Lenin.jpg</t>
+          <t>home/07-20-2026/Vadala.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
+          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ikka</t>
+          <t>Mister Middle Class</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,24 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Ikka.jpg</t>
+          <t>home/07-20-2026/Mister Middle Class.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
+          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mukhbir: The Story of a Spy</t>
+          <t>Transfer Trimurthulu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
+          <t>home/07-20-2026/Transfer Trimurthulu.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
+          <t>https://www.youtube.com/watch?v=cnqP9cCU5Ak</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tholaivil Oru Kadhal</t>
+          <t>Hrudhayam Murali</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -593,34 +593,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Tholaivil Oru Kadhal.jpg</t>
+          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bR1s6WIsyfE</t>
+          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>The Trip</t>
+          <t>Gedelaraju Kakinada Taluka</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -628,34 +628,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/07-13-2026/The Trip.jpg</t>
+          <t>home/07-20-2026/Gedelaraju Kakinada Taluka.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=K9bPJmy68Rs</t>
+          <t>https://www.youtube.com/watch?v=SBX2RFgxzYg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hollow Man 2</t>
+          <t>Ek Din</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -663,24 +663,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Hollow Man 2.jpg</t>
+          <t>home/07-20-2026/Ek Din.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=koZuEDeQf3Q</t>
+          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lenin</t>
+          <t>The Odyssey</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -698,34 +698,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Lenin.jpg</t>
+          <t>home/07-20-2026/The Odyssey.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
+          <t>https://www.youtube.com/watch?v=f_bKjZeJBBI</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Only the Brave</t>
+          <t>Vadala</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -733,34 +733,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Only the Brave.jpg</t>
+          <t>home/07-20-2026/Vadala.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EE_GY6zccqc</t>
+          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dhamaal 4</t>
+          <t>Hijack 1971</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,24 +768,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Dhamaal 4.jpg</t>
+          <t>home/07-20-2026/Hijack 1971.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IG-eByZdz6Y</t>
+          <t>https://www.youtube.com/watch?v=UxyutkXQnvA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ikka</t>
+          <t>Mister Middle Class</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -803,24 +803,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Ikka.jpg</t>
+          <t>home/07-20-2026/Mister Middle Class.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
+          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mukhbir: The Story of a Spy</t>
+          <t>Ek Din</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,24 +838,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
+          <t>home/07-20-2026/Ek Din.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
+          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Shikhandi</t>
+          <t>Ek Din</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,24 +873,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Shikhandi.jpg</t>
+          <t>home/07-20-2026/Ek Din.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vLuLhH7oREY</t>
+          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Thiraivi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -908,24 +908,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-20-2026/Thiraivi.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=YMLv6vV43Vo</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Hrudhayam Murali</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -943,34 +943,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>13 Days, 13 Nights</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -978,24 +978,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-20-2026/13 Days, 13 Nights.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=mAKOqFt-LVQ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>23 000 Lives</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,29 +1013,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-20-2026/23 000 Lives.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=89dugTvBEWw</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Chithini</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1048,24 +1048,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-20-2026/Chithini.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=pRbfgUVGAJg</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Lenin</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1083,24 +1083,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-13-2026/Lenin.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Ikka</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1118,24 +1118,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-13-2026/Ikka.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Pati Patni Aur Woh Do</t>
+          <t>Mukhbir: The Story of a Spy</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Pati Patni Aur Woh Do.jpg</t>
+          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ceooxuS-sww</t>
+          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Tholaivil Oru Kadhal</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1188,34 +1188,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-13-2026/Tholaivil Oru Kadhal.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=bR1s6WIsyfE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>The Trip</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1223,34 +1223,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-13-2026/The Trip.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=K9bPJmy68Rs</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Hollow Man 2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1258,24 +1258,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-13-2026/Hollow Man 2.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=koZuEDeQf3Q</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Lenin</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1293,34 +1293,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-13-2026/Lenin.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Only the Brave</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1328,24 +1328,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-13-2026/Only the Brave.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=EE_GY6zccqc</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Dhamaal 4</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1363,24 +1363,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/Dhamaal 4.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=IG-eByZdz6Y</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Ikka</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1398,24 +1398,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/Ikka.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Mukhbir: The Story of a Spy</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1433,24 +1433,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nagabandham</t>
+          <t>Shikhandi</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1468,24 +1468,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Nagabandham.jpg</t>
+          <t>home/07-13-2026/Shikhandi.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
+          <t>https://www.youtube.com/watch?v=vLuLhH7oREY</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Chand Mera Dil</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1503,24 +1503,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Chand Mera Dil.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rRQ8oKCoYrQ</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Kotha Malupu</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1538,24 +1538,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Kotha Malupu.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qnd1Xwv9NP8</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Double Barrel</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1573,24 +1573,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Double Barrel.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Ij0mjRt1QIA</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nagabandham</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1608,24 +1608,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Nagabandham.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1678,24 +1678,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1713,24 +1713,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Pati Patni Aur Woh Do</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1748,24 +1748,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Pati Patni Aur Woh Do.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=ceooxuS-sww</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1818,24 +1818,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1853,24 +1853,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Alpha.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Pritam and Pedro Season 1</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1888,24 +1888,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Charukesi</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1923,24 +1923,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Charukesi.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1958,24 +1958,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Daadi Ki Shaadi</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1993,24 +1993,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Hangman</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2028,24 +2028,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Hangman.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2063,24 +2063,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Chand Mera Dil</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2098,24 +2098,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-06-2026/Chand Mera Dil.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=rRQ8oKCoYrQ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Kotha Malupu</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2133,24 +2133,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-06-2026/Kotha Malupu.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=qnd1Xwv9NP8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Double Barrel</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2168,24 +2168,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-06-2026/Double Barrel.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=Ij0mjRt1QIA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2203,24 +2203,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2273,24 +2273,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2308,24 +2308,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2343,34 +2343,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Bossa Nova</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2378,24 +2378,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Bossa Nova.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Super Dog and Super Cat</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2413,24 +2413,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2448,24 +2448,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-03-2026/Alpha.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Pritam and Pedro Season 1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2483,24 +2483,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Elra Kaaleliyatte Kaala</t>
+          <t>Charukesi</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2518,24 +2518,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
+          <t>home/07-03-2026/Charukesi.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
+          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Hunting Jessica Brok</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2553,24 +2553,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Obsession</t>
+          <t>Daadi Ki Shaadi</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2588,34 +2588,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Obsession.jpg</t>
+          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
+          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Continental Split</t>
+          <t>Hangman</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2623,34 +2623,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Continental Split.jpg</t>
+          <t>home/07-03-2026/Hangman.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
+          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Great White Waters</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2658,34 +2658,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Great White Waters.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Road Wars: Max Fury</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2693,24 +2693,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Supergirl</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2728,34 +2728,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Supergirl.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>The Last Breath</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2763,24 +2763,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Last Breath.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Little Brother</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2798,24 +2798,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Little Brother.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2833,24 +2833,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>The Yeti</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2868,24 +2868,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Yeti.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2903,24 +2903,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2938,34 +2938,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Lingam Season 1</t>
+          <t>Bossa Nova</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2973,24 +2973,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Lingam Season 1.jpg</t>
+          <t>home/07-02-2026/Bossa Nova.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
+          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Moondram Kan</t>
+          <t>Super Dog and Super Cat</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3008,24 +3008,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Moondram Kan.jpg</t>
+          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
+          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Raja Shivaji</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3043,24 +3043,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Raja Shivaji.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3078,24 +3078,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Elra Kaaleliyatte Kaala</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3113,24 +3113,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>In the Hand of Dante</t>
+          <t>Hunting Jessica Brok</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3148,24 +3148,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
+          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
+          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Maa Inti Bangaaram</t>
+          <t>Obsession</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3183,34 +3183,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
+          <t>home/07-01-2026/Obsession.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
+          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Deewana</t>
+          <t>Continental Split</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3218,34 +3218,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Deewana.jpg</t>
+          <t>home/07-01-2026/Continental Split.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
+          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Vanda Devullu</t>
+          <t>Great White Waters</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3253,34 +3253,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Vanda Devullu.jpg</t>
+          <t>home/07-01-2026/Great White Waters.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
+          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Road Wars: Max Fury</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3288,24 +3288,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>M4M: Motive for Murder</t>
+          <t>Supergirl</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3323,34 +3323,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
+          <t>home/07-01-2026/Supergirl.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
+          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Blast</t>
+          <t>The Last Breath</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3358,29 +3358,29 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blast.jpg</t>
+          <t>home/07-01-2026/The Last Breath.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
+          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Avatar: Fire and Ash</t>
+          <t>Little Brother</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3393,24 +3393,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
+          <t>home/07-01-2026/Little Brother.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
+          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>The Sheep Detectives</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3428,29 +3428,29 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
+          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
+          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Gladiator Underground</t>
+          <t>The Yeti</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3463,24 +3463,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Gladiator Underground.jpg</t>
+          <t>home/07-01-2026/The Yeti.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
+          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3498,24 +3498,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3533,24 +3533,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Painkili</t>
+          <t>Lingam Season 1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3568,34 +3568,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Painkili.jpg</t>
+          <t>home/06-25-2026/Lingam Season 1.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
+          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Seems Like Old Times</t>
+          <t>Moondram Kan</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3603,34 +3603,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
+          <t>home/06-25-2026/Moondram Kan.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
+          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>The Furies</t>
+          <t>Raja Shivaji</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3638,24 +3638,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Furies.jpg</t>
+          <t>home/06-25-2026/Raja Shivaji.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
+          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Garbham</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3673,34 +3673,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Garbham.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Blind Waters</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3708,24 +3708,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blind Waters.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>In the Hand of Dante</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3743,24 +3743,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Maa Inti Bangaaram</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3778,24 +3778,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Deewana</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3813,24 +3813,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/Deewana.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Vanda Devullu</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3848,24 +3848,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Vanda Devullu.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Thank You Subbarao</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3883,24 +3883,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>M4M: Motive for Murder</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3918,24 +3918,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
+          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Blast</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3953,29 +3953,29 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Blast.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Husbands in Action</t>
+          <t>Avatar: Fire and Ash</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3988,24 +3988,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Husbands in Action.jpg</t>
+          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
+          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cocktail 2</t>
+          <t>The Sheep Detectives</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4023,34 +4023,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Cocktail 2.jpg</t>
+          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
+          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Gladiator Underground</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4058,24 +4058,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/Gladiator Underground.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Voicemails for Isabelle</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4093,24 +4093,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4128,24 +4128,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Save The Tigers Season 3</t>
+          <t>Painkili</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4163,34 +4163,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
+          <t>home/06-24-2026/Painkili.jpg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
+          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Seems Like Old Times</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4198,34 +4198,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>The Grey Men 2</t>
+          <t>The Furies</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4233,24 +4233,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>home/06-19-2026/The Grey Men 2.jpg</t>
+          <t>home/06-24-2026/The Furies.jpg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
+          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Garbham</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4268,34 +4268,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Garbham.jpg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Blind Waters</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4303,24 +4303,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Blind Waters.jpg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -4355,7 +4355,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Mortal Kombat 2</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -4390,7 +4390,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4408,24 +4408,24 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4443,24 +4443,24 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Veerabhadrudu</t>
+          <t>Thank You Subbarao</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4478,24 +4478,24 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
+          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
+          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4513,24 +4513,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sattendru Maarudhu Vaanilai</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4548,24 +4548,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Husbands in Action</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4583,34 +4583,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Husbands in Action.jpg</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Pongala</t>
+          <t>Cocktail 2</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4618,24 +4618,24 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Pongala.jpg</t>
+          <t>home/06-19-2026/Cocktail 2.jpg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
+          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4653,24 +4653,24 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Shelter.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Whistle</t>
+          <t>Voicemails for Isabelle</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4688,24 +4688,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Whistle.jpg</t>
+          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
+          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4723,24 +4723,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Save The Tigers Season 3</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4758,34 +4758,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>The Deep</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4793,29 +4793,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>home/06-16-2026/The Deep.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Seven Years in Tibet</t>
+          <t>The Grey Men 2</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4828,24 +4828,24 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
+          <t>home/06-19-2026/The Grey Men 2.jpg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
+          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Kolahalamedu</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4863,24 +4863,24 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kolahalamedu.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4898,24 +4898,24 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Normal.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4933,24 +4933,24 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Vikalpa</t>
+          <t>Mortal Kombat 2</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4968,24 +4968,24 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Vikalpa.jpg</t>
+          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
+          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -5020,7 +5020,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Karuppu</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Karuppu.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5055,7 +5055,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sshhh Season 3</t>
+          <t>Veerabhadrudu</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
+          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
+          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5090,7 +5090,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>R.L. Stine’s Pumpkinhead</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5125,7 +5125,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5143,24 +5143,24 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peddi.jpg</t>
+          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
+          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5178,34 +5178,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Pongala</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5213,24 +5213,24 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-16-2026/Pongala.jpg</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5248,24 +5248,24 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Shelter.jpg</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5283,24 +5283,24 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Whistle.jpg</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5318,24 +5318,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5353,34 +5353,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>The Deep</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5388,34 +5388,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Trikala Script of God.jpg</t>
+          <t>home/06-16-2026/The Deep.jpg</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
+          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Seven Years in Tibet</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5423,24 +5423,24 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>Kolahalamedu</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5458,24 +5458,24 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-16-2026/Kolahalamedu.jpg</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5493,24 +5493,24 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-16-2026/Normal.jpg</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5528,24 +5528,24 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Blast Zone.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Vikalpa</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5563,24 +5563,24 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Maa Behen.jpg</t>
+          <t>home/06-16-2026/Vikalpa.jpg</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5598,24 +5598,24 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kattalan.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Karuppu</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5633,34 +5633,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-16-2026/Karuppu.jpg</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>Sshhh Season 3</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5668,24 +5668,24 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Beast of War.jpg</t>
+          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>R.L. Stine’s Pumpkinhead</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5703,24 +5703,24 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sandigdham.jpg</t>
+          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kara.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5755,7 +5755,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5790,7 +5790,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Purushaha.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -5825,7 +5825,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Hai Jawani Toh Ishq Hona Hai</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5860,7 +5860,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Summer House</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Summer House.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -5895,7 +5895,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5930,7 +5930,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Juniors Journey</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Juniors Journey.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -5965,7 +5965,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ginny Weds Sunny 2</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -6000,7 +6000,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peter.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -6035,7 +6035,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -6070,7 +6070,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -6105,7 +6105,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6140,7 +6140,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6175,7 +6175,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Kattalan</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Kattalan.jpg</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -6210,33 +6210,628 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
+          <t>Ramani Kalyanam</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Beast of War</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Beast of War.jpg</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Sandigdham</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Kara</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Kara.jpg</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>KD: The Devil</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Purushaha</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Purushaha.jpg</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Summer House</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Summer House.jpg</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>1</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Juniors Journey</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Ginny Weds Sunny 2</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Ugly Story</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
           <t>Office Romance</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
         <is>
           <t>Telugu Dubbed</t>
         </is>
       </c>
-      <c r="D166" t="n">
-        <v>1</v>
-      </c>
-      <c r="E166" t="inlineStr">
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="inlineStr">
         <is>
           <t>home/06-06-2026/Office Romance.jpg</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="F183" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
+      <c r="G183" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
@@ -6253,7 +6848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6275,120 +6870,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B14" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G183"/>
+  <dimension ref="A1:G205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Vadala</t>
+          <t>Chennai Love Story</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Vadala.jpg</t>
+          <t>home/08-01-2026/Chennai Love Story.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
+          <t>https://www.youtube.com/watch?v=nYYjR9diizE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mister Middle Class</t>
+          <t>Srinivasa Mangapuram</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,24 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Mister Middle Class.jpg</t>
+          <t>home/08-01-2026/Srinivasa Mangapuram.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
+          <t>https://www.youtube.com/watch?v=kKIqF2oyj1Q</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Transfer Trimurthulu</t>
+          <t>Jana Nayakudu</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Transfer Trimurthulu.jpg</t>
+          <t>home/08-01-2026/Jana Nayakudu.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cnqP9cCU5Ak</t>
+          <t>https://www.youtube.com/watch?v=L81nWRwRmnI</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hrudhayam Murali</t>
+          <t>Gatta Kusthi 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -593,24 +593,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
+          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
+          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gedelaraju Kakinada Taluka</t>
+          <t>Police Complaint</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -628,24 +628,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Gedelaraju Kakinada Taluka.jpg</t>
+          <t>home/08-01-2026/Police Complaint.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SBX2RFgxzYg</t>
+          <t>https://www.youtube.com/watch?v=87aOxmtPmX0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ek Din</t>
+          <t>Love Oh Love</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -663,24 +663,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Ek Din.jpg</t>
+          <t>home/08-01-2026/Love Oh Love.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
+          <t>https://www.youtube.com/watch?v=ikZoI6wmvBQ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>The Odyssey</t>
+          <t>Balan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -698,24 +698,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/07-20-2026/The Odyssey.jpg</t>
+          <t>home/08-01-2026/Balan.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f_bKjZeJBBI</t>
+          <t>https://www.youtube.com/watch?v=cjWTqndgZ_M</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Vadala</t>
+          <t>Objection My Lord Season 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -733,34 +733,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Vadala.jpg</t>
+          <t>home/08-01-2026/Objection My Lord Season 1.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
+          <t>https://www.youtube.com/watch?v=Fhr9JdlLRwY</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hijack 1971</t>
+          <t>Con City</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,24 +768,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Hijack 1971.jpg</t>
+          <t>home/08-01-2026/Con City.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UxyutkXQnvA</t>
+          <t>https://www.youtube.com/watch?v=wT2VV6bq6hU</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mister Middle Class</t>
+          <t>Pallichattambi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -803,24 +803,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Mister Middle Class.jpg</t>
+          <t>home/08-01-2026/Pallichattambi.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
+          <t>https://www.youtube.com/watch?v=k6WQlVFkvgg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ek Din</t>
+          <t>Chinna Chinna Aasai</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,24 +838,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Ek Din.jpg</t>
+          <t>home/08-01-2026/Chinna Chinna Aasai.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
+          <t>https://www.youtube.com/watch?v=f_mCvoMgoYs</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ek Din</t>
+          <t>Balan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,24 +873,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Ek Din.jpg</t>
+          <t>home/08-01-2026/Balan.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
+          <t>https://www.youtube.com/watch?v=cjWTqndgZ_M</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Thiraivi</t>
+          <t>Spider-Man: Brand New Day</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -908,24 +908,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Thiraivi.jpg</t>
+          <t>home/08-01-2026/Spider-Man Brand New Day.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YMLv6vV43Vo</t>
+          <t>https://www.youtube.com/watch?v=62bIsvRcPv0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Hrudhayam Murali</t>
+          <t>Objection My Lord Season 1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -943,34 +943,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
+          <t>home/08-01-2026/Objection My Lord Season 1.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
+          <t>https://www.youtube.com/watch?v=Fhr9JdlLRwY</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13 Days, 13 Nights</t>
+          <t>Srinivasa Mangapuram</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -978,24 +978,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/07-20-2026/13 Days, 13 Nights.jpg</t>
+          <t>home/08-01-2026/Srinivasa Mangapuram.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mAKOqFt-LVQ</t>
+          <t>https://www.youtube.com/watch?v=kKIqF2oyj1Q</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>23 000 Lives</t>
+          <t>Son of Sara: Volume 1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1013,34 +1013,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/07-20-2026/23 000 Lives.jpg</t>
+          <t>home/08-01-2026/Son of Sara Volume 1.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=89dugTvBEWw</t>
+          <t>https://www.youtube.com/watch?v=ZTkXpVGpcRk</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Chithini</t>
+          <t>Police Complaint</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1048,24 +1048,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Chithini.jpg</t>
+          <t>home/08-01-2026/Police Complaint.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pRbfgUVGAJg</t>
+          <t>https://www.youtube.com/watch?v=-q63oK7GhI0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lenin</t>
+          <t>Chum</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1083,24 +1083,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Lenin.jpg</t>
+          <t>home/08-01-2026/Chum.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
+          <t>https://www.youtube.com/watch?v=VUdPlZgXOjE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ikka</t>
+          <t>Gatta Kusthi 2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1118,24 +1118,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Ikka.jpg</t>
+          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
+          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mukhbir: The Story of a Spy</t>
+          <t>Gatta Kusthi 2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
+          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
+          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tholaivil Oru Kadhal</t>
+          <t>Love Oh Love</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1188,34 +1188,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Tholaivil Oru Kadhal.jpg</t>
+          <t>home/08-01-2026/Love Oh Love.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bR1s6WIsyfE</t>
+          <t>https://www.youtube.com/watch?v=ikZoI6wmvBQ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>The Trip</t>
+          <t>Kaalam Paranja Kadha</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1223,34 +1223,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/07-13-2026/The Trip.jpg</t>
+          <t>home/08-01-2026/Kaalam Paranja Kadha.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=K9bPJmy68Rs</t>
+          <t>https://www.youtube.com/watch?v=Hox9qawUA-g</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hollow Man 2</t>
+          <t>Vadala</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1258,24 +1258,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Hollow Man 2.jpg</t>
+          <t>home/07-20-2026/Vadala.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=koZuEDeQf3Q</t>
+          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lenin</t>
+          <t>Mister Middle Class</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1293,34 +1293,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Lenin.jpg</t>
+          <t>home/07-20-2026/Mister Middle Class.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
+          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Only the Brave</t>
+          <t>Transfer Trimurthulu</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1328,24 +1328,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Only the Brave.jpg</t>
+          <t>home/07-20-2026/Transfer Trimurthulu.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EE_GY6zccqc</t>
+          <t>https://www.youtube.com/watch?v=cnqP9cCU5Ak</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dhamaal 4</t>
+          <t>Hrudhayam Murali</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1363,24 +1363,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Dhamaal 4.jpg</t>
+          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IG-eByZdz6Y</t>
+          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ikka</t>
+          <t>Gedelaraju Kakinada Taluka</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1398,24 +1398,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Ikka.jpg</t>
+          <t>home/07-20-2026/Gedelaraju Kakinada Taluka.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
+          <t>https://www.youtube.com/watch?v=SBX2RFgxzYg</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mukhbir: The Story of a Spy</t>
+          <t>Ek Din</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1433,24 +1433,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
+          <t>home/07-20-2026/Ek Din.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
+          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Shikhandi</t>
+          <t>The Odyssey</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1468,24 +1468,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Shikhandi.jpg</t>
+          <t>home/07-20-2026/The Odyssey.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vLuLhH7oREY</t>
+          <t>https://www.youtube.com/watch?v=f_bKjZeJBBI</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Vadala</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1503,34 +1503,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-20-2026/Vadala.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Hijack 1971</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1538,24 +1538,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-20-2026/Hijack 1971.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=UxyutkXQnvA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Mister Middle Class</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1573,24 +1573,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-20-2026/Mister Middle Class.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Ek Din</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1608,24 +1608,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-20-2026/Ek Din.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Ek Din</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-20-2026/Ek Din.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Thiraivi</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1678,24 +1678,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-20-2026/Thiraivi.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=YMLv6vV43Vo</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Hrudhayam Murali</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1713,34 +1713,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Pati Patni Aur Woh Do</t>
+          <t>13 Days, 13 Nights</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1748,24 +1748,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Pati Patni Aur Woh Do.jpg</t>
+          <t>home/07-20-2026/13 Days, 13 Nights.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ceooxuS-sww</t>
+          <t>https://www.youtube.com/watch?v=mAKOqFt-LVQ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>23 000 Lives</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1783,34 +1783,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-20-2026/23 000 Lives.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=89dugTvBEWw</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Chithini</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1818,24 +1818,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-20-2026/Chithini.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=pRbfgUVGAJg</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Lenin</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1853,24 +1853,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-13-2026/Lenin.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Ikka</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1888,24 +1888,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-13-2026/Ikka.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Mukhbir: The Story of a Spy</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1923,24 +1923,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Tholaivil Oru Kadhal</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1958,34 +1958,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/Tholaivil Oru Kadhal.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=bR1s6WIsyfE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>The Trip</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1993,34 +1993,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/The Trip.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=K9bPJmy68Rs</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Hollow Man 2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2028,24 +2028,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/Hollow Man 2.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=koZuEDeQf3Q</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Nagabandham</t>
+          <t>Lenin</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2063,34 +2063,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Nagabandham.jpg</t>
+          <t>home/07-13-2026/Lenin.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
+          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Chand Mera Dil</t>
+          <t>Only the Brave</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2098,24 +2098,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Chand Mera Dil.jpg</t>
+          <t>home/07-13-2026/Only the Brave.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rRQ8oKCoYrQ</t>
+          <t>https://www.youtube.com/watch?v=EE_GY6zccqc</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kotha Malupu</t>
+          <t>Dhamaal 4</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2133,24 +2133,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Kotha Malupu.jpg</t>
+          <t>home/07-13-2026/Dhamaal 4.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qnd1Xwv9NP8</t>
+          <t>https://www.youtube.com/watch?v=IG-eByZdz6Y</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Double Barrel</t>
+          <t>Ikka</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2168,24 +2168,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Double Barrel.jpg</t>
+          <t>home/07-13-2026/Ikka.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Ij0mjRt1QIA</t>
+          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Nagabandham</t>
+          <t>Mukhbir: The Story of a Spy</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2203,24 +2203,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Nagabandham.jpg</t>
+          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
+          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Shikhandi</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-13-2026/Shikhandi.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=vLuLhH7oREY</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2273,24 +2273,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2308,24 +2308,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2343,24 +2343,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2378,24 +2378,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2413,24 +2413,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2448,24 +2448,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Alpha.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pritam and Pedro Season 1</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2483,24 +2483,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Charukesi</t>
+          <t>Pati Patni Aur Woh Do</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2518,24 +2518,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Charukesi.jpg</t>
+          <t>home/07-09-2026/Pati Patni Aur Woh Do.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
+          <t>https://www.youtube.com/watch?v=ceooxuS-sww</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2553,24 +2553,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Daadi Ki Shaadi</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Hangman</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2623,24 +2623,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Hangman.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2650,7 +2650,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2658,24 +2658,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2693,24 +2693,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2763,24 +2763,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2798,24 +2798,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2833,24 +2833,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Chand Mera Dil</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2868,24 +2868,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-06-2026/Chand Mera Dil.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=rRQ8oKCoYrQ</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Kotha Malupu</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2903,24 +2903,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-06-2026/Kotha Malupu.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=qnd1Xwv9NP8</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Double Barrel</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2938,34 +2938,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-06-2026/Double Barrel.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=Ij0mjRt1QIA</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Bossa Nova</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2973,24 +2973,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Bossa Nova.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Super Dog and Super Cat</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3008,24 +3008,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3043,24 +3043,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3078,24 +3078,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Elra Kaaleliyatte Kaala</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3113,24 +3113,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Hunting Jessica Brok</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3148,24 +3148,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Obsession</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3183,34 +3183,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Obsession.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Continental Split</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3218,34 +3218,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Continental Split.jpg</t>
+          <t>home/07-03-2026/Alpha.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
+          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Great White Waters</t>
+          <t>Pritam and Pedro Season 1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3253,34 +3253,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Great White Waters.jpg</t>
+          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
+          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Road Wars: Max Fury</t>
+          <t>Charukesi</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3288,24 +3288,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
+          <t>home/07-03-2026/Charukesi.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
+          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Supergirl</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3323,34 +3323,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Supergirl.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>The Last Breath</t>
+          <t>Daadi Ki Shaadi</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3358,24 +3358,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Last Breath.jpg</t>
+          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
+          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Little Brother</t>
+          <t>Hangman</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3393,24 +3393,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Little Brother.jpg</t>
+          <t>home/07-03-2026/Hangman.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
+          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3428,24 +3428,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>The Yeti</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3463,24 +3463,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Yeti.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3498,24 +3498,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3533,24 +3533,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Lingam Season 1</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3568,24 +3568,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Lingam Season 1.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Moondram Kan</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3603,24 +3603,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Moondram Kan.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Raja Shivaji</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3638,24 +3638,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Raja Shivaji.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3673,24 +3673,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3708,29 +3708,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>In the Hand of Dante</t>
+          <t>Bossa Nova</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3743,24 +3743,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
+          <t>home/07-02-2026/Bossa Nova.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
+          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Maa Inti Bangaaram</t>
+          <t>Super Dog and Super Cat</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3778,24 +3778,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
+          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
+          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Deewana</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3813,24 +3813,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Deewana.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Vanda Devullu</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3848,24 +3848,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Vanda Devullu.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Elra Kaaleliyatte Kaala</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3883,24 +3883,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>M4M: Motive for Murder</t>
+          <t>Hunting Jessica Brok</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3918,24 +3918,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
+          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
+          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Blast</t>
+          <t>Obsession</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3953,34 +3953,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blast.jpg</t>
+          <t>home/07-01-2026/Obsession.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
+          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Avatar: Fire and Ash</t>
+          <t>Continental Split</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3988,34 +3988,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
+          <t>home/07-01-2026/Continental Split.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
+          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>The Sheep Detectives</t>
+          <t>Great White Waters</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4023,34 +4023,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
+          <t>home/07-01-2026/Great White Waters.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
+          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Gladiator Underground</t>
+          <t>Road Wars: Max Fury</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4058,24 +4058,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Gladiator Underground.jpg</t>
+          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
+          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Supergirl</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4093,34 +4093,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/07-01-2026/Supergirl.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>The Last Breath</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4128,24 +4128,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/07-01-2026/The Last Breath.jpg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Painkili</t>
+          <t>Little Brother</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4163,34 +4163,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Painkili.jpg</t>
+          <t>home/07-01-2026/Little Brother.jpg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
+          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Seems Like Old Times</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4198,34 +4198,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
+          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
+          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>The Furies</t>
+          <t>The Yeti</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4233,24 +4233,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Furies.jpg</t>
+          <t>home/07-01-2026/The Yeti.jpg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
+          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Garbham</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4268,34 +4268,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Garbham.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Blind Waters</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4303,24 +4303,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blind Waters.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Lingam Season 1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4338,24 +4338,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-25-2026/Lingam Season 1.jpg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Moondram Kan</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4373,24 +4373,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-25-2026/Moondram Kan.jpg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Raja Shivaji</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4408,24 +4408,24 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-25-2026/Raja Shivaji.jpg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4443,24 +4443,24 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Thank You Subbarao</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4478,24 +4478,24 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>In the Hand of Dante</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4513,24 +4513,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
+          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Maa Inti Bangaaram</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4548,24 +4548,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Husbands in Action</t>
+          <t>Deewana</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4583,24 +4583,24 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Husbands in Action.jpg</t>
+          <t>home/06-24-2026/Deewana.jpg</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
+          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Cocktail 2</t>
+          <t>Vanda Devullu</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4618,24 +4618,24 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Cocktail 2.jpg</t>
+          <t>home/06-24-2026/Vanda Devullu.jpg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
+          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4653,24 +4653,24 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Voicemails for Isabelle</t>
+          <t>M4M: Motive for Murder</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4688,24 +4688,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
+          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
+          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Blast</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4723,34 +4723,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/Blast.jpg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Save The Tigers Season 3</t>
+          <t>Avatar: Fire and Ash</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4758,24 +4758,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
+          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
+          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>The Sheep Detectives</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4793,24 +4793,24 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>The Grey Men 2</t>
+          <t>Gladiator Underground</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4828,24 +4828,24 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>home/06-19-2026/The Grey Men 2.jpg</t>
+          <t>home/06-24-2026/Gladiator Underground.jpg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
+          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4863,24 +4863,24 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4898,24 +4898,24 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Painkili</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4933,29 +4933,29 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Painkili.jpg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Mortal Kombat 2</t>
+          <t>Seems Like Old Times</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4968,34 +4968,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
+          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
+          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>The Furies</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5003,24 +5003,24 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-24-2026/The Furies.jpg</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Garbham</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5038,34 +5038,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-24-2026/Garbham.jpg</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Veerabhadrudu</t>
+          <t>Blind Waters</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5073,24 +5073,24 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
+          <t>home/06-24-2026/Blind Waters.jpg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
+          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5108,24 +5108,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sattendru Maarudhu Vaanilai</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5143,24 +5143,24 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5178,34 +5178,34 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Pongala</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5213,24 +5213,24 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Pongala.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Thank You Subbarao</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5248,24 +5248,24 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Shelter.jpg</t>
+          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
+          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Whistle</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5283,24 +5283,24 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Whistle.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
+          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5318,24 +5318,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Husbands in Action</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5353,34 +5353,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Husbands in Action.jpg</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>The Deep</t>
+          <t>Cocktail 2</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5388,34 +5388,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>home/06-16-2026/The Deep.jpg</t>
+          <t>home/06-19-2026/Cocktail 2.jpg</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
+          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Seven Years in Tibet</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5423,24 +5423,24 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Kolahalamedu</t>
+          <t>Voicemails for Isabelle</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5458,24 +5458,24 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kolahalamedu.jpg</t>
+          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
+          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5493,24 +5493,24 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Normal.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Save The Tigers Season 3</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5528,24 +5528,24 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Vikalpa</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5563,34 +5563,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Vikalpa.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>The Grey Men 2</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5598,24 +5598,24 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/The Grey Men 2.jpg</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Karuppu</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5633,24 +5633,24 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Karuppu.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sshhh Season 3</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5668,24 +5668,24 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>R.L. Stine’s Pumpkinhead</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5703,24 +5703,24 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Mortal Kombat 2</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5738,24 +5738,24 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peddi.jpg</t>
+          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
+          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5773,24 +5773,24 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5808,24 +5808,24 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Veerabhadrudu</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5843,24 +5843,24 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5878,24 +5878,24 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5913,24 +5913,24 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5948,34 +5948,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>Pongala</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5983,24 +5983,24 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Trikala Script of God.jpg</t>
+          <t>home/06-16-2026/Pongala.jpg</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
+          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6018,24 +6018,24 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Shelter.jpg</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6053,24 +6053,24 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-16-2026/Whistle.jpg</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6088,24 +6088,24 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6123,34 +6123,34 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Blast Zone.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>The Deep</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6158,34 +6158,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Maa Behen.jpg</t>
+          <t>home/06-16-2026/The Deep.jpg</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Seven Years in Tibet</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6193,24 +6193,24 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kattalan.jpg</t>
+          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Kolahalamedu</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6228,34 +6228,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-16-2026/Kolahalamedu.jpg</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6263,24 +6263,24 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Beast of War.jpg</t>
+          <t>home/06-16-2026/Normal.jpg</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6298,24 +6298,24 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sandigdham.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Vikalpa</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6333,24 +6333,24 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kara.jpg</t>
+          <t>home/06-16-2026/Vikalpa.jpg</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6368,24 +6368,24 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Karuppu</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6403,24 +6403,24 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Purushaha.jpg</t>
+          <t>home/06-16-2026/Karuppu.jpg</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Hai Jawani Toh Ishq Hona Hai</t>
+          <t>Sshhh Season 3</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6438,24 +6438,24 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Summer House</t>
+          <t>R.L. Stine’s Pumpkinhead</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6473,24 +6473,24 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Summer House.jpg</t>
+          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -6525,7 +6525,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Juniors Journey</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Juniors Journey.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -6560,7 +6560,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Ginny Weds Sunny 2</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -6595,7 +6595,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peter.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -6630,7 +6630,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -6665,7 +6665,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -6700,7 +6700,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -6735,7 +6735,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -6770,7 +6770,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -6805,33 +6805,803 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
+          <t>Sukhamano Sukhamann</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Carmeni Selvam</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Blast Zone</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Maa Behen</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>1</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Kattalan</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Kattalan.jpg</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Ramani Kalyanam</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>1</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Beast of War</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>1</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Beast of War.jpg</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Sandigdham</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>1</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Kara</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Kara.jpg</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>KD: The Devil</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Purushaha</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>1</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Purushaha.jpg</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>1</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Summer House</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Summer House.jpg</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Juniors Journey</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Ginny Weds Sunny 2</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>1</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Ugly Story</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
           <t>Office Romance</t>
         </is>
       </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
         <is>
           <t>Telugu Dubbed</t>
         </is>
       </c>
-      <c r="D183" t="n">
-        <v>1</v>
-      </c>
-      <c r="E183" t="inlineStr">
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="inlineStr">
         <is>
           <t>home/06-06-2026/Office Romance.jpg</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
+      <c r="F205" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
+      <c r="G205" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
@@ -6848,7 +7618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6870,130 +7640,140 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B15" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,14 +418,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G205"/>
+  <dimension ref="A1:G225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
     <col width="47" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chennai Love Story</t>
+          <t>Oh Sukumari</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Chennai Love Story.jpg</t>
+          <t>home/08-07-2026/Oh Sukumari.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nYYjR9diizE</t>
+          <t>https://www.youtube.com/watch?v=TL0-kMdqt_s</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Srinivasa Mangapuram</t>
+          <t>M.R.P – Neekentha Naakentha</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,24 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Srinivasa Mangapuram.jpg</t>
+          <t>home/08-07-2026/M.R.P – Neekentha Naakentha.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kKIqF2oyj1Q</t>
+          <t>https://www.youtube.com/watch?v=vaXa2-WIBE0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jana Nayakudu</t>
+          <t>Uyir</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Jana Nayakudu.jpg</t>
+          <t>home/08-07-2026/Uyir.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=L81nWRwRmnI</t>
+          <t>https://www.youtube.com/watch?v=DyTziQOTNK4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gatta Kusthi 2</t>
+          <t>Operation Safed Sagar Season 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -593,24 +593,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
+          <t>home/08-07-2026/Operation Safed Sagar Season 1.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
+          <t>https://www.youtube.com/watch?v=eFwHqth3i1Y</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Police Complaint</t>
+          <t>Second Case Of Seetharam</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -628,24 +628,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Police Complaint.jpg</t>
+          <t>home/08-07-2026/Second Case Of Seetharam.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=87aOxmtPmX0</t>
+          <t>https://www.youtube.com/watch?v=t7fvUNU7lnk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Love Oh Love</t>
+          <t>Vadhandhi Season 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -663,24 +663,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Love Oh Love.jpg</t>
+          <t>home/08-07-2026/Vadhandhi Season 2.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ikZoI6wmvBQ</t>
+          <t>https://www.youtube.com/watch?v=7cCI3G8XmH8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Balan</t>
+          <t>Geetha Sakshiga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -698,24 +698,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Balan.jpg</t>
+          <t>home/08-07-2026/Geetha Sakshiga.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cjWTqndgZ_M</t>
+          <t>https://www.youtube.com/watch?v=Md37YuwURBI</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Objection My Lord Season 1</t>
+          <t>Mahabali 1980’s</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -733,24 +733,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Objection My Lord Season 1.jpg</t>
+          <t>home/08-07-2026/Mahabali 1980’s.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Fhr9JdlLRwY</t>
+          <t>https://www.youtube.com/watch?v=1NKlkWQi4rM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Con City</t>
+          <t>Uyir</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -768,24 +768,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Con City.jpg</t>
+          <t>home/08-07-2026/Uyir.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wT2VV6bq6hU</t>
+          <t>https://www.youtube.com/watch?v=DyTziQOTNK4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pallichattambi</t>
+          <t>The Last House</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -803,24 +803,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Pallichattambi.jpg</t>
+          <t>home/08-07-2026/The Last House.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k6WQlVFkvgg</t>
+          <t>https://www.youtube.com/watch?v=MLxgaz2Zp1k</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chinna Chinna Aasai</t>
+          <t>Operation Safed Sagar Season 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -838,24 +838,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Chinna Chinna Aasai.jpg</t>
+          <t>home/08-07-2026/Operation Safed Sagar Season 1.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f_mCvoMgoYs</t>
+          <t>https://www.youtube.com/watch?v=eFwHqth3i1Y</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Balan</t>
+          <t>Maggi Pusthaka</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,24 +873,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Balan.jpg</t>
+          <t>home/08-07-2026/Maggi Pusthaka.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cjWTqndgZ_M</t>
+          <t>https://www.youtube.com/watch?v=APr2T-qgoRc</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spider-Man: Brand New Day</t>
+          <t>Sathyathil Sambhavichathu</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -908,24 +908,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Spider-Man Brand New Day.jpg</t>
+          <t>home/08-07-2026/Sathyathil Sambhavichathu.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=62bIsvRcPv0</t>
+          <t>https://www.youtube.com/watch?v=_rO-Fw0TBos</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Objection My Lord Season 1</t>
+          <t>The Super Mario Galaxy Movie</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -943,24 +943,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Objection My Lord Season 1.jpg</t>
+          <t>home/08-07-2026/The Super Mario Galaxy Movie.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Fhr9JdlLRwY</t>
+          <t>https://www.youtube.com/watch?v=FdL2GorGdKc</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Srinivasa Mangapuram</t>
+          <t>M.R.P – Neekentha Naakentha</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -978,24 +978,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Srinivasa Mangapuram.jpg</t>
+          <t>home/08-07-2026/M.R.P – Neekentha Naakentha.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kKIqF2oyj1Q</t>
+          <t>https://www.youtube.com/watch?v=vaXa2-WIBE0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Son of Sara: Volume 1</t>
+          <t>Oh Sukumari</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,24 +1013,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Son of Sara Volume 1.jpg</t>
+          <t>home/08-07-2026/Oh Sukumari.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZTkXpVGpcRk</t>
+          <t>https://www.youtube.com/watch?v=TL0-kMdqt_s</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Police Complaint</t>
+          <t>Main Vaapas Aaunga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1048,24 +1048,24 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Police Complaint.jpg</t>
+          <t>home/08-07-2026/Main Vaapas Aaunga.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-q63oK7GhI0</t>
+          <t>https://www.youtube.com/watch?v=PRUTWluKRW8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Chum</t>
+          <t>Idhayam Murali</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1083,24 +1083,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Chum.jpg</t>
+          <t>home/08-07-2026/Idhayam Murali.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=VUdPlZgXOjE</t>
+          <t>https://www.youtube.com/watch?v=lfoQfD0AjTs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gatta Kusthi 2</t>
+          <t>Vadhandhi Season 2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1118,24 +1118,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
+          <t>home/08-07-2026/Vadhandhi Season 2.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
+          <t>https://www.youtube.com/watch?v=7cCI3G8XmH8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gatta Kusthi 2</t>
+          <t>Oh Sukumari</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
+          <t>home/08-07-2026/Oh Sukumari.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
+          <t>https://www.youtube.com/watch?v=TL0-kMdqt_s</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Love Oh Love</t>
+          <t>Chennai Love Story</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Love Oh Love.jpg</t>
+          <t>home/08-01-2026/Chennai Love Story.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ikZoI6wmvBQ</t>
+          <t>https://www.youtube.com/watch?v=nYYjR9diizE</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1205,7 +1205,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kaalam Paranja Kadha</t>
+          <t>Srinivasa Mangapuram</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Kaalam Paranja Kadha.jpg</t>
+          <t>home/08-01-2026/Srinivasa Mangapuram.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Hox9qawUA-g</t>
+          <t>https://www.youtube.com/watch?v=kKIqF2oyj1Q</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1240,7 +1240,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vadala</t>
+          <t>Jana Nayakudu</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1258,24 +1258,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Vadala.jpg</t>
+          <t>home/08-01-2026/Jana Nayakudu.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
+          <t>https://www.youtube.com/watch?v=L81nWRwRmnI</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Mister Middle Class</t>
+          <t>Gatta Kusthi 2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Mister Middle Class.jpg</t>
+          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
+          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Transfer Trimurthulu</t>
+          <t>Police Complaint</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1328,24 +1328,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Transfer Trimurthulu.jpg</t>
+          <t>home/08-01-2026/Police Complaint.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cnqP9cCU5Ak</t>
+          <t>https://www.youtube.com/watch?v=87aOxmtPmX0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hrudhayam Murali</t>
+          <t>Love Oh Love</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1363,24 +1363,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
+          <t>home/08-01-2026/Love Oh Love.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
+          <t>https://www.youtube.com/watch?v=ikZoI6wmvBQ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Gedelaraju Kakinada Taluka</t>
+          <t>Balan</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1398,24 +1398,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Gedelaraju Kakinada Taluka.jpg</t>
+          <t>home/08-01-2026/Balan.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SBX2RFgxzYg</t>
+          <t>https://www.youtube.com/watch?v=cjWTqndgZ_M</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Ek Din</t>
+          <t>Objection My Lord Season 1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1433,24 +1433,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Ek Din.jpg</t>
+          <t>home/08-01-2026/Objection My Lord Season 1.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
+          <t>https://www.youtube.com/watch?v=Fhr9JdlLRwY</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>The Odyssey</t>
+          <t>Con City</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1468,24 +1468,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/07-20-2026/The Odyssey.jpg</t>
+          <t>home/08-01-2026/Con City.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f_bKjZeJBBI</t>
+          <t>https://www.youtube.com/watch?v=wT2VV6bq6hU</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Vadala</t>
+          <t>Pallichattambi</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1503,34 +1503,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Vadala.jpg</t>
+          <t>home/08-01-2026/Pallichattambi.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
+          <t>https://www.youtube.com/watch?v=k6WQlVFkvgg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Hijack 1971</t>
+          <t>Chinna Chinna Aasai</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1538,24 +1538,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Hijack 1971.jpg</t>
+          <t>home/08-01-2026/Chinna Chinna Aasai.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UxyutkXQnvA</t>
+          <t>https://www.youtube.com/watch?v=f_mCvoMgoYs</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mister Middle Class</t>
+          <t>Balan</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1573,24 +1573,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Mister Middle Class.jpg</t>
+          <t>home/08-01-2026/Balan.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
+          <t>https://www.youtube.com/watch?v=cjWTqndgZ_M</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ek Din</t>
+          <t>Spider-Man: Brand New Day</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1608,24 +1608,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Ek Din.jpg</t>
+          <t>home/08-01-2026/Spider-Man Brand New Day.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
+          <t>https://www.youtube.com/watch?v=62bIsvRcPv0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ek Din</t>
+          <t>Objection My Lord Season 1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Ek Din.jpg</t>
+          <t>home/08-01-2026/Objection My Lord Season 1.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
+          <t>https://www.youtube.com/watch?v=Fhr9JdlLRwY</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Thiraivi</t>
+          <t>Srinivasa Mangapuram</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1678,24 +1678,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Thiraivi.jpg</t>
+          <t>home/08-01-2026/Srinivasa Mangapuram.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YMLv6vV43Vo</t>
+          <t>https://www.youtube.com/watch?v=kKIqF2oyj1Q</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Hrudhayam Murali</t>
+          <t>Son of Sara: Volume 1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1713,34 +1713,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
+          <t>home/08-01-2026/Son of Sara Volume 1.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
+          <t>https://www.youtube.com/watch?v=ZTkXpVGpcRk</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>13 Days, 13 Nights</t>
+          <t>Police Complaint</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1748,24 +1748,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>home/07-20-2026/13 Days, 13 Nights.jpg</t>
+          <t>home/08-01-2026/Police Complaint.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mAKOqFt-LVQ</t>
+          <t>https://www.youtube.com/watch?v=-q63oK7GhI0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>23 000 Lives</t>
+          <t>Chum</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1783,29 +1783,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>home/07-20-2026/23 000 Lives.jpg</t>
+          <t>home/08-01-2026/Chum.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=89dugTvBEWw</t>
+          <t>https://www.youtube.com/watch?v=VUdPlZgXOjE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Chithini</t>
+          <t>Gatta Kusthi 2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1818,24 +1818,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Chithini.jpg</t>
+          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pRbfgUVGAJg</t>
+          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lenin</t>
+          <t>Gatta Kusthi 2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1853,24 +1853,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Lenin.jpg</t>
+          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
+          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ikka</t>
+          <t>Love Oh Love</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1888,24 +1888,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Ikka.jpg</t>
+          <t>home/08-01-2026/Love Oh Love.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
+          <t>https://www.youtube.com/watch?v=ikZoI6wmvBQ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mukhbir: The Story of a Spy</t>
+          <t>Kaalam Paranja Kadha</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1923,24 +1923,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
+          <t>home/08-01-2026/Kaalam Paranja Kadha.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
+          <t>https://www.youtube.com/watch?v=Hox9qawUA-g</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Tholaivil Oru Kadhal</t>
+          <t>Vadala</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1958,34 +1958,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Tholaivil Oru Kadhal.jpg</t>
+          <t>home/07-20-2026/Vadala.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bR1s6WIsyfE</t>
+          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>The Trip</t>
+          <t>Mister Middle Class</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1993,34 +1993,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>home/07-13-2026/The Trip.jpg</t>
+          <t>home/07-20-2026/Mister Middle Class.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=K9bPJmy68Rs</t>
+          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Hollow Man 2</t>
+          <t>Transfer Trimurthulu</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2028,24 +2028,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Hollow Man 2.jpg</t>
+          <t>home/07-20-2026/Transfer Trimurthulu.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=koZuEDeQf3Q</t>
+          <t>https://www.youtube.com/watch?v=cnqP9cCU5Ak</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Lenin</t>
+          <t>Hrudhayam Murali</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2063,34 +2063,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Lenin.jpg</t>
+          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
+          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Only the Brave</t>
+          <t>Gedelaraju Kakinada Taluka</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2098,24 +2098,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Only the Brave.jpg</t>
+          <t>home/07-20-2026/Gedelaraju Kakinada Taluka.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EE_GY6zccqc</t>
+          <t>https://www.youtube.com/watch?v=SBX2RFgxzYg</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dhamaal 4</t>
+          <t>Ek Din</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2133,24 +2133,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Dhamaal 4.jpg</t>
+          <t>home/07-20-2026/Ek Din.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IG-eByZdz6Y</t>
+          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ikka</t>
+          <t>The Odyssey</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2168,24 +2168,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Ikka.jpg</t>
+          <t>home/07-20-2026/The Odyssey.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
+          <t>https://www.youtube.com/watch?v=f_bKjZeJBBI</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mukhbir: The Story of a Spy</t>
+          <t>Vadala</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2203,34 +2203,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
+          <t>home/07-20-2026/Vadala.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
+          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Shikhandi</t>
+          <t>Hijack 1971</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Shikhandi.jpg</t>
+          <t>home/07-20-2026/Hijack 1971.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vLuLhH7oREY</t>
+          <t>https://www.youtube.com/watch?v=UxyutkXQnvA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Mister Middle Class</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2273,24 +2273,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-20-2026/Mister Middle Class.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Ek Din</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2308,24 +2308,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-20-2026/Ek Din.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Ek Din</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2343,24 +2343,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-20-2026/Ek Din.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Thiraivi</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2378,24 +2378,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-20-2026/Thiraivi.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=YMLv6vV43Vo</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Hrudhayam Murali</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2413,34 +2413,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>13 Days, 13 Nights</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2448,24 +2448,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-20-2026/13 Days, 13 Nights.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=mAKOqFt-LVQ</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>23 000 Lives</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2483,34 +2483,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-20-2026/23 000 Lives.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=89dugTvBEWw</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Pati Patni Aur Woh Do</t>
+          <t>Chithini</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2518,24 +2518,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Pati Patni Aur Woh Do.jpg</t>
+          <t>home/07-20-2026/Chithini.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ceooxuS-sww</t>
+          <t>https://www.youtube.com/watch?v=pRbfgUVGAJg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Lenin</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2553,24 +2553,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-13-2026/Lenin.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Ikka</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-13-2026/Ikka.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Mukhbir: The Story of a Spy</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2623,24 +2623,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Tholaivil Oru Kadhal</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2658,34 +2658,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-13-2026/Tholaivil Oru Kadhal.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=bR1s6WIsyfE</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>The Trip</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2693,34 +2693,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-13-2026/The Trip.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=K9bPJmy68Rs</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Hollow Man 2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/Hollow Man 2.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=koZuEDeQf3Q</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Lenin</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2763,34 +2763,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/Lenin.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Only the Brave</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2798,24 +2798,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/Only the Brave.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=EE_GY6zccqc</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Nagabandham</t>
+          <t>Dhamaal 4</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2833,24 +2833,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Nagabandham.jpg</t>
+          <t>home/07-13-2026/Dhamaal 4.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
+          <t>https://www.youtube.com/watch?v=IG-eByZdz6Y</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Chand Mera Dil</t>
+          <t>Ikka</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2868,24 +2868,24 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Chand Mera Dil.jpg</t>
+          <t>home/07-13-2026/Ikka.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rRQ8oKCoYrQ</t>
+          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Kotha Malupu</t>
+          <t>Mukhbir: The Story of a Spy</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2903,24 +2903,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Kotha Malupu.jpg</t>
+          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qnd1Xwv9NP8</t>
+          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Double Barrel</t>
+          <t>Shikhandi</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2938,24 +2938,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Double Barrel.jpg</t>
+          <t>home/07-13-2026/Shikhandi.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Ij0mjRt1QIA</t>
+          <t>https://www.youtube.com/watch?v=vLuLhH7oREY</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Nagabandham</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2973,24 +2973,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Nagabandham.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3008,24 +3008,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3043,24 +3043,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3078,24 +3078,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3113,24 +3113,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3148,24 +3148,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3183,24 +3183,24 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Pati Patni Aur Woh Do</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3218,24 +3218,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Alpha.jpg</t>
+          <t>home/07-09-2026/Pati Patni Aur Woh Do.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
+          <t>https://www.youtube.com/watch?v=ceooxuS-sww</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Pritam and Pedro Season 1</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3253,24 +3253,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Charukesi</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3288,24 +3288,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Charukesi.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3323,24 +3323,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Daadi Ki Shaadi</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3358,24 +3358,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Hangman</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3393,24 +3393,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Hangman.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3428,24 +3428,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3463,24 +3463,24 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3498,24 +3498,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3533,24 +3533,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Chand Mera Dil</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3568,24 +3568,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-06-2026/Chand Mera Dil.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=rRQ8oKCoYrQ</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Kotha Malupu</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3603,24 +3603,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-06-2026/Kotha Malupu.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=qnd1Xwv9NP8</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Double Barrel</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3638,24 +3638,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-06-2026/Double Barrel.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=Ij0mjRt1QIA</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3673,24 +3673,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3708,34 +3708,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Bossa Nova</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3743,24 +3743,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Bossa Nova.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Super Dog and Super Cat</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3778,24 +3778,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3813,24 +3813,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3848,24 +3848,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Elra Kaaleliyatte Kaala</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3883,24 +3883,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Hunting Jessica Brok</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3918,24 +3918,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
+          <t>home/07-03-2026/Alpha.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
+          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Obsession</t>
+          <t>Pritam and Pedro Season 1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3953,34 +3953,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Obsession.jpg</t>
+          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
+          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Continental Split</t>
+          <t>Charukesi</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3988,34 +3988,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Continental Split.jpg</t>
+          <t>home/07-03-2026/Charukesi.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
+          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Great White Waters</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4023,34 +4023,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Great White Waters.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Road Wars: Max Fury</t>
+          <t>Daadi Ki Shaadi</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4058,24 +4058,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
+          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
+          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Supergirl</t>
+          <t>Hangman</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4093,34 +4093,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Supergirl.jpg</t>
+          <t>home/07-03-2026/Hangman.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
+          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>The Last Breath</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4128,24 +4128,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Last Breath.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Little Brother</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4163,24 +4163,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Little Brother.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4198,24 +4198,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>The Yeti</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4233,24 +4233,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Yeti.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4268,24 +4268,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4303,24 +4303,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Lingam Season 1</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4338,24 +4338,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Lingam Season 1.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Moondram Kan</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4373,24 +4373,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Moondram Kan.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Raja Shivaji</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4408,34 +4408,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Raja Shivaji.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Bossa Nova</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4443,24 +4443,24 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-02-2026/Bossa Nova.jpg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Super Dog and Super Cat</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4478,24 +4478,24 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>In the Hand of Dante</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4513,24 +4513,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Maa Inti Bangaaram</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4548,24 +4548,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Deewana</t>
+          <t>Elra Kaaleliyatte Kaala</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4583,24 +4583,24 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Deewana.jpg</t>
+          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
+          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Vanda Devullu</t>
+          <t>Hunting Jessica Brok</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4618,24 +4618,24 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Vanda Devullu.jpg</t>
+          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
+          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Obsession</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4653,34 +4653,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/07-01-2026/Obsession.jpg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>M4M: Motive for Murder</t>
+          <t>Continental Split</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4688,34 +4688,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
+          <t>home/07-01-2026/Continental Split.jpg</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
+          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Blast</t>
+          <t>Great White Waters</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4723,34 +4723,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blast.jpg</t>
+          <t>home/07-01-2026/Great White Waters.jpg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
+          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Avatar: Fire and Ash</t>
+          <t>Road Wars: Max Fury</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4758,24 +4758,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
+          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
+          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>The Sheep Detectives</t>
+          <t>Supergirl</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4793,29 +4793,29 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
+          <t>home/07-01-2026/Supergirl.jpg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
+          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Gladiator Underground</t>
+          <t>The Last Breath</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4828,24 +4828,24 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Gladiator Underground.jpg</t>
+          <t>home/07-01-2026/The Last Breath.jpg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
+          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Little Brother</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4863,24 +4863,24 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/07-01-2026/Little Brother.jpg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4898,24 +4898,24 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Painkili</t>
+          <t>The Yeti</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4933,34 +4933,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Painkili.jpg</t>
+          <t>home/07-01-2026/The Yeti.jpg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
+          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Seems Like Old Times</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4968,34 +4968,34 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>The Furies</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5003,24 +5003,24 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Furies.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Garbham</t>
+          <t>Lingam Season 1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5038,34 +5038,34 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Garbham.jpg</t>
+          <t>home/06-25-2026/Lingam Season 1.jpg</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
+          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Blind Waters</t>
+          <t>Moondram Kan</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5073,24 +5073,24 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blind Waters.jpg</t>
+          <t>home/06-25-2026/Moondram Kan.jpg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
+          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Raja Shivaji</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5100,7 +5100,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5108,24 +5108,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-25-2026/Raja Shivaji.jpg</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5143,24 +5143,24 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5178,24 +5178,24 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>In the Hand of Dante</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5213,24 +5213,24 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Thank You Subbarao</t>
+          <t>Maa Inti Bangaaram</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5248,24 +5248,24 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
+          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
+          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Deewana</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5283,24 +5283,24 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Deewana.jpg</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
+          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Vanda Devullu</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5318,24 +5318,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Vanda Devullu.jpg</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Husbands in Action</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5353,24 +5353,24 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Husbands in Action.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Cocktail 2</t>
+          <t>M4M: Motive for Murder</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5388,24 +5388,24 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Cocktail 2.jpg</t>
+          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
+          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Blast</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5423,29 +5423,29 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/Blast.jpg</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Voicemails for Isabelle</t>
+          <t>Avatar: Fire and Ash</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -5458,24 +5458,24 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
+          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
+          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>The Sheep Detectives</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5493,34 +5493,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Save The Tigers Season 3</t>
+          <t>Gladiator Underground</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5528,24 +5528,24 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
+          <t>home/06-24-2026/Gladiator Underground.jpg</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
+          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5563,34 +5563,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>The Grey Men 2</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5598,24 +5598,24 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>home/06-19-2026/The Grey Men 2.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Painkili</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5633,34 +5633,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Painkili.jpg</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Seems Like Old Times</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5668,34 +5668,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>The Furies</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5703,24 +5703,24 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/The Furies.jpg</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Mortal Kombat 2</t>
+          <t>Garbham</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5738,34 +5738,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
+          <t>home/06-24-2026/Garbham.jpg</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
+          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Blind Waters</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5773,24 +5773,24 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-24-2026/Blind Waters.jpg</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5808,24 +5808,24 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Veerabhadrudu</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5843,24 +5843,24 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5878,24 +5878,24 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sattendru Maarudhu Vaanilai</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5913,24 +5913,24 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Thank You Subbarao</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5948,29 +5948,29 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Pongala</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5983,24 +5983,24 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Pongala.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
+          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6018,24 +6018,24 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Shelter.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Whistle</t>
+          <t>Husbands in Action</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6053,24 +6053,24 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Whistle.jpg</t>
+          <t>home/06-19-2026/Husbands in Action.jpg</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
+          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Cocktail 2</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6088,24 +6088,24 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Cocktail 2.jpg</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6123,29 +6123,29 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>The Deep</t>
+          <t>Voicemails for Isabelle</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -6158,34 +6158,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>home/06-16-2026/The Deep.jpg</t>
+          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
+          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Seven Years in Tibet</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6193,24 +6193,24 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Kolahalamedu</t>
+          <t>Save The Tigers Season 3</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6228,24 +6228,24 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kolahalamedu.jpg</t>
+          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
+          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6263,34 +6263,34 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Normal.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>The Grey Men 2</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6298,24 +6298,24 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/The Grey Men 2.jpg</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Vikalpa</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6333,24 +6333,24 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Vikalpa.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6368,24 +6368,24 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Karuppu</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6403,24 +6403,24 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Karuppu.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Sshhh Season 3</t>
+          <t>Mortal Kombat 2</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6438,24 +6438,24 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
+          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
+          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>R.L. Stine’s Pumpkinhead</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -6490,7 +6490,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6508,24 +6508,24 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peddi.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Veerabhadrudu</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6543,24 +6543,24 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6578,24 +6578,24 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6613,24 +6613,24 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6648,34 +6648,34 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Pongala</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6683,24 +6683,24 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-16-2026/Pongala.jpg</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6718,24 +6718,24 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-16-2026/Shelter.jpg</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
+          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6753,24 +6753,24 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Trikala Script of God.jpg</t>
+          <t>home/06-16-2026/Whistle.jpg</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
+          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6788,24 +6788,24 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6823,34 +6823,34 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>The Deep</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6858,34 +6858,34 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-16-2026/The Deep.jpg</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>Seven Years in Tibet</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6893,24 +6893,24 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Blast Zone.jpg</t>
+          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Kolahalamedu</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6928,24 +6928,24 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Maa Behen.jpg</t>
+          <t>home/06-16-2026/Kolahalamedu.jpg</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6963,24 +6963,24 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kattalan.jpg</t>
+          <t>home/06-16-2026/Normal.jpg</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6998,34 +6998,34 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>Vikalpa</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7033,24 +7033,24 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Beast of War.jpg</t>
+          <t>home/06-16-2026/Vikalpa.jpg</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7068,24 +7068,24 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sandigdham.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Karuppu</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7103,24 +7103,24 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kara.jpg</t>
+          <t>home/06-16-2026/Karuppu.jpg</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Sshhh Season 3</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7138,24 +7138,24 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>R.L. Stine’s Pumpkinhead</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7173,24 +7173,24 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Purushaha.jpg</t>
+          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Hai Jawani Toh Ishq Hona Hai</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -7200,7 +7200,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -7225,7 +7225,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Summer House</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7243,12 +7243,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Summer House.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -7260,7 +7260,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7278,12 +7278,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -7295,7 +7295,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Juniors Journey</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7313,12 +7313,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Juniors Journey.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -7330,7 +7330,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Ginny Weds Sunny 2</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -7365,7 +7365,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peter.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -7400,7 +7400,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -7435,7 +7435,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7505,7 +7505,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -7540,7 +7540,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -7575,33 +7575,733 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
+          <t>Blast Zone</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Maa Behen</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Kattalan</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Kattalan.jpg</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Ramani Kalyanam</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Beast of War</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>1</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Beast of War.jpg</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Sandigdham</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Kara</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Kara.jpg</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>KD: The Devil</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Purushaha</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Purushaha.jpg</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Summer House</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Telugu Dubbed</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Summer House.jpg</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Juniors Journey</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Ginny Weds Sunny 2</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Ugly Story</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>1</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
           <t>Office Romance</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
         <is>
           <t>Telugu Dubbed</t>
         </is>
       </c>
-      <c r="D205" t="n">
-        <v>1</v>
-      </c>
-      <c r="E205" t="inlineStr">
+      <c r="D225" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" t="inlineStr">
         <is>
           <t>home/06-06-2026/Office Romance.jpg</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
+      <c r="F225" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
+      <c r="G225" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
@@ -7618,7 +8318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7640,140 +8340,150 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B16" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G225"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Oh Sukumari</t>
+          <t>Korean Kanakaraju</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,24 +488,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Oh Sukumari.jpg</t>
+          <t>home/08-10-2026/Korean Kanakaraju.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TL0-kMdqt_s</t>
+          <t>https://www.youtube.com/watch?v=JIqKjjTfOxM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M.R.P – Neekentha Naakentha</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -523,24 +523,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/08-07-2026/M.R.P – Neekentha Naakentha.jpg</t>
+          <t>home/08-10-2026/DC.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vaXa2-WIBE0</t>
+          <t>https://www.youtube.com/watch?v=2kntxizQIFI</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Uyir</t>
+          <t>Korean Kanakaraju</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -558,24 +558,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Uyir.jpg</t>
+          <t>home/08-10-2026/Korean Kanakaraju.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DyTziQOTNK4</t>
+          <t>https://www.youtube.com/watch?v=JIqKjjTfOxM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Operation Safed Sagar Season 1</t>
+          <t>Nizhal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -593,24 +593,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Operation Safed Sagar Season 1.jpg</t>
+          <t>home/08-10-2026/Nizhal.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=eFwHqth3i1Y</t>
+          <t>https://www.youtube.com/watch?v=yqgTPndvRXo</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Second Case Of Seetharam</t>
+          <t>Moda Kavida Vatavarana</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -628,24 +628,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Second Case Of Seetharam.jpg</t>
+          <t>home/08-10-2026/Moda Kavida Vatavarana.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t7fvUNU7lnk</t>
+          <t>https://www.youtube.com/watch?v=0RuXnzkjAtU</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Vadhandhi Season 2</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -663,24 +663,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Vadhandhi Season 2.jpg</t>
+          <t>home/08-10-2026/DC.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7cCI3G8XmH8</t>
+          <t>https://www.youtube.com/watch?v=2kntxizQIFI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Geetha Sakshiga</t>
+          <t>Oh Sukumari</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Geetha Sakshiga.jpg</t>
+          <t>home/08-07-2026/Oh Sukumari.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Md37YuwURBI</t>
+          <t>https://www.youtube.com/watch?v=TL0-kMdqt_s</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mahabali 1980’s</t>
+          <t>M.R.P – Neekentha Naakentha</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -733,12 +733,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Mahabali 1980’s.jpg</t>
+          <t>home/08-07-2026/M.R.P – Neekentha Naakentha.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1NKlkWQi4rM</t>
+          <t>https://www.youtube.com/watch?v=vaXa2-WIBE0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -785,7 +785,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>The Last House</t>
+          <t>Operation Safed Sagar Season 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -803,12 +803,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/08-07-2026/The Last House.jpg</t>
+          <t>home/08-07-2026/Operation Safed Sagar Season 1.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=MLxgaz2Zp1k</t>
+          <t>https://www.youtube.com/watch?v=eFwHqth3i1Y</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -820,7 +820,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Operation Safed Sagar Season 1</t>
+          <t>Second Case Of Seetharam</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -838,12 +838,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Operation Safed Sagar Season 1.jpg</t>
+          <t>home/08-07-2026/Second Case Of Seetharam.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=eFwHqth3i1Y</t>
+          <t>https://www.youtube.com/watch?v=t7fvUNU7lnk</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -855,7 +855,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Maggi Pusthaka</t>
+          <t>Vadhandhi Season 2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,12 +873,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Maggi Pusthaka.jpg</t>
+          <t>home/08-07-2026/Vadhandhi Season 2.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=APr2T-qgoRc</t>
+          <t>https://www.youtube.com/watch?v=7cCI3G8XmH8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sathyathil Sambhavichathu</t>
+          <t>Geetha Sakshiga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -908,12 +908,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Sathyathil Sambhavichathu.jpg</t>
+          <t>home/08-07-2026/Geetha Sakshiga.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_rO-Fw0TBos</t>
+          <t>https://www.youtube.com/watch?v=Md37YuwURBI</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -925,7 +925,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>The Super Mario Galaxy Movie</t>
+          <t>Mahabali 1980’s</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -943,12 +943,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/08-07-2026/The Super Mario Galaxy Movie.jpg</t>
+          <t>home/08-07-2026/Mahabali 1980’s.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=FdL2GorGdKc</t>
+          <t>https://www.youtube.com/watch?v=1NKlkWQi4rM</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -960,7 +960,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M.R.P – Neekentha Naakentha</t>
+          <t>Uyir</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -978,12 +978,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/08-07-2026/M.R.P – Neekentha Naakentha.jpg</t>
+          <t>home/08-07-2026/Uyir.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vaXa2-WIBE0</t>
+          <t>https://www.youtube.com/watch?v=DyTziQOTNK4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -995,7 +995,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Oh Sukumari</t>
+          <t>The Last House</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,12 +1013,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Oh Sukumari.jpg</t>
+          <t>home/08-07-2026/The Last House.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TL0-kMdqt_s</t>
+          <t>https://www.youtube.com/watch?v=MLxgaz2Zp1k</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1030,7 +1030,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Main Vaapas Aaunga</t>
+          <t>Operation Safed Sagar Season 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1048,12 +1048,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Main Vaapas Aaunga.jpg</t>
+          <t>home/08-07-2026/Operation Safed Sagar Season 1.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PRUTWluKRW8</t>
+          <t>https://www.youtube.com/watch?v=eFwHqth3i1Y</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Idhayam Murali</t>
+          <t>Maggi Pusthaka</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1083,12 +1083,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Idhayam Murali.jpg</t>
+          <t>home/08-07-2026/Maggi Pusthaka.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lfoQfD0AjTs</t>
+          <t>https://www.youtube.com/watch?v=APr2T-qgoRc</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Vadhandhi Season 2</t>
+          <t>Sathyathil Sambhavichathu</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Vadhandhi Season 2.jpg</t>
+          <t>home/08-07-2026/Sathyathil Sambhavichathu.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7cCI3G8XmH8</t>
+          <t>https://www.youtube.com/watch?v=_rO-Fw0TBos</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Oh Sukumari</t>
+          <t>The Super Mario Galaxy Movie</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Oh Sukumari.jpg</t>
+          <t>home/08-07-2026/The Super Mario Galaxy Movie.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TL0-kMdqt_s</t>
+          <t>https://www.youtube.com/watch?v=FdL2GorGdKc</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1170,7 +1170,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Chennai Love Story</t>
+          <t>M.R.P – Neekentha Naakentha</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1188,24 +1188,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Chennai Love Story.jpg</t>
+          <t>home/08-07-2026/M.R.P – Neekentha Naakentha.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nYYjR9diizE</t>
+          <t>https://www.youtube.com/watch?v=vaXa2-WIBE0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Srinivasa Mangapuram</t>
+          <t>Oh Sukumari</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Srinivasa Mangapuram.jpg</t>
+          <t>home/08-07-2026/Oh Sukumari.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kKIqF2oyj1Q</t>
+          <t>https://www.youtube.com/watch?v=TL0-kMdqt_s</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jana Nayakudu</t>
+          <t>Main Vaapas Aaunga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1258,24 +1258,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Jana Nayakudu.jpg</t>
+          <t>home/08-07-2026/Main Vaapas Aaunga.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=L81nWRwRmnI</t>
+          <t>https://www.youtube.com/watch?v=PRUTWluKRW8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gatta Kusthi 2</t>
+          <t>Idhayam Murali</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
+          <t>home/08-07-2026/Idhayam Murali.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
+          <t>https://www.youtube.com/watch?v=lfoQfD0AjTs</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Police Complaint</t>
+          <t>Vadhandhi Season 2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1328,24 +1328,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Police Complaint.jpg</t>
+          <t>home/08-07-2026/Vadhandhi Season 2.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=87aOxmtPmX0</t>
+          <t>https://www.youtube.com/watch?v=7cCI3G8XmH8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Love Oh Love</t>
+          <t>Oh Sukumari</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1363,24 +1363,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Love Oh Love.jpg</t>
+          <t>home/08-07-2026/Oh Sukumari.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ikZoI6wmvBQ</t>
+          <t>https://www.youtube.com/watch?v=TL0-kMdqt_s</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Balan</t>
+          <t>Chennai Love Story</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Balan.jpg</t>
+          <t>home/08-01-2026/Chennai Love Story.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cjWTqndgZ_M</t>
+          <t>https://www.youtube.com/watch?v=nYYjR9diizE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Objection My Lord Season 1</t>
+          <t>Srinivasa Mangapuram</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Objection My Lord Season 1.jpg</t>
+          <t>home/08-01-2026/Srinivasa Mangapuram.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Fhr9JdlLRwY</t>
+          <t>https://www.youtube.com/watch?v=kKIqF2oyj1Q</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1450,7 +1450,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Con City</t>
+          <t>Jana Nayakudu</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Con City.jpg</t>
+          <t>home/08-01-2026/Jana Nayakudu.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wT2VV6bq6hU</t>
+          <t>https://www.youtube.com/watch?v=L81nWRwRmnI</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1485,7 +1485,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Pallichattambi</t>
+          <t>Gatta Kusthi 2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Pallichattambi.jpg</t>
+          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k6WQlVFkvgg</t>
+          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1520,7 +1520,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Chinna Chinna Aasai</t>
+          <t>Police Complaint</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Chinna Chinna Aasai.jpg</t>
+          <t>home/08-01-2026/Police Complaint.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f_mCvoMgoYs</t>
+          <t>https://www.youtube.com/watch?v=87aOxmtPmX0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1555,7 +1555,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Balan</t>
+          <t>Love Oh Love</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Balan.jpg</t>
+          <t>home/08-01-2026/Love Oh Love.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cjWTqndgZ_M</t>
+          <t>https://www.youtube.com/watch?v=ikZoI6wmvBQ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1590,7 +1590,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Spider-Man: Brand New Day</t>
+          <t>Balan</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1608,12 +1608,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Spider-Man Brand New Day.jpg</t>
+          <t>home/08-01-2026/Balan.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=62bIsvRcPv0</t>
+          <t>https://www.youtube.com/watch?v=cjWTqndgZ_M</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1660,7 +1660,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Srinivasa Mangapuram</t>
+          <t>Con City</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Srinivasa Mangapuram.jpg</t>
+          <t>home/08-01-2026/Con City.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kKIqF2oyj1Q</t>
+          <t>https://www.youtube.com/watch?v=wT2VV6bq6hU</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Son of Sara: Volume 1</t>
+          <t>Pallichattambi</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Son of Sara Volume 1.jpg</t>
+          <t>home/08-01-2026/Pallichattambi.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZTkXpVGpcRk</t>
+          <t>https://www.youtube.com/watch?v=k6WQlVFkvgg</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1730,7 +1730,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Police Complaint</t>
+          <t>Chinna Chinna Aasai</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Police Complaint.jpg</t>
+          <t>home/08-01-2026/Chinna Chinna Aasai.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-q63oK7GhI0</t>
+          <t>https://www.youtube.com/watch?v=f_mCvoMgoYs</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1765,7 +1765,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Chum</t>
+          <t>Balan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Chum.jpg</t>
+          <t>home/08-01-2026/Balan.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=VUdPlZgXOjE</t>
+          <t>https://www.youtube.com/watch?v=cjWTqndgZ_M</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1800,7 +1800,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Gatta Kusthi 2</t>
+          <t>Spider-Man: Brand New Day</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1818,12 +1818,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
+          <t>home/08-01-2026/Spider-Man Brand New Day.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
+          <t>https://www.youtube.com/watch?v=62bIsvRcPv0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1835,7 +1835,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Gatta Kusthi 2</t>
+          <t>Objection My Lord Season 1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
+          <t>home/08-01-2026/Objection My Lord Season 1.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
+          <t>https://www.youtube.com/watch?v=Fhr9JdlLRwY</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1870,7 +1870,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Love Oh Love</t>
+          <t>Srinivasa Mangapuram</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Love Oh Love.jpg</t>
+          <t>home/08-01-2026/Srinivasa Mangapuram.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ikZoI6wmvBQ</t>
+          <t>https://www.youtube.com/watch?v=kKIqF2oyj1Q</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1905,7 +1905,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kaalam Paranja Kadha</t>
+          <t>Son of Sara: Volume 1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Kaalam Paranja Kadha.jpg</t>
+          <t>home/08-01-2026/Son of Sara Volume 1.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Hox9qawUA-g</t>
+          <t>https://www.youtube.com/watch?v=ZTkXpVGpcRk</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1940,7 +1940,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Vadala</t>
+          <t>Police Complaint</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1958,24 +1958,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Vadala.jpg</t>
+          <t>home/08-01-2026/Police Complaint.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
+          <t>https://www.youtube.com/watch?v=-q63oK7GhI0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mister Middle Class</t>
+          <t>Chum</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1993,24 +1993,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Mister Middle Class.jpg</t>
+          <t>home/08-01-2026/Chum.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
+          <t>https://www.youtube.com/watch?v=VUdPlZgXOjE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Transfer Trimurthulu</t>
+          <t>Gatta Kusthi 2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2028,24 +2028,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Transfer Trimurthulu.jpg</t>
+          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cnqP9cCU5Ak</t>
+          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Hrudhayam Murali</t>
+          <t>Gatta Kusthi 2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2063,24 +2063,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
+          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
+          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Gedelaraju Kakinada Taluka</t>
+          <t>Love Oh Love</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2098,24 +2098,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Gedelaraju Kakinada Taluka.jpg</t>
+          <t>home/08-01-2026/Love Oh Love.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SBX2RFgxzYg</t>
+          <t>https://www.youtube.com/watch?v=ikZoI6wmvBQ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ek Din</t>
+          <t>Kaalam Paranja Kadha</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2133,24 +2133,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Ek Din.jpg</t>
+          <t>home/08-01-2026/Kaalam Paranja Kadha.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
+          <t>https://www.youtube.com/watch?v=Hox9qawUA-g</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>The Odyssey</t>
+          <t>Vadala</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>home/07-20-2026/The Odyssey.jpg</t>
+          <t>home/07-20-2026/Vadala.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f_bKjZeJBBI</t>
+          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2185,7 +2185,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Vadala</t>
+          <t>Mister Middle Class</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Vadala.jpg</t>
+          <t>home/07-20-2026/Mister Middle Class.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
+          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2220,17 +2220,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hijack 1971</t>
+          <t>Transfer Trimurthulu</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Hijack 1971.jpg</t>
+          <t>home/07-20-2026/Transfer Trimurthulu.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UxyutkXQnvA</t>
+          <t>https://www.youtube.com/watch?v=cnqP9cCU5Ak</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2255,7 +2255,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Mister Middle Class</t>
+          <t>Hrudhayam Murali</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Mister Middle Class.jpg</t>
+          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
+          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2290,7 +2290,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ek Din</t>
+          <t>Gedelaraju Kakinada Taluka</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Ek Din.jpg</t>
+          <t>home/07-20-2026/Gedelaraju Kakinada Taluka.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
+          <t>https://www.youtube.com/watch?v=SBX2RFgxzYg</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2360,7 +2360,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Thiraivi</t>
+          <t>The Odyssey</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Thiraivi.jpg</t>
+          <t>home/07-20-2026/The Odyssey.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YMLv6vV43Vo</t>
+          <t>https://www.youtube.com/watch?v=f_bKjZeJBBI</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2395,7 +2395,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Hrudhayam Murali</t>
+          <t>Vadala</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
+          <t>home/07-20-2026/Vadala.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
+          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2430,12 +2430,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>13 Days, 13 Nights</t>
+          <t>Hijack 1971</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>home/07-20-2026/13 Days, 13 Nights.jpg</t>
+          <t>home/07-20-2026/Hijack 1971.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mAKOqFt-LVQ</t>
+          <t>https://www.youtube.com/watch?v=UxyutkXQnvA</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2465,7 +2465,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>23 000 Lives</t>
+          <t>Mister Middle Class</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>home/07-20-2026/23 000 Lives.jpg</t>
+          <t>home/07-20-2026/Mister Middle Class.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=89dugTvBEWw</t>
+          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2500,17 +2500,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Chithini</t>
+          <t>Ek Din</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Chithini.jpg</t>
+          <t>home/07-20-2026/Ek Din.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pRbfgUVGAJg</t>
+          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2535,7 +2535,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Lenin</t>
+          <t>Ek Din</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2553,24 +2553,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Lenin.jpg</t>
+          <t>home/07-20-2026/Ek Din.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
+          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ikka</t>
+          <t>Thiraivi</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Ikka.jpg</t>
+          <t>home/07-20-2026/Thiraivi.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
+          <t>https://www.youtube.com/watch?v=YMLv6vV43Vo</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mukhbir: The Story of a Spy</t>
+          <t>Hrudhayam Murali</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2623,34 +2623,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
+          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
+          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tholaivil Oru Kadhal</t>
+          <t>13 Days, 13 Nights</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2658,29 +2658,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Tholaivil Oru Kadhal.jpg</t>
+          <t>home/07-20-2026/13 Days, 13 Nights.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bR1s6WIsyfE</t>
+          <t>https://www.youtube.com/watch?v=mAKOqFt-LVQ</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>The Trip</t>
+          <t>23 000 Lives</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2693,34 +2693,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>home/07-13-2026/The Trip.jpg</t>
+          <t>home/07-20-2026/23 000 Lives.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=K9bPJmy68Rs</t>
+          <t>https://www.youtube.com/watch?v=89dugTvBEWw</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Hollow Man 2</t>
+          <t>Chithini</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2728,17 +2728,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Hollow Man 2.jpg</t>
+          <t>home/07-20-2026/Chithini.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=koZuEDeQf3Q</t>
+          <t>https://www.youtube.com/watch?v=pRbfgUVGAJg</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -2780,17 +2780,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Only the Brave</t>
+          <t>Ikka</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Only the Brave.jpg</t>
+          <t>home/07-13-2026/Ikka.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EE_GY6zccqc</t>
+          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2815,7 +2815,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Dhamaal 4</t>
+          <t>Mukhbir: The Story of a Spy</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Dhamaal 4.jpg</t>
+          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IG-eByZdz6Y</t>
+          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2850,7 +2850,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ikka</t>
+          <t>Tholaivil Oru Kadhal</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Ikka.jpg</t>
+          <t>home/07-13-2026/Tholaivil Oru Kadhal.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
+          <t>https://www.youtube.com/watch?v=bR1s6WIsyfE</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2885,17 +2885,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mukhbir: The Story of a Spy</t>
+          <t>The Trip</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
+          <t>home/07-13-2026/The Trip.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
+          <t>https://www.youtube.com/watch?v=K9bPJmy68Rs</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2920,17 +2920,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Shikhandi</t>
+          <t>Hollow Man 2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Shikhandi.jpg</t>
+          <t>home/07-13-2026/Hollow Man 2.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vLuLhH7oREY</t>
+          <t>https://www.youtube.com/watch?v=koZuEDeQf3Q</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2955,7 +2955,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Lenin</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2973,34 +2973,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-13-2026/Lenin.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Only the Brave</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3008,24 +3008,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/Only the Brave.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=EE_GY6zccqc</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Dhamaal 4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3043,24 +3043,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-13-2026/Dhamaal 4.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=IG-eByZdz6Y</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Ikka</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3078,24 +3078,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-13-2026/Ikka.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Mukhbir: The Story of a Spy</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3113,24 +3113,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Shikhandi</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3148,24 +3148,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-13-2026/Shikhandi.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=vLuLhH7oREY</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3200,7 +3200,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Pati Patni Aur Woh Do</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Pati Patni Aur Woh Do.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ceooxuS-sww</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3270,7 +3270,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3305,7 +3305,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3375,7 +3375,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3410,7 +3410,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Pati Patni Aur Woh Do</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-09-2026/Pati Patni Aur Woh Do.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=ceooxuS-sww</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3445,7 +3445,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3480,7 +3480,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3515,7 +3515,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Nagabandham</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3533,24 +3533,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Nagabandham.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Chand Mera Dil</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3568,24 +3568,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Chand Mera Dil.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rRQ8oKCoYrQ</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Kotha Malupu</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3603,24 +3603,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Kotha Malupu.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qnd1Xwv9NP8</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Double Barrel</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3638,24 +3638,24 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Double Barrel.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Ij0mjRt1QIA</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Nagabandham</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3673,24 +3673,24 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Nagabandham.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3700,7 +3700,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3708,24 +3708,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3743,24 +3743,24 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Chand Mera Dil</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3778,24 +3778,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-06-2026/Chand Mera Dil.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=rRQ8oKCoYrQ</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Kotha Malupu</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3813,24 +3813,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-06-2026/Kotha Malupu.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=qnd1Xwv9NP8</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Double Barrel</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3848,24 +3848,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-06-2026/Double Barrel.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=Ij0mjRt1QIA</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3883,24 +3883,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3918,24 +3918,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Alpha.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Pritam and Pedro Season 1</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3953,24 +3953,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Charukesi</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Charukesi.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4005,7 +4005,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4040,7 +4040,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Daadi Ki Shaadi</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4075,7 +4075,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Hangman</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Hangman.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4110,7 +4110,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Alpha</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-03-2026/Alpha.jpg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4145,7 +4145,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Pritam and Pedro Season 1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4180,7 +4180,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Charukesi</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-03-2026/Charukesi.jpg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4215,7 +4215,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4250,7 +4250,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Daadi Ki Shaadi</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4285,7 +4285,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Hangman</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4303,24 +4303,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-03-2026/Hangman.jpg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4338,24 +4338,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4373,24 +4373,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4408,34 +4408,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Bossa Nova</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4443,24 +4443,24 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Bossa Nova.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Super Dog and Super Cat</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4478,24 +4478,24 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
+          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4513,24 +4513,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4548,24 +4548,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Elra Kaaleliyatte Kaala</t>
+          <t>Super Subbu Season 1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4583,24 +4583,24 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
+          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
+          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Hunting Jessica Brok</t>
+          <t>Isakapatnam Season 1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4618,34 +4618,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
+          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
+          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Obsession</t>
+          <t>Bossa Nova</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>English</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4653,34 +4653,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Obsession.jpg</t>
+          <t>home/07-02-2026/Bossa Nova.jpg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
+          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Continental Split</t>
+          <t>Super Dog and Super Cat</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4688,34 +4688,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Continental Split.jpg</t>
+          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
+          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Great White Waters</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4723,12 +4723,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Great White Waters.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4740,17 +4740,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Road Wars: Max Fury</t>
+          <t>Enola Holmes 3</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4758,12 +4758,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
+          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
+          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4775,7 +4775,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Supergirl</t>
+          <t>Elra Kaaleliyatte Kaala</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4793,12 +4793,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Supergirl.jpg</t>
+          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
+          <t>https://www.youtube.com/watch?v=-orG1Tkpgko</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -4810,12 +4810,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>The Last Breath</t>
+          <t>Hunting Jessica Brok</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Last Breath.jpg</t>
+          <t>home/07-01-2026/Hunting Jessica Brok.jpg</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
+          <t>https://www.youtube.com/watch?v=QTstODhLads</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -4845,7 +4845,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Little Brother</t>
+          <t>Obsession</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>English</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Little Brother.jpg</t>
+          <t>home/07-01-2026/Obsession.jpg</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
+          <t>https://www.youtube.com/watch?v=t-5a_Y-lFPU</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -4880,17 +4880,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Continental Split</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
+          <t>home/07-01-2026/Continental Split.jpg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
+          <t>https://www.youtube.com/watch?v=OMOaeA6AzSc</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4915,17 +4915,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>The Yeti</t>
+          <t>Great White Waters</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4933,12 +4933,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>home/07-01-2026/The Yeti.jpg</t>
+          <t>home/07-01-2026/Great White Waters.jpg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
+          <t>https://www.youtube.com/watch?v=lsAHdAAU9wg</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4950,17 +4950,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>Road Wars: Max Fury</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4968,24 +4968,24 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-01-2026/Road Wars Max Fury.jpg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=z5HpCIJQ4rI</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Supergirl</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5003,34 +5003,34 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/07-01-2026/Supergirl.jpg</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=rKW50w6i9HI</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Lingam Season 1</t>
+          <t>The Last Breath</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5038,24 +5038,24 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Lingam Season 1.jpg</t>
+          <t>home/07-01-2026/The Last Breath.jpg</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
+          <t>https://www.youtube.com/watch?v=RbPA9F9BmDA</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Moondram Kan</t>
+          <t>Little Brother</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5073,24 +5073,24 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Moondram Kan.jpg</t>
+          <t>home/07-01-2026/Little Brother.jpg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
+          <t>https://www.youtube.com/watch?v=bWtrFcerKE0</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Raja Shivaji</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5108,24 +5108,24 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Raja Shivaji.jpg</t>
+          <t>home/07-01-2026/Welcome to the Jungle.jpg</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
+          <t>https://www.youtube.com/watch?v=R704yP3dlXw</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Dooradarshini</t>
+          <t>The Yeti</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5143,24 +5143,24 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Dooradarshini.jpg</t>
+          <t>home/07-01-2026/The Yeti.jpg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
+          <t>https://www.youtube.com/watch?v=lI3A9sDAaqY</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Revolver Rinko</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>home/06-25-2026/Revolver Rinko.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5195,7 +5195,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>In the Hand of Dante</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5230,7 +5230,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Maa Inti Bangaaram</t>
+          <t>Lingam Season 1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5248,24 +5248,24 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
+          <t>home/06-25-2026/Lingam Season 1.jpg</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
+          <t>https://www.youtube.com/watch?v=EOB0Ypf9DYY</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Deewana</t>
+          <t>Moondram Kan</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5283,24 +5283,24 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Deewana.jpg</t>
+          <t>home/06-25-2026/Moondram Kan.jpg</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
+          <t>https://www.youtube.com/watch?v=cUtwr5E4gZc</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Vanda Devullu</t>
+          <t>Raja Shivaji</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5318,24 +5318,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Vanda Devullu.jpg</t>
+          <t>home/06-25-2026/Raja Shivaji.jpg</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
+          <t>https://www.youtube.com/watch?v=Bgy00eaFyhE</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>Dooradarshini</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5353,24 +5353,24 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-25-2026/Dooradarshini.jpg</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=9rgcKPWK0A4</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>M4M: Motive for Murder</t>
+          <t>Revolver Rinko</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5388,24 +5388,24 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
+          <t>home/06-25-2026/Revolver Rinko.jpg</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
+          <t>https://www.youtube.com/watch?v=yktB0FrgC3c</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Blast</t>
+          <t>In the Hand of Dante</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5423,34 +5423,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blast.jpg</t>
+          <t>home/06-25-2026/In the Hand of Dante.jpg</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
+          <t>https://www.youtube.com/watch?v=cXA3Zgsky18</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Avatar: Fire and Ash</t>
+          <t>Maa Inti Bangaaram</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
+          <t>home/06-24-2026/Maa Inti Bangaaram.jpg</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
+          <t>https://www.youtube.com/watch?v=B9d-wISnm8s</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -5475,7 +5475,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>The Sheep Detectives</t>
+          <t>Deewana</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
+          <t>home/06-24-2026/Deewana.jpg</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
+          <t>https://www.youtube.com/watch?v=f-ok5QZNGVc</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -5510,17 +5510,17 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Gladiator Underground</t>
+          <t>Vanda Devullu</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Gladiator Underground.jpg</t>
+          <t>home/06-24-2026/Vanda Devullu.jpg</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
+          <t>https://www.youtube.com/watch?v=KL8GfzfiH2s</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5580,7 +5580,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Breakfast</t>
+          <t>M4M: Motive for Murder</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Breakfast.jpg</t>
+          <t>home/06-24-2026/M4M Motive for Murder.jpg</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
+          <t>https://www.youtube.com/watch?v=8cFotZMVw60</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5615,7 +5615,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Painkili</t>
+          <t>Blast</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Painkili.jpg</t>
+          <t>home/06-24-2026/Blast.jpg</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
+          <t>https://www.youtube.com/watch?v=aM5OLvxFBO4</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5650,12 +5650,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Seems Like Old Times</t>
+          <t>Avatar: Fire and Ash</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
+          <t>home/06-24-2026/Avatar Fire and Ash.jpg</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
+          <t>https://www.youtube.com/watch?v=nb_fFj_0rq8</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5685,17 +5685,17 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>The Furies</t>
+          <t>The Sheep Detectives</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>home/06-24-2026/The Furies.jpg</t>
+          <t>home/06-24-2026/The Sheep Detectives.jpg</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
+          <t>https://www.youtube.com/watch?v=pyZI5oM6hWk</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5720,17 +5720,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Garbham</t>
+          <t>Gladiator Underground</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Garbham.jpg</t>
+          <t>home/06-24-2026/Gladiator Underground.jpg</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
+          <t>https://www.youtube.com/watch?v=1ssNi5j32cU</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5755,17 +5755,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Blind Waters</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Tamil Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>home/06-24-2026/Blind Waters.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5790,7 +5790,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Drishyam 3</t>
+          <t>Breakfast</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5808,24 +5808,24 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Drishyam 3.jpg</t>
+          <t>home/06-24-2026/Breakfast.jpg</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
+          <t>https://www.youtube.com/watch?v=IB2D2cl3fEE</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Painkili</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5843,34 +5843,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-24-2026/Painkili.jpg</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=zN2ris5E_qc</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Seems Like Old Times</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5878,34 +5878,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-24-2026/Seems Like Old Times.jpg</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=kw9TPR93kPk</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>The Furies</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5913,24 +5913,24 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/The Furies.jpg</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=lRwNFNNNTC0</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Thank You Subbarao</t>
+          <t>Garbham</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5948,34 +5948,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
+          <t>home/06-24-2026/Garbham.jpg</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
+          <t>https://www.youtube.com/watch?v=j2G8FlUiXLs</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Blind Waters</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5983,17 +5983,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-24-2026/Blind Waters.jpg</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
+          <t>https://www.youtube.com/watch?v=g7vcFjjo474</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6035,7 +6035,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Husbands in Action</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Husbands in Action.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -6070,7 +6070,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Cocktail 2</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Cocktail 2.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -6105,7 +6105,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6140,7 +6140,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Voicemails for Isabelle</t>
+          <t>Thank You Subbarao</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
+          <t>home/06-19-2026/Thank You Subbarao.jpg</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
+          <t>https://www.youtube.com/watch?v=1MXKjHJUyfQ</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6175,7 +6175,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Anali</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6193,12 +6193,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Anali.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
+          <t>https://www.youtube.com/watch?v=syBtRf69q6s</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -6210,7 +6210,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Save The Tigers Season 3</t>
+          <t>Drishyam 3</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
+          <t>home/06-19-2026/Drishyam 3.jpg</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
+          <t>https://www.youtube.com/watch?v=07h9Y1XKBWI</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -6245,7 +6245,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Razor</t>
+          <t>Husbands in Action</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Razor.jpg</t>
+          <t>home/06-19-2026/Husbands in Action.jpg</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
+          <t>https://www.youtube.com/watch?v=PSJgwm2xcbI</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -6280,17 +6280,17 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>The Grey Men 2</t>
+          <t>Cocktail 2</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>home/06-19-2026/The Grey Men 2.jpg</t>
+          <t>home/06-19-2026/Cocktail 2.jpg</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
+          <t>https://www.youtube.com/watch?v=XXxUqLHq1xg</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -6315,7 +6315,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6333,12 +6333,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -6350,7 +6350,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Athiradi</t>
+          <t>Voicemails for Isabelle</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Athiradi.jpg</t>
+          <t>home/06-19-2026/Voicemails for Isabelle.jpg</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
+          <t>https://www.youtube.com/watch?v=9mi3YVYm3ZU</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -6385,7 +6385,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Mareechika</t>
+          <t>Anali</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mareechika.jpg</t>
+          <t>home/06-19-2026/Anali.jpg</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
+          <t>https://www.youtube.com/watch?v=h6-GMidsxjw</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -6420,7 +6420,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Mortal Kombat 2</t>
+          <t>Save The Tigers Season 3</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
+          <t>home/06-19-2026/Save The Tigers Season 3.jpg</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
+          <t>https://www.youtube.com/watch?v=wob0NDMQqGY</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -6455,7 +6455,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Razor</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6473,34 +6473,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-19-2026/Razor.jpg</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=B8U25waRtfQ</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>The Grey Men 2</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6508,24 +6508,24 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-19-2026/The Grey Men 2.jpg</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=u_E-pQ56Vm4</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Veerabhadrudu</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6543,24 +6543,24 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Athiradi</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6578,24 +6578,24 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Athiradi.jpg</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=NFZmwmAZqXE</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Sattendru Maarudhu Vaanilai</t>
+          <t>Mareechika</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6613,24 +6613,24 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
+          <t>home/06-19-2026/Mareechika.jpg</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
+          <t>https://www.youtube.com/watch?v=kCaQSTaqqgI</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>Mortal Kombat 2</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6648,34 +6648,34 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-19-2026/Mortal Kombat 2.jpg</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=ZdC5mFHPldg</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Pongala</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Pongala.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -6700,7 +6700,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Shelter</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Shelter.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -6735,7 +6735,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Whistle</t>
+          <t>Veerabhadrudu</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Whistle.jpg</t>
+          <t>home/06-16-2026/Veerabhadrudu.jpg</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
+          <t>https://www.youtube.com/watch?v=vH0Q5t_JUng</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -6770,7 +6770,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6788,12 +6788,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -6805,7 +6805,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Kenatha Kanom</t>
+          <t>Sattendru Maarudhu Vaanilai</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6823,12 +6823,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
+          <t>home/06-16-2026/Sattendru Maarudhu Vaanilai.jpg</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
+          <t>https://www.youtube.com/watch?v=Lbxw9Q3YmMw</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -6840,17 +6840,17 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>The Deep</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6858,12 +6858,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>home/06-16-2026/The Deep.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -6875,17 +6875,17 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Seven Years in Tibet</t>
+          <t>Pongala</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6893,12 +6893,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
+          <t>home/06-16-2026/Pongala.jpg</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
+          <t>https://www.youtube.com/watch?v=CDjL0lbpr40</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -6910,7 +6910,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Kolahalamedu</t>
+          <t>Shelter</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Kolahalamedu.jpg</t>
+          <t>home/06-16-2026/Shelter.jpg</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
+          <t>https://www.youtube.com/watch?v=whOG1iwBGnM</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -6945,7 +6945,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Whistle</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Normal.jpg</t>
+          <t>home/06-16-2026/Whistle.jpg</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
+          <t>https://www.youtube.com/watch?v=a6gxDFGte5M</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -6980,7 +6980,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Sing Geetham</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sing Geetham.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -7015,7 +7015,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Vikalpa</t>
+          <t>Kenatha Kanom</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -7025,7 +7025,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Vikalpa.jpg</t>
+          <t>home/06-16-2026/Kenatha Kanom.jpg</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
+          <t>https://www.youtube.com/watch?v=-qogxgbsxOQ</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -7050,17 +7050,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Dridam</t>
+          <t>The Deep</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Dridam.jpg</t>
+          <t>home/06-16-2026/The Deep.jpg</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
+          <t>https://www.youtube.com/watch?v=qqdagoaQM7w</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -7085,17 +7085,17 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Karuppu</t>
+          <t>Seven Years in Tibet</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Karuppu.jpg</t>
+          <t>home/06-16-2026/Seven Years in Tibet.jpg</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
+          <t>https://www.youtube.com/watch?v=m9a_7WFcPlI</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Sshhh Season 3</t>
+          <t>Kolahalamedu</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
+          <t>home/06-16-2026/Kolahalamedu.jpg</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
+          <t>https://www.youtube.com/watch?v=431lKAQyxd0</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -7155,7 +7155,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>R.L. Stine’s Pumpkinhead</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
+          <t>home/06-16-2026/Normal.jpg</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
+          <t>https://www.youtube.com/watch?v=aGdWT9_cEQY</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -7190,7 +7190,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Peddi</t>
+          <t>Sing Geetham</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -7208,24 +7208,24 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peddi.jpg</t>
+          <t>home/06-16-2026/Sing Geetham.jpg</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
+          <t>https://www.youtube.com/watch?v=8CzkA3WXjtQ</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Vikalpa</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7243,24 +7243,24 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-16-2026/Vikalpa.jpg</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=9Jysx8EdZKM</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Dridam</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7278,24 +7278,24 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-16-2026/Dridam.jpg</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=AiFCD2aSnlc</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Karuppu</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7313,24 +7313,24 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-16-2026/Karuppu.jpg</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=JpVl_-1YgIo</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Sshhh Season 3</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -7348,24 +7348,24 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-16-2026/Sshhh Season 3.jpg</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=92eqbag5gRU</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>R.L. Stine’s Pumpkinhead</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7375,7 +7375,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7383,24 +7383,24 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-16-2026/R.L. Stine’s Pumpkinhead.jpg</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=gqmrfVrPJlY</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Godari Gattupaina</t>
+          <t>Peddi</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
+          <t>home/06-06-2026/Peddi.jpg</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
+          <t>https://www.youtube.com/watch?v=sF2dj7ycZvA</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -7435,7 +7435,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Trikala: Script of God</t>
+          <t>Ugly Story</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Trikala Script of God.jpg</t>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -7470,7 +7470,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/29.jpg</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -7505,7 +7505,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Sukhamano Sukhamann</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -7540,7 +7540,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Carmeni Selvam</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -7575,7 +7575,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Blast Zone</t>
+          <t>The Rise of Ashoka</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Blast Zone.jpg</t>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -7610,7 +7610,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Maa Behen</t>
+          <t>Godari Gattupaina</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Maa Behen.jpg</t>
+          <t>home/06-06-2026/Godari Gattupaina.jpg</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
+          <t>https://www.youtube.com/watch?v=Q2ea_B_Y67M</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -7645,7 +7645,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Kattalan</t>
+          <t>Trikala: Script of God</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7663,12 +7663,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kattalan.jpg</t>
+          <t>home/06-06-2026/Trikala Script of God.jpg</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
+          <t>https://www.youtube.com/watch?v=U098Oyg8nYo</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -7680,7 +7680,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Ramani Kalyanam</t>
+          <t>Patriot</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
+          <t>home/06-06-2026/Patriot.jpg</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -7715,17 +7715,17 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Beast of War</t>
+          <t>Sukhamano Sukhamann</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Beast of War.jpg</t>
+          <t>home/06-06-2026/Sukhamano Sukhamann.jpg</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
+          <t>https://www.youtube.com/watch?v=YiYDvpWNK3o</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -7750,7 +7750,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Sandigdham</t>
+          <t>Carmeni Selvam</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Sandigdham.jpg</t>
+          <t>home/06-06-2026/Carmeni Selvam.jpg</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
+          <t>https://www.youtube.com/watch?v=W4BLjlRo4Bs</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -7785,7 +7785,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Blast Zone</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Kara.jpg</t>
+          <t>home/06-06-2026/Blast Zone.jpg</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
+          <t>https://www.youtube.com/watch?v=_vbRwxitX2o</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -7820,7 +7820,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>KD: The Devil</t>
+          <t>Maa Behen</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -7830,7 +7830,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>home/06-06-2026/KD The Devil.jpg</t>
+          <t>home/06-06-2026/Maa Behen.jpg</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
+          <t>https://www.youtube.com/watch?v=xYbLpsEhcfA</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -7855,7 +7855,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Purushaha</t>
+          <t>Kattalan</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Purushaha.jpg</t>
+          <t>home/06-06-2026/Kattalan.jpg</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
+          <t>https://www.youtube.com/watch?v=iQMvxXmCk9I</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -7890,7 +7890,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Hai Jawani Toh Ishq Hona Hai</t>
+          <t>Ramani Kalyanam</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
+          <t>home/06-06-2026/Ramani Kalyanam.jpg</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
+          <t>https://www.youtube.com/watch?v=Iax6gOtJSw4</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -7925,12 +7925,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Summer House</t>
+          <t>Beast of War</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Summer House.jpg</t>
+          <t>home/06-06-2026/Beast of War.jpg</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
+          <t>https://www.youtube.com/watch?v=x4Dk6joTDRg</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -7960,7 +7960,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Patriot</t>
+          <t>Sandigdham</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Patriot.jpg</t>
+          <t>home/06-06-2026/Sandigdham.jpg</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+          <t>https://www.youtube.com/watch?v=wTYXAINrYkw</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -7995,7 +7995,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Juniors Journey</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Juniors Journey.jpg</t>
+          <t>home/06-06-2026/Kara.jpg</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
+          <t>https://www.youtube.com/watch?v=xkQS_TET5NI</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -8030,7 +8030,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Ginny Weds Sunny 2</t>
+          <t>KD: The Devil</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
+          <t>home/06-06-2026/KD The Devil.jpg</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
+          <t>https://www.youtube.com/watch?v=yQLKrS5N4KU</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -8065,7 +8065,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Purushaha</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Peter.jpg</t>
+          <t>home/06-06-2026/Purushaha.jpg</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+          <t>https://www.youtube.com/watch?v=xs_NcJrsVy8</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -8100,7 +8100,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Hai Jawani Toh Ishq Hona Hai</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8118,12 +8118,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Hai Jawani Toh Ishq Hona Hai.jpg</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=rFOdIv1jwhc</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -8135,7 +8135,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>Summer House</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>home/06-06-2026/29.jpg</t>
+          <t>home/06-06-2026/Summer House.jpg</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+          <t>https://www.youtube.com/watch?v=9wGlGOhyLZk</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -8180,7 +8180,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8205,7 +8205,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Ugly Story</t>
+          <t>Juniors Journey</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>home/06-06-2026/Ugly Story.jpg</t>
+          <t>home/06-06-2026/Juniors Journey.jpg</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+          <t>https://www.youtube.com/watch?v=uWgcpFbSnz8</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -8240,7 +8240,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>The Rise of Ashoka</t>
+          <t>Ginny Weds Sunny 2</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+          <t>home/06-06-2026/Ginny Weds Sunny 2.jpg</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+          <t>https://www.youtube.com/watch?v=NO7OOWCWmM0</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -8275,33 +8275,243 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
+          <t>Peter</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>1</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Peter.jpg</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=y25zcSqAdVs</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>1</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>1</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/29.jpg</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=BwnSbiNMe60</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Patriot</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>1</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Patriot.jpg</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=XTc2dLAgABI</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Ugly Story</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>1</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/Ugly Story.jpg</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=7hLQtxlhmeM</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>The Rise of Ashoka</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>1</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>home/06-06-2026/The Rise of Ashoka.jpg</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=k4X8z0hWQ4I</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
           <t>Office Romance</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
         <is>
           <t>Telugu Dubbed</t>
         </is>
       </c>
-      <c r="D225" t="n">
-        <v>1</v>
-      </c>
-      <c r="E225" t="inlineStr">
+      <c r="D231" t="n">
+        <v>1</v>
+      </c>
+      <c r="E231" t="inlineStr">
         <is>
           <t>home/06-06-2026/Office Romance.jpg</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
+      <c r="F231" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=M7KrcId8LQg</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
+      <c r="G231" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
@@ -8318,7 +8528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8340,150 +8550,160 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B17" t="n">
         <v>32</v>
       </c>
     </row>

--- a/output/home.xlsx
+++ b/output/home.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G231"/>
+  <dimension ref="A1:G253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Korean Kanakaraju</t>
+          <t>Snake 5: Monster City</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -488,34 +488,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>home/08-10-2026/Korean Kanakaraju.jpg</t>
+          <t>home/08-20-2026/Snake 5 Monster City.jpg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JIqKjjTfOxM</t>
+          <t>https://www.youtube.com/watch?v=JowF3hTYces</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Ghost in the Shell</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -523,34 +523,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>home/08-10-2026/DC.jpg</t>
+          <t>home/08-20-2026/Ghost in the Shell.jpg</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2kntxizQIFI</t>
+          <t>https://www.youtube.com/watch?v=tRkb1X9ovI4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Korean Kanakaraju</t>
+          <t>Insidious: The Red Door</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -558,34 +558,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>home/08-10-2026/Korean Kanakaraju.jpg</t>
+          <t>home/08-20-2026/Insidious The Red Door.jpg</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=JIqKjjTfOxM</t>
+          <t>https://www.youtube.com/watch?v=ZuQuOnYnr3Q</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nizhal</t>
+          <t>Insidious: The Last Key</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -593,24 +593,24 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>home/08-10-2026/Nizhal.jpg</t>
+          <t>home/08-20-2026/Insidious The Last Key.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=yqgTPndvRXo</t>
+          <t>https://www.youtube.com/watch?v=acQyrwQyCOk</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Moda Kavida Vatavarana</t>
+          <t>Agadha</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -628,24 +628,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>home/08-10-2026/Moda Kavida Vatavarana.jpg</t>
+          <t>home/08-19-2026/Agadha.jpg</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=0RuXnzkjAtU</t>
+          <t>https://www.youtube.com/watch?v=LHxKhCcMFl8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>Hushar Pittalu</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -663,24 +663,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>home/08-10-2026/DC.jpg</t>
+          <t>home/08-19-2026/Hushar Pittalu.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2kntxizQIFI</t>
+          <t>https://www.youtube.com/watch?v=Lpzh4JPRD9Q</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oh Sukumari</t>
+          <t>Heartin</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -698,24 +698,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Oh Sukumari.jpg</t>
+          <t>home/08-19-2026/Heartin.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TL0-kMdqt_s</t>
+          <t>https://www.youtube.com/watch?v=83QUpVbaeHM</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M.R.P – Neekentha Naakentha</t>
+          <t>Forest Guard</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -733,24 +733,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>home/08-07-2026/M.R.P – Neekentha Naakentha.jpg</t>
+          <t>home/08-19-2026/Forest Guard.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vaXa2-WIBE0</t>
+          <t>https://www.youtube.com/watch?v=GiO4mMFEd4A</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Uyir</t>
+          <t>Mr. Work from Home</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -768,24 +768,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Uyir.jpg</t>
+          <t>home/08-19-2026/Mr. Work from Home.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DyTziQOTNK4</t>
+          <t>https://www.youtube.com/watch?v=850mw3ETSgQ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Operation Safed Sagar Season 1</t>
+          <t>Achyuta Avataaram</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -803,24 +803,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Operation Safed Sagar Season 1.jpg</t>
+          <t>home/08-19-2026/Achyuta Avataaram.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=eFwHqth3i1Y</t>
+          <t>https://www.youtube.com/watch?v=S75v8woMc-I</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Second Case Of Seetharam</t>
+          <t>Aroopi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -838,24 +838,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Second Case Of Seetharam.jpg</t>
+          <t>home/08-19-2026/Aroopi.jpg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=t7fvUNU7lnk</t>
+          <t>https://www.youtube.com/watch?v=8CsDfDLqCDA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Vadhandhi Season 2</t>
+          <t>Minions and Monsters</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -873,34 +873,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Vadhandhi Season 2.jpg</t>
+          <t>home/08-19-2026/Minions and Monsters.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7cCI3G8XmH8</t>
+          <t>https://www.youtube.com/watch?v=ZSdOwt-G49w</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Geetha Sakshiga</t>
+          <t>Stolen Girl</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -908,24 +908,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Geetha Sakshiga.jpg</t>
+          <t>home/08-19-2026/Stolen Girl.jpg</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Md37YuwURBI</t>
+          <t>https://www.youtube.com/watch?v=V4bQuYwFtOQ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mahabali 1980’s</t>
+          <t>Hushar Pittalu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -943,24 +943,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Mahabali 1980’s.jpg</t>
+          <t>home/08-19-2026/Hushar Pittalu.jpg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1NKlkWQi4rM</t>
+          <t>https://www.youtube.com/watch?v=ak_46UsN_6k</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Uyir</t>
+          <t>Heartin</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -978,24 +978,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Uyir.jpg</t>
+          <t>home/08-19-2026/Heartin.jpg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DyTziQOTNK4</t>
+          <t>https://www.youtube.com/watch?v=83QUpVbaeHM</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>The Last House</t>
+          <t>Forest Guard</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1013,24 +1013,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>home/08-07-2026/The Last House.jpg</t>
+          <t>home/08-19-2026/Forest Guard.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=MLxgaz2Zp1k</t>
+          <t>https://www.youtube.com/watch?v=GiO4mMFEd4A</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Operation Safed Sagar Season 1</t>
+          <t>Agadha</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1048,34 +1048,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Operation Safed Sagar Season 1.jpg</t>
+          <t>home/08-19-2026/Agadha.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=eFwHqth3i1Y</t>
+          <t>https://www.youtube.com/watch?v=LHxKhCcMFl8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Maggi Pusthaka</t>
+          <t>Interstellar</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Tamil Dubbed</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1083,24 +1083,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Maggi Pusthaka.jpg</t>
+          <t>home/08-19-2026/Interstellar.jpg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=APr2T-qgoRc</t>
+          <t>https://www.youtube.com/watch?v=2LqzF5WauAw</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sathyathil Sambhavichathu</t>
+          <t>The Death of Robin Hood</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1118,24 +1118,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Sathyathil Sambhavichathu.jpg</t>
+          <t>home/08-19-2026/The Death of Robin Hood.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_rO-Fw0TBos</t>
+          <t>https://www.youtube.com/watch?v=tlSDDuWxO_0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>The Super Mario Galaxy Movie</t>
+          <t>Euphoria</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1153,24 +1153,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>home/08-07-2026/The Super Mario Galaxy Movie.jpg</t>
+          <t>home/08-19-2026/Euphoria.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=FdL2GorGdKc</t>
+          <t>https://www.youtube.com/watch?v=C4C0O4lv7ro</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M.R.P – Neekentha Naakentha</t>
+          <t>Awarapan 2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1188,34 +1188,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>home/08-07-2026/M.R.P – Neekentha Naakentha.jpg</t>
+          <t>home/08-19-2026/Awarapan 2.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vaXa2-WIBE0</t>
+          <t>https://www.youtube.com/watch?v=qkaSXCqdecM</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Oh Sukumari</t>
+          <t>To the Max</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1223,24 +1223,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Oh Sukumari.jpg</t>
+          <t>home/08-19-2026/To the Max.jpg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TL0-kMdqt_s</t>
+          <t>https://www.youtube.com/watch?v=WXNUynl-hX8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Main Vaapas Aaunga</t>
+          <t>Korean Kanakaraju</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1258,24 +1258,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Main Vaapas Aaunga.jpg</t>
+          <t>home/08-10-2026/Korean Kanakaraju.jpg</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PRUTWluKRW8</t>
+          <t>https://www.youtube.com/watch?v=JIqKjjTfOxM</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Idhayam Murali</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1293,24 +1293,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Idhayam Murali.jpg</t>
+          <t>home/08-10-2026/DC.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lfoQfD0AjTs</t>
+          <t>https://www.youtube.com/watch?v=2kntxizQIFI</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vadhandhi Season 2</t>
+          <t>Korean Kanakaraju</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1328,24 +1328,24 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Vadhandhi Season 2.jpg</t>
+          <t>home/08-10-2026/Korean Kanakaraju.jpg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7cCI3G8XmH8</t>
+          <t>https://www.youtube.com/watch?v=JIqKjjTfOxM</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Oh Sukumari</t>
+          <t>Nizhal</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1363,24 +1363,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>home/08-07-2026/Oh Sukumari.jpg</t>
+          <t>home/08-10-2026/Nizhal.jpg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TL0-kMdqt_s</t>
+          <t>https://www.youtube.com/watch?v=yqgTPndvRXo</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Chennai Love Story</t>
+          <t>Moda Kavida Vatavarana</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1398,24 +1398,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Chennai Love Story.jpg</t>
+          <t>home/08-10-2026/Moda Kavida Vatavarana.jpg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=nYYjR9diizE</t>
+          <t>https://www.youtube.com/watch?v=0RuXnzkjAtU</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Srinivasa Mangapuram</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1433,24 +1433,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Srinivasa Mangapuram.jpg</t>
+          <t>home/08-10-2026/DC.jpg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kKIqF2oyj1Q</t>
+          <t>https://www.youtube.com/watch?v=2kntxizQIFI</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jana Nayakudu</t>
+          <t>Oh Sukumari</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1468,24 +1468,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Jana Nayakudu.jpg</t>
+          <t>home/08-07-2026/Oh Sukumari.jpg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=L81nWRwRmnI</t>
+          <t>https://www.youtube.com/watch?v=TL0-kMdqt_s</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gatta Kusthi 2</t>
+          <t>M.R.P – Neekentha Naakentha</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1503,24 +1503,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
+          <t>home/08-07-2026/M.R.P – Neekentha Naakentha.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
+          <t>https://www.youtube.com/watch?v=vaXa2-WIBE0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Police Complaint</t>
+          <t>Uyir</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1538,24 +1538,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Police Complaint.jpg</t>
+          <t>home/08-07-2026/Uyir.jpg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=87aOxmtPmX0</t>
+          <t>https://www.youtube.com/watch?v=DyTziQOTNK4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Love Oh Love</t>
+          <t>Operation Safed Sagar Season 1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1573,24 +1573,24 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Love Oh Love.jpg</t>
+          <t>home/08-07-2026/Operation Safed Sagar Season 1.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ikZoI6wmvBQ</t>
+          <t>https://www.youtube.com/watch?v=eFwHqth3i1Y</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Balan</t>
+          <t>Second Case Of Seetharam</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1608,24 +1608,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Balan.jpg</t>
+          <t>home/08-07-2026/Second Case Of Seetharam.jpg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cjWTqndgZ_M</t>
+          <t>https://www.youtube.com/watch?v=t7fvUNU7lnk</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Objection My Lord Season 1</t>
+          <t>Vadhandhi Season 2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Objection My Lord Season 1.jpg</t>
+          <t>home/08-07-2026/Vadhandhi Season 2.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Fhr9JdlLRwY</t>
+          <t>https://www.youtube.com/watch?v=7cCI3G8XmH8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Con City</t>
+          <t>Geetha Sakshiga</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1678,24 +1678,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Con City.jpg</t>
+          <t>home/08-07-2026/Geetha Sakshiga.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=wT2VV6bq6hU</t>
+          <t>https://www.youtube.com/watch?v=Md37YuwURBI</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pallichattambi</t>
+          <t>Mahabali 1980’s</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1713,24 +1713,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Pallichattambi.jpg</t>
+          <t>home/08-07-2026/Mahabali 1980’s.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=k6WQlVFkvgg</t>
+          <t>https://www.youtube.com/watch?v=1NKlkWQi4rM</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Chinna Chinna Aasai</t>
+          <t>Uyir</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1748,24 +1748,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Chinna Chinna Aasai.jpg</t>
+          <t>home/08-07-2026/Uyir.jpg</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f_mCvoMgoYs</t>
+          <t>https://www.youtube.com/watch?v=DyTziQOTNK4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Balan</t>
+          <t>The Last House</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Balan.jpg</t>
+          <t>home/08-07-2026/The Last House.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cjWTqndgZ_M</t>
+          <t>https://www.youtube.com/watch?v=MLxgaz2Zp1k</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Spider-Man: Brand New Day</t>
+          <t>Operation Safed Sagar Season 1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1818,24 +1818,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Spider-Man Brand New Day.jpg</t>
+          <t>home/08-07-2026/Operation Safed Sagar Season 1.jpg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=62bIsvRcPv0</t>
+          <t>https://www.youtube.com/watch?v=eFwHqth3i1Y</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Objection My Lord Season 1</t>
+          <t>Maggi Pusthaka</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1853,24 +1853,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Objection My Lord Season 1.jpg</t>
+          <t>home/08-07-2026/Maggi Pusthaka.jpg</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Fhr9JdlLRwY</t>
+          <t>https://www.youtube.com/watch?v=APr2T-qgoRc</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Srinivasa Mangapuram</t>
+          <t>Sathyathil Sambhavichathu</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1888,24 +1888,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Srinivasa Mangapuram.jpg</t>
+          <t>home/08-07-2026/Sathyathil Sambhavichathu.jpg</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=kKIqF2oyj1Q</t>
+          <t>https://www.youtube.com/watch?v=_rO-Fw0TBos</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Son of Sara: Volume 1</t>
+          <t>The Super Mario Galaxy Movie</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1923,24 +1923,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Son of Sara Volume 1.jpg</t>
+          <t>home/08-07-2026/The Super Mario Galaxy Movie.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ZTkXpVGpcRk</t>
+          <t>https://www.youtube.com/watch?v=FdL2GorGdKc</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Police Complaint</t>
+          <t>M.R.P – Neekentha Naakentha</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1958,24 +1958,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Police Complaint.jpg</t>
+          <t>home/08-07-2026/M.R.P – Neekentha Naakentha.jpg</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=-q63oK7GhI0</t>
+          <t>https://www.youtube.com/watch?v=vaXa2-WIBE0</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chum</t>
+          <t>Oh Sukumari</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1993,24 +1993,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Chum.jpg</t>
+          <t>home/08-07-2026/Oh Sukumari.jpg</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=VUdPlZgXOjE</t>
+          <t>https://www.youtube.com/watch?v=TL0-kMdqt_s</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Gatta Kusthi 2</t>
+          <t>Main Vaapas Aaunga</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2028,24 +2028,24 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
+          <t>home/08-07-2026/Main Vaapas Aaunga.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
+          <t>https://www.youtube.com/watch?v=PRUTWluKRW8</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Gatta Kusthi 2</t>
+          <t>Idhayam Murali</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2063,24 +2063,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
+          <t>home/08-07-2026/Idhayam Murali.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
+          <t>https://www.youtube.com/watch?v=lfoQfD0AjTs</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Love Oh Love</t>
+          <t>Vadhandhi Season 2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2098,24 +2098,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Love Oh Love.jpg</t>
+          <t>home/08-07-2026/Vadhandhi Season 2.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ikZoI6wmvBQ</t>
+          <t>https://www.youtube.com/watch?v=7cCI3G8XmH8</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kaalam Paranja Kadha</t>
+          <t>Oh Sukumari</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2133,24 +2133,24 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>home/08-01-2026/Kaalam Paranja Kadha.jpg</t>
+          <t>home/08-07-2026/Oh Sukumari.jpg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Hox9qawUA-g</t>
+          <t>https://www.youtube.com/watch?v=TL0-kMdqt_s</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Vadala</t>
+          <t>Chennai Love Story</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2168,24 +2168,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Vadala.jpg</t>
+          <t>home/08-01-2026/Chennai Love Story.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
+          <t>https://www.youtube.com/watch?v=nYYjR9diizE</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mister Middle Class</t>
+          <t>Srinivasa Mangapuram</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2203,24 +2203,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Mister Middle Class.jpg</t>
+          <t>home/08-01-2026/Srinivasa Mangapuram.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
+          <t>https://www.youtube.com/watch?v=kKIqF2oyj1Q</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Transfer Trimurthulu</t>
+          <t>Jana Nayakudu</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2238,24 +2238,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Transfer Trimurthulu.jpg</t>
+          <t>home/08-01-2026/Jana Nayakudu.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=cnqP9cCU5Ak</t>
+          <t>https://www.youtube.com/watch?v=L81nWRwRmnI</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Hrudhayam Murali</t>
+          <t>Gatta Kusthi 2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2273,24 +2273,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
+          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
+          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Gedelaraju Kakinada Taluka</t>
+          <t>Police Complaint</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2308,24 +2308,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Gedelaraju Kakinada Taluka.jpg</t>
+          <t>home/08-01-2026/Police Complaint.jpg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=SBX2RFgxzYg</t>
+          <t>https://www.youtube.com/watch?v=87aOxmtPmX0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ek Din</t>
+          <t>Love Oh Love</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2343,24 +2343,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Ek Din.jpg</t>
+          <t>home/08-01-2026/Love Oh Love.jpg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
+          <t>https://www.youtube.com/watch?v=ikZoI6wmvBQ</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>The Odyssey</t>
+          <t>Balan</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2378,24 +2378,24 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>home/07-20-2026/The Odyssey.jpg</t>
+          <t>home/08-01-2026/Balan.jpg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=f_bKjZeJBBI</t>
+          <t>https://www.youtube.com/watch?v=cjWTqndgZ_M</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Vadala</t>
+          <t>Objection My Lord Season 1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2413,34 +2413,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Vadala.jpg</t>
+          <t>home/08-01-2026/Objection My Lord Season 1.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
+          <t>https://www.youtube.com/watch?v=Fhr9JdlLRwY</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Hijack 1971</t>
+          <t>Con City</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2448,24 +2448,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Hijack 1971.jpg</t>
+          <t>home/08-01-2026/Con City.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UxyutkXQnvA</t>
+          <t>https://www.youtube.com/watch?v=wT2VV6bq6hU</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Mister Middle Class</t>
+          <t>Pallichattambi</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2483,24 +2483,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Mister Middle Class.jpg</t>
+          <t>home/08-01-2026/Pallichattambi.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
+          <t>https://www.youtube.com/watch?v=k6WQlVFkvgg</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ek Din</t>
+          <t>Chinna Chinna Aasai</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2518,24 +2518,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Ek Din.jpg</t>
+          <t>home/08-01-2026/Chinna Chinna Aasai.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
+          <t>https://www.youtube.com/watch?v=f_mCvoMgoYs</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ek Din</t>
+          <t>Balan</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2553,24 +2553,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Ek Din.jpg</t>
+          <t>home/08-01-2026/Balan.jpg</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
+          <t>https://www.youtube.com/watch?v=cjWTqndgZ_M</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Thiraivi</t>
+          <t>Spider-Man: Brand New Day</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2588,24 +2588,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Thiraivi.jpg</t>
+          <t>home/08-01-2026/Spider-Man Brand New Day.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=YMLv6vV43Vo</t>
+          <t>https://www.youtube.com/watch?v=62bIsvRcPv0</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Hrudhayam Murali</t>
+          <t>Objection My Lord Season 1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2623,34 +2623,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
+          <t>home/08-01-2026/Objection My Lord Season 1.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
+          <t>https://www.youtube.com/watch?v=Fhr9JdlLRwY</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>13 Days, 13 Nights</t>
+          <t>Srinivasa Mangapuram</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2658,24 +2658,24 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>home/07-20-2026/13 Days, 13 Nights.jpg</t>
+          <t>home/08-01-2026/Srinivasa Mangapuram.jpg</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=mAKOqFt-LVQ</t>
+          <t>https://www.youtube.com/watch?v=kKIqF2oyj1Q</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>23 000 Lives</t>
+          <t>Son of Sara: Volume 1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2693,34 +2693,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>home/07-20-2026/23 000 Lives.jpg</t>
+          <t>home/08-01-2026/Son of Sara Volume 1.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=89dugTvBEWw</t>
+          <t>https://www.youtube.com/watch?v=ZTkXpVGpcRk</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Chithini</t>
+          <t>Police Complaint</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2728,24 +2728,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>home/07-20-2026/Chithini.jpg</t>
+          <t>home/08-01-2026/Police Complaint.jpg</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=pRbfgUVGAJg</t>
+          <t>https://www.youtube.com/watch?v=-q63oK7GhI0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Lenin</t>
+          <t>Chum</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2763,24 +2763,24 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Lenin.jpg</t>
+          <t>home/08-01-2026/Chum.jpg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
+          <t>https://www.youtube.com/watch?v=VUdPlZgXOjE</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ikka</t>
+          <t>Gatta Kusthi 2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2798,24 +2798,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Ikka.jpg</t>
+          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
+          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mukhbir: The Story of a Spy</t>
+          <t>Gatta Kusthi 2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2833,24 +2833,24 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
+          <t>home/08-01-2026/Gatta Kusthi 2.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
+          <t>https://www.youtube.com/watch?v=18HeyuDeLbY</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Tholaivil Oru Kadhal</t>
+          <t>Love Oh Love</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2868,34 +2868,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Tholaivil Oru Kadhal.jpg</t>
+          <t>home/08-01-2026/Love Oh Love.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=bR1s6WIsyfE</t>
+          <t>https://www.youtube.com/watch?v=ikZoI6wmvBQ</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>The Trip</t>
+          <t>Kaalam Paranja Kadha</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2903,34 +2903,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>home/07-13-2026/The Trip.jpg</t>
+          <t>home/08-01-2026/Kaalam Paranja Kadha.jpg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=K9bPJmy68Rs</t>
+          <t>https://www.youtube.com/watch?v=Hox9qawUA-g</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hollow Man 2</t>
+          <t>Vadala</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2938,24 +2938,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Hollow Man 2.jpg</t>
+          <t>home/07-20-2026/Vadala.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=koZuEDeQf3Q</t>
+          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Lenin</t>
+          <t>Mister Middle Class</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2973,34 +2973,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Lenin.jpg</t>
+          <t>home/07-20-2026/Mister Middle Class.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
+          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Only the Brave</t>
+          <t>Transfer Trimurthulu</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3008,24 +3008,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Only the Brave.jpg</t>
+          <t>home/07-20-2026/Transfer Trimurthulu.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=EE_GY6zccqc</t>
+          <t>https://www.youtube.com/watch?v=cnqP9cCU5Ak</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Dhamaal 4</t>
+          <t>Hrudhayam Murali</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3043,24 +3043,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Dhamaal 4.jpg</t>
+          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=IG-eByZdz6Y</t>
+          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ikka</t>
+          <t>Gedelaraju Kakinada Taluka</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3078,24 +3078,24 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Ikka.jpg</t>
+          <t>home/07-20-2026/Gedelaraju Kakinada Taluka.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
+          <t>https://www.youtube.com/watch?v=SBX2RFgxzYg</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Mukhbir: The Story of a Spy</t>
+          <t>Ek Din</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3113,24 +3113,24 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
+          <t>home/07-20-2026/Ek Din.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
+          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Shikhandi</t>
+          <t>The Odyssey</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3148,24 +3148,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>home/07-13-2026/Shikhandi.jpg</t>
+          <t>home/07-20-2026/The Odyssey.jpg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vLuLhH7oREY</t>
+          <t>https://www.youtube.com/watch?v=f_bKjZeJBBI</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Vadala</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3183,34 +3183,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-20-2026/Vadala.jpg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=BntzaB_nZNQ</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Hijack 1971</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3218,24 +3218,24 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-20-2026/Hijack 1971.jpg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=UxyutkXQnvA</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Mister Middle Class</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3253,24 +3253,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-20-2026/Mister Middle Class.jpg</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=4NrHIWfX3n8</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Ek Din</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3288,24 +3288,24 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-20-2026/Ek Din.jpg</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Ek Din</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3323,24 +3323,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-20-2026/Ek Din.jpg</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=RCmyr_d3Hi0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Thiraivi</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3358,24 +3358,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-20-2026/Thiraivi.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=YMLv6vV43Vo</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>Hrudhayam Murali</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3393,34 +3393,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-20-2026/Hrudhayam Murali.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=7RCeBn0n9IA</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Pati Patni Aur Woh Do</t>
+          <t>13 Days, 13 Nights</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3428,24 +3428,24 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Pati Patni Aur Woh Do.jpg</t>
+          <t>home/07-20-2026/13 Days, 13 Nights.jpg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ceooxuS-sww</t>
+          <t>https://www.youtube.com/watch?v=mAKOqFt-LVQ</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Dose</t>
+          <t>23 000 Lives</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3463,34 +3463,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Dose.jpg</t>
+          <t>home/07-20-2026/23 000 Lives.jpg</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
+          <t>https://www.youtube.com/watch?v=89dugTvBEWw</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Chithini</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3498,24 +3498,24 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-20-2026/Chithini.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=pRbfgUVGAJg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Lenin</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3533,24 +3533,24 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-13-2026/Lenin.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Parimala and Co</t>
+          <t>Ikka</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3568,24 +3568,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Parimala and Co.jpg</t>
+          <t>home/07-13-2026/Ikka.jpg</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
+          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Double Occupancy</t>
+          <t>Mukhbir: The Story of a Spy</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3603,24 +3603,24 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Double Occupancy.jpg</t>
+          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
+          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Tholaivil Oru Kadhal</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3638,34 +3638,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/Tholaivil Oru Kadhal.jpg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=bR1s6WIsyfE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>The Trip</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3673,34 +3673,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/The Trip.jpg</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=K9bPJmy68Rs</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Balti</t>
+          <t>Hollow Man 2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3708,24 +3708,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>home/07-09-2026/Balti.jpg</t>
+          <t>home/07-13-2026/Hollow Man 2.jpg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
+          <t>https://www.youtube.com/watch?v=koZuEDeQf3Q</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Nagabandham</t>
+          <t>Lenin</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3743,34 +3743,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Nagabandham.jpg</t>
+          <t>home/07-13-2026/Lenin.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
+          <t>https://www.youtube.com/watch?v=_d8Gw4ZkEqs</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Chand Mera Dil</t>
+          <t>Only the Brave</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu Dubbed</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3778,24 +3778,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Chand Mera Dil.jpg</t>
+          <t>home/07-13-2026/Only the Brave.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rRQ8oKCoYrQ</t>
+          <t>https://www.youtube.com/watch?v=EE_GY6zccqc</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Kotha Malupu</t>
+          <t>Dhamaal 4</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3813,24 +3813,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Kotha Malupu.jpg</t>
+          <t>home/07-13-2026/Dhamaal 4.jpg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=qnd1Xwv9NP8</t>
+          <t>https://www.youtube.com/watch?v=IG-eByZdz6Y</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Double Barrel</t>
+          <t>Ikka</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3848,24 +3848,24 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Double Barrel.jpg</t>
+          <t>home/07-13-2026/Ikka.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=Ij0mjRt1QIA</t>
+          <t>https://www.youtube.com/watch?v=unf8x_aZg9Y</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Nagabandham</t>
+          <t>Mukhbir: The Story of a Spy</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3883,24 +3883,24 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>home/07-06-2026/Nagabandham.jpg</t>
+          <t>home/07-13-2026/Mukhbir The Story of a Spy.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
+          <t>https://www.youtube.com/watch?v=DHz6kJOdf90</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Shikhandi</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Kannada</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3918,24 +3918,24 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-13-2026/Shikhandi.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=vLuLhH7oREY</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Rao Bahadur</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3953,24 +3953,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>home/07-04-2026/Rao Bahadur.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3988,24 +3988,24 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4023,24 +4023,24 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4058,24 +4058,24 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4093,24 +4093,24 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Alpha</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4128,24 +4128,24 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Alpha.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=QRqGwGwo1Y0</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Pritam and Pedro Season 1</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4163,24 +4163,24 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Pritam and Pedro Season 1.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=rEtzygjtBrs</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Charukesi</t>
+          <t>Pati Patni Aur Woh Do</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4198,24 +4198,24 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Charukesi.jpg</t>
+          <t>home/07-09-2026/Pati Patni Aur Woh Do.jpg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3QLKK5UqJbI</t>
+          <t>https://www.youtube.com/watch?v=ceooxuS-sww</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Dose</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Malayalam</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4233,24 +4233,24 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Dose.jpg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=_ZlWpPcMlig</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Daadi Ki Shaadi</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4268,24 +4268,24 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Daadi Ki Shaadi.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=vMYy2bNc9YU</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Hangman</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4303,24 +4303,24 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Hangman.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=A_ga4aC0yOo</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Parimala and Co</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4338,24 +4338,24 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Parimala and Co.jpg</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=x9qiUBtFgH4</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Double Occupancy</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4365,7 +4365,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4373,24 +4373,24 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Double Occupancy.jpg</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=6QNUFgR2HLk</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Mollywood Times</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Malayalam</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4408,24 +4408,24 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Mollywood Times.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4443,24 +4443,24 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Karakkam</t>
+          <t>Balti</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4478,24 +4478,24 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>home/07-03-2026/Karakkam.jpg</t>
+          <t>home/07-09-2026/Balti.jpg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=AhincTvRnAk</t>
+          <t>https://www.youtube.com/watch?v=lPXF3zGrmCU</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4513,24 +4513,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Chand Mera Dil</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Telugu</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4548,24 +4548,24 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-06-2026/Chand Mera Dil.jpg</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=rRQ8oKCoYrQ</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Super Subbu Season 1</t>
+          <t>Kotha Malupu</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4583,24 +4583,24 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Subbu Season 1.jpg</t>
+          <t>home/07-06-2026/Kotha Malupu.jpg</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=dgWHvUjtDJE</t>
+          <t>https://www.youtube.com/watch?v=qnd1Xwv9NP8</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Isakapatnam Season 1</t>
+          <t>Double Barrel</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4618,34 +4618,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Isakapatnam Season 1.jpg</t>
+          <t>home/07-06-2026/Double Barrel.jpg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y9QWCzuZOtQ</t>
+          <t>https://www.youtube.com/watch?v=Ij0mjRt1QIA</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Bossa Nova</t>
+          <t>Nagabandham</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4653,24 +4653,24 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Bossa Nova.jpg</t>
+          <t>home/07-06-2026/Nagabandham.jpg</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=y5GD52Hi3oE</t>
+          <t>https://www.youtube.com/watch?v=4YkbZTSoG2g</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Super Dog and Super Cat</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4688,24 +4688,24 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>home/07-02-2026/Super Dog and Super Cat.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=PV6lzAJTfMk</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Rao Bahadur</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4723,24 +4723,24 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-04-2026/Rao Bahadur.jpg</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=aevbXGQKlw8</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Enola Holmes 3</t>
+          <t>Mollywood Times</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Telugu Dubbed</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4758,24 +4758,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Enola Holmes 3.jpg</t>
+          <t>home/07-03-2026/Mollywood Times.jpg</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=n_pEJjq-9xQ</t>
+          <t>https://www.youtube.com/watch?v=1BwH4jpVv6c</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Elra Kaaleliyatte Kaala</t>
+          <t>Karakkam</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Kannada</t>
+          <t>Telugu</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4793,24 +4793,24 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>home/07-01-2026/Elra Kaaleliyatte Kaala.jpg</t>
+          <t>home/07-03-2026/Karakkam.jpg</t>
         </is>
 